--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2140,6 +2140,76 @@
       <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IM-020</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر + vHigh/vLow زباله به Imbalance_Evaluate بده</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ماژول باید روی valid گیت بزند و بدون episode کاذب بماند؛ ورودی‌ها از task_control صفر شده</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>بدون episode کاذب</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -751,7 +751,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>اختلاف دو نیم را با بار نامتقارن به بالای ۳۰۰mV ببر و ۳۰ ثانیه نگه دار</t>
+          <t>گام ۱: صبر کن دست‌کم 10 دقیقه از پایان شارژ گذشته باشد (گیت زمانی استراحت تمام شده باشد) و شمارندهٔ رویداد (events) فعلی را از پنل یادداشت کن.
+گام ۲: با بار نامتقارن روی دو نیم‌باتری، اختلاف ولتاژ دو نیم را بالای 300 میلی‌ولت ببر.
+گام ۳: اختلاف را 30 ثانیه پیوسته بالای حد نگه دار.
+گام ۴: در پنل ببین: دقیقاً یک رویداد شمرده شده باشد (events = قبلی + 1).</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -834,7 +837,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>بلافاصله پس از پایان شارژ اختلاف را بالای حد نگه دار</t>
+          <t>گام ۱: یک شارژ را تازه تمام کن و شمارندهٔ events را یادداشت کن.
+گام ۲: بلافاصله بعد از پایان شارژ، اختلاف دو نیم را بالای 300 میلی‌ولت ببر و نگه دار.
+گام ۳: تا دقیقهٔ 10 بعد از پایان شارژ نگاه کن: هیچ رویدادی نباید شمرده شود (گیت استراحت هنوز بسته است).
+گام ۴: وقتی 10 دقیقه گذشت و اختلاف هنوز بالاست، شمارش باید از همان‌جا شروع شود.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -917,7 +923,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>حین دشارژ اختلاف را بالای ۵۰۰mV ببر</t>
+          <t>گام ۱: خروجی را روی باتری بگذار (در حال دشارژ باشد) و شمارندهٔ events را یادداشت کن.
+گام ۲: حین دشارژ اختلاف دو نیم را بالای 500 میلی‌ولت ببر.
+گام ۳: 30 ثانیه نگه دار.
+گام ۴: چون روی باتری هستیم، بدون نیاز به گیت زمانی 10 دقیقه‌ای باید یک رویداد شمرده شود (events = قبلی + 1).</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1000,7 +1009,10 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>اختلاف را دقیقاً به زیر حد منهای ۱۰۰mV بیاور و دوباره بالا ببر</t>
+          <t>گام ۱: یک اپیزود فعال بساز (اختلاف بالای حد مثل IM-001) و events را یادداشت کن.
+گام ۲: اختلاف را دقیقاً به زیر «حد منهای 100 میلی‌ولت» بیاور تا اپیزود بسته شود.
+گام ۳: دوباره اختلاف را بالای حد ببر تا اپیزود دوم شروع شود.
+گام ۴: این رفت‌وبرگشت را 2 چرخه انجام بده؛ هر اپیزود باید فقط یک‌بار شمرده شود (در مجموع دقیقاً +1 برای هر اپیزود).</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1083,7 +1095,9 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>اختلاف را ۶۰ ثانیه در بازهٔ حد تا حد منهای هیسترزیس نگه دار</t>
+          <t>گام ۱: اختلاف دو نیم را به نزدیک حد برسان (در بازهٔ 200 تا 300 میلی‌ولت، یعنی داخل هیسترزیس).
+گام ۲: 60 ثانیه همان‌جا نگه دار و events را نگاه کن.
+گام ۳: نه رویداد تازه‌ای باید شمرده شود نه اپیزود به‌صورت نوسانی باز و بسته شود؛ events باید بی‌تغییر بماند.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1166,7 +1180,10 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>برق برد را کاملاً قطع و وصل کن</t>
+          <t>گام ۱: چند رویداد بساز تا events بزرگ‌تر از صفر شود و مقدارش را یادداشت کن.
+گام ۲: برق برد را کاملاً قطع کن و دوباره وصل کن.
+گام ۳: بعد از بوت، events را در پنل بخوان: باید دقیقاً همان مقدار قبل از قطع باشد (از NVM برگشته، ریست نشده).
+گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر بار همان عدد را باید ببینی.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1249,7 +1266,10 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>یک رویداد دیگر بساز تا به ۱۰ برسد</t>
+          <t>گام ۱: شمارندهٔ events را به 9 برسان.
+گام ۲: یک رویداد دیگر بساز تا به 10 برسد (رویداد دهم).
+گام ۳: به چراغ‌ها نگاه کن: قفل باید فعال شده باشد؛ LED قرمز چشمک‌زن و سبز و زرد خاموش.
+گام ۴: در پنل چک کن اسلات 202 برابر 1 باشد و چشمک قرمز مطابق پارامترهای 123 (دوره) و 124 (سهم روشنی) باشد.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1332,7 +1352,10 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>دورهٔ ۱۲۳ و سهم روشنی ۱۲۴ را اندازه بگیر</t>
+          <t>گام ۱: قفل را فعال نگه دار (IM-007).
+گام ۲: پارامتر 123 (دورهٔ چشمک) را 1000 میلی‌ثانیه و پارامتر 124 (سهم روشنی) را 50 درصد بگذار.
+گام ۳: با کرنومتر یا اسیلوسکوپ یک دورهٔ کامل چشمک قرمز را اندازه بگیر و مدت روشنی را هم بخوان.
+گام ۴: در 60 ثانیه چند دوره را چک کن: دوره باید 1000 میلی‌ثانیه و روشنی 50 درصد باشد، با خطای حداکثر ±5 درصد.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1415,7 +1438,10 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>یک ساعت کامل منتظر بمان یا ۱۱۵ را موقتاً کوچک کن</t>
+          <t>گام ۱: قفل فعال باشد.
+گام ۲: برای کوتاه شدن تست می‌توانی پارامتر 115 (دورهٔ بوق) را موقتاً کوچک کنی، وگرنه یک ساعت کامل باید صبر کنی.
+گام ۳: یک دورهٔ کامل (پارامتر 115) منتظر بمان.
+گام ۴: باید یک بوق کوتاه شنیده و دیده شود و طولش برابر پارامتر 116 باشد.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1498,7 +1524,10 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>ورودی را قطع کن تا سیستم بخواهد روی باتری برود</t>
+          <t>گام ۱: قفل فعال باشد و تیک پارامتر 117 (مسدودی خروجی بعد از قفل) خورده باشد.
+گام ۲: ورودی را قطع کن تا سیستم بخواهد روی باتری برود.
+گام ۳: 30 ثانیه رلهٔ خروجی را مستقیم اندازه بگیر.
+گام ۴: باتری هرگز نباید روی خروجی وصل شود؛ رلهٔ خروجی نباید وصل شود.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1581,7 +1610,10 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>پارامتر ۱۱۷ را صفر کن</t>
+          <t>گام ۱: قفل فعال باشد (IM-007).
+گام ۲: پارامتر 117 را صفر کن (block_output_en = 0).
+گام ۳: 30 ثانیه نگاه کن: وتوی خروجی باید برداشته شود و خروجی مجاز شود.
+گام ۴: ولی قفل و چهرهٔ قرمز باید سر جایشان بمانند؛ اسلات 202 همچنان 1 است.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1664,7 +1696,10 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>۲۰ سیکل کامل شارژ را در حالت قفل بگذران</t>
+          <t>گام ۱: قفل فعال باشد.
+گام ۲: در حالت قفل، 20 سیکل کامل شارژ را یکی‌یکی بگذران (هر سیکل تا FLOAT واقعی).
+گام ۳: شمارندهٔ سیکل‌ها را نگاه کن که به پارامتر 118 برسد.
+گام ۴: بعد از رسیدن به سقف 118، شارژ همان پک باید مسدود شود: اسلات 201 باید 20 باشد و هیچ‌کدام از دو کانال دیگر شارژ نکنند.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1747,7 +1782,10 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>هر دو نیم‌باتری را ۳ ثانیهٔ کامل جدا نگه دار</t>
+          <t>گام ۱: قفل فعال و شمارنده‌ها پر باشند؛ مقادیر اسلات‌های 200 تا 202 را یادداشت کن.
+گام ۲: هر دو نیم‌باتری را کامل جدا کن (باتری نباشد).
+گام ۳: دقیقاً 3 ثانیهٔ کامل جدا نگه دار.
+گام ۴: باتری را وصل کن و اسلات‌ها را بخوان: همهٔ شمارنده‌ها و خود قفل باید صفر و ریست شده باشند (هر سه اسلات 200، 201 و 202 صفر).</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1830,7 +1868,10 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>باتری را کمتر از ۳ ثانیه جدا کن</t>
+          <t>گام ۱: قفل فعال باشد و مقادیر اسلات‌ها را یادداشت کن.
+گام ۲: باتری را جدا کن ولی کمتر از 3 ثانیه (مثلاً 1 ثانیه) و دوباره وصل کن.
+گام ۳: این کار را 5 بار تکرار کن.
+گام ۴: هیچ ریستی نباید رخ داده باشد؛ اسلات‌ها باید دقیقاً همان مقادیر گام ۱ باشند.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1913,7 +1954,10 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>برای هر پارامتر ۱۰۸..۱۱۸ و ۱۲۳..۱۲۴ مقدار بیرون از بازه بفرست</t>
+          <t>گام ۱: لینک ESP را برقرار کن.
+گام ۲: برای هر یک از پارامترهای 108 تا 118 و 123 و 124، یک مقدار بیرون از بازهٔ مجاز بفرست (یکی‌یکی، هر کدام یک تبادل).
+گام ۳: پاسخ برد را بخوان: هر مقدار یا باید رد شود یا به نزدیک‌ترین حد مجاز گیره (clamp) شود و مقدار اعمال‌شده برگردانده شود.
+گام ۴: هر پارامتر را با GET دوباره بخوان؛ مقدار نهایی باید داخل بازهٔ مجاز باشد.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1996,7 +2040,10 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>یک یا چند پارامتر سناریو ۵ را از پنل تغییر بده و ذخیره کن، سپس تغذیه را کامل قطع و دوباره وصل کن و همان پارامترها را از پنل بخوان</t>
+          <t>گام ۱: دستگاه روشن و پنل وصل باشد؛ مقادیر فعلی پارامترهای سناریو ۵ را یادداشت کن.
+گام ۲: یک یا چند پارامتر را عوض کن؛ مثلاً پارامتر 108 را 450 میلی‌ولت و پارامتر 112 را 45000 میلی‌ثانیه بگذار و ذخیره کن تا در NVM بنشیند.
+گام ۳: تغذیه را کاملاً قطع کن و دوباره وصل کن.
+گام ۴: همان پارامترها را از پنل بخوان: هر پارامتر تغییرکرده باید دقیقاً همان مقدار قبل از قطع برق باشد؛ پارامترهای دست‌نخورده باید پیش‌فرض خودشان را نشان دهند، نه اینکه پیش‌فرض کامپایل جای همه را گرفته باشد.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2083,7 +2130,10 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>پس از ثبت رویداد/قفل، تغذیه را قطع و وصل کن و شمارنده‌ها را در پنل بخوان</t>
+          <t>گام ۱: دست‌کم یک رویداد بساز (events &gt; 0) و اگر می‌توانی قفل را هم فعال کن (latched = 1)؛ هر سه مقدار events و cycles و latched را یادداشت کن.
+گام ۲: تغذیه را کاملاً قطع کن و دوباره وصل کن.
+گام ۳: بعد از بوت شمارنده‌ها و وضعیت قفل را در پنل بخوان.
+گام ۴: هر سه باید دقیقاً همان مقادیر قبل از قطع برق باشند.</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2166,7 +2216,9 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>snapshot نامعتبر + vHigh/vLow زباله به Imbalance_Evaluate بده</t>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و ولتاژهای بالا/پایین (vHigh/vLow) را عمداً زباله بگذار.
+گام ۲: آن را 3 ثانیه به Imbalance_Evaluate بده (ورودی‌ها را task_control از قبل صفر می‌کند).
+گام ۳: شمارنده و وضعیت اپیزود را نگاه کن: ماژول باید روی valid گیت بزند و هیچ اپیزود کاذبی نباید ساخته شود.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2199,14 +2251,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>events بدون تغییر تا سپری‌شدن ۱۱۰</t>
+          <t>events بدون تغییر تا سپری‌شدن مهلت پارامتر 110 (پیش‌فرض 10 دقیقه، یعنی 600000 میلی‌ثانیه) از پایان شارژ</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +68,74 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +152,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,11 +195,25 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -142,6 +247,89 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,6 +693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -515,21 +704,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Imbalance</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Imbalance | سناریوی ۵: قضاوت عدم‌توازن دو نیم‌باتری با شمارش ماندگار رویداد و قفل</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -539,55 +728,58 @@
       <c r="A4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>سناریوی ۵: پایش قدرمطلق اختلاف دو نیم‌باتری ۱۲ ولتی |v_bat_high - v_bat_low| و قضاوت عدم‌توازن با شمارش ماندگار رویداد.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>ماژول منطق خالص است: همهٔ ورودی‌ها و زمان جاری از بیرون می‌آیند و هیچ وابستگی به BSP یا RTOS ندارد؛ سیم‌بندی در task_control.c است.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>گیت زمانی: حد استراحت (۱۰۸) فقط در استراحت و پس از ۱۱۰ از پایان شارژ، و حین شارژ پس از ۱۱۱؛ در دشارژ حد ۱۰۹ بلافاصله اعمال می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>رویداد = فراتر از حد به‌طور پیوسته برای ۱۱۲؛ پایان اپیزود با هیسترزیس ۱۱۳؛ هر اپیزود فقط یک‌بار شمرده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>رویدادها ≥ ۱۱۴ → قفل: قرمز چشمک‌زن + بوق ساعتی + وتوی خروجی (در صورت تیک ۱۱۷)؛ ۱۱۸ سیکل شارژ در قفل → مسدودی شارژ.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>نبود باتری برای ۳ ثانیهٔ پیوسته = تعویض واقعی → ریست خودکار همهٔ شمارنده‌ها و قفل.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>شمارنده‌ها در اسلات‌های ۲۰۰..۲۰۲ ماندگارند و با قطع برق پاک نمی‌شوند. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -595,161 +787,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Imbalance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="15" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="15" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>IM-001</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>آستانهٔ استراحت</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>بیش از ۱۰ دقیقه از پایان شارژ گذشته</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>گام ۱: صبر کن دست‌کم 10 دقیقه از پایان شارژ گذشته باشد (گیت زمانی استراحت تمام شده باشد) و شمارندهٔ رویداد (events) فعلی را از پنل یادداشت کن.
 گام ۲: با بار نامتقارن روی دو نیم‌باتری، اختلاف ولتاژ دو نیم را بالای 300 میلی‌ولت ببر.
@@ -757,85 +950,85 @@
 گام ۴: در پنل ببین: دقیقاً یک رویداد شمرده شده باشد (events = قبلی + 1).</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>|اختلاف| &gt; ۳۰۰mV</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>یک رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>شمارنده ماندگار</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>events = قبلی + ۱ در پنل</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="M5" s="21" t="n"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>IM-002</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>گیت زمانی پس از شارژ</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>شارژ تازه تمام شده</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>گام ۱: یک شارژ را تازه تمام کن و شمارندهٔ events را یادداشت کن.
 گام ۲: بلافاصله بعد از پایان شارژ، اختلاف دو نیم را بالای 300 میلی‌ولت ببر و نگه دار.
@@ -843,85 +1036,85 @@
 گام ۴: وقتی 10 دقیقه گذشت و اختلاف هنوز بالاست، شمارش باید از همان‌جا شروع شود.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>|اختلاف| &gt; ۳۰۰mV</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>تا دقیقهٔ ۱۰</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>تا پیش از ۱۰ دقیقه هیچ رویدادی شمرده نمی‌شود</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>بدون شمارش</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>events بدون تغییر تا سپری‌شدن مهلت پارامتر 110 (پیش‌فرض 10 دقیقه، یعنی 600000 میلی‌ثانیه) از پایان شارژ</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="M6" s="26" t="n"/>
+      <c r="N6" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O6" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>IM-003</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>آستانهٔ دشارژ</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>خروجی روی باتری</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>گام ۱: خروجی را روی باتری بگذار (در حال دشارژ باشد) و شمارندهٔ events را یادداشت کن.
 گام ۲: حین دشارژ اختلاف دو نیم را بالای 500 میلی‌ولت ببر.
@@ -929,85 +1122,85 @@
 گام ۴: چون روی باتری هستیم، بدون نیاز به گیت زمانی 10 دقیقه‌ای باید یک رویداد شمرده شود (events = قبلی + 1).</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>|اختلاف| &gt; ۵۰۰mV و onBattery</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>بدون نیاز به گیت زمانی، رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>شمارنده ماندگار</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>events = قبلی + ۱</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>IM-004</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>هیسترزیس پایان اپیزود</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>یک اپیزود فعال</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>گام ۱: یک اپیزود فعال بساز (اختلاف بالای حد مثل IM-001) و events را یادداشت کن.
 گام ۲: اختلاف را دقیقاً به زیر «حد منهای 100 میلی‌ولت» بیاور تا اپیزود بسته شود.
@@ -1015,170 +1208,170 @@
 گام ۴: این رفت‌وبرگشت را 2 چرخه انجام بده؛ هر اپیزود باید فقط یک‌بار شمرده شود (در مجموع دقیقاً +1 برای هر اپیزود).</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>عبور از حد و بازگشت</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>۲ چرخه</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>هر اپیزود فقط یک‌بار شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>بدون شمارش مضاعف</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>events دقیقاً +۱ به ازای هر اپیزود</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O8" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q8" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>IM-005</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>نوسان دور حد</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>اختلاف نزدیک حد</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>گام ۱: اختلاف دو نیم را به نزدیک حد برسان (در بازهٔ 200 تا 300 میلی‌ولت، یعنی داخل هیسترزیس).
 گام ۲: 60 ثانیه همان‌جا نگه دار و events را نگاه کن.
 گام ۳: نه رویداد تازه‌ای باید شمرده شود نه اپیزود به‌صورت نوسانی باز و بسته شود؛ events باید بی‌تغییر بماند.</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>۲۰۰..۳۰۰mV</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>۶۰ ثانیه</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>نه رویداد تازه نه پایان نوسانی اپیزود</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>events بدون تغییر</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L9" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q9" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>IM-006</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>events &gt; 0</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>گام ۱: چند رویداد بساز تا events بزرگ‌تر از صفر شود و مقدارش را یادداشت کن.
 گام ۲: برق برد را کاملاً قطع کن و دوباره وصل کن.
@@ -1186,85 +1379,85 @@
 گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر بار همان عدد را باید ببینی.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>قطع کامل تغذیه</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>۳ بار</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>شمارنده از NVM بازمی‌گردد و ادامه می‌یابد (ریست نمی‌شود)</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>اسلات ۲۰۰ ماندگار</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>events پس از بوت برابر پیش از قطع</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="M10" s="26" t="n"/>
+      <c r="N10" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q10" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>IM-007</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>قفل شدن</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>events = ۹</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>گام ۱: شمارندهٔ events را به 9 برسان.
 گام ۲: یک رویداد دیگر بساز تا به 10 برسد (رویداد دهم).
@@ -1272,85 +1465,85 @@
 گام ۴: در پنل چک کن اسلات 202 برابر 1 باشد و چشمک قرمز مطابق پارامترهای 123 (دوره) و 124 (سهم روشنی) باشد.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>events ≥ ۱۱۴</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>یک رویداد</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>قفل فعال: LED قرمز چشمک‌زن، سبز و زرد خاموش</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>latch ماندگار</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>اسلات ۲۰۲ = ۱ و چهرهٔ LED مطابق ۱۲۳/۱۲۴</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O11" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q11" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>IM-008</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>چشمک قفل</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>گام ۱: قفل را فعال نگه دار (IM-007).
 گام ۲: پارامتر 123 (دورهٔ چشمک) را 1000 میلی‌ثانیه و پارامتر 124 (سهم روشنی) را 50 درصد بگذار.
@@ -1358,85 +1551,85 @@
 گام ۴: در 60 ثانیه چند دوره را چک کن: دوره باید 1000 میلی‌ثانیه و روشنی 50 درصد باشد، با خطای حداکثر ±5 درصد.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>۱۰۰۰ms و ۵۰٪</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>۶۰ ثانیه</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>چشمک قرمز با همان دوره و duty</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>اندازه‌گیری با کرنومتر یا اسیلوسکوپ در ±۵٪</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="M12" s="26" t="n"/>
+      <c r="N12" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O12" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P12" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>IM-009</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>بوق ساعتی</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد.
 گام ۲: برای کوتاه شدن تست می‌توانی پارامتر 115 (دورهٔ بوق) را موقتاً کوچک کنی، وگرنه یک ساعت کامل باید صبر کنی.
@@ -1444,85 +1637,85 @@
 گام ۴: باید یک بوق کوتاه شنیده و دیده شود و طولش برابر پارامتر 116 باشد.</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>دورهٔ ۱۱۵</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>یک دوره</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>یک بوق کوتاه به طول ۱۱۶</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>تکرارشونده</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>بوق دیده و شنیده می‌شود و طولش مطابق ۱۱۶ است</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O13" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>IM-010</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>وتوی خروجی</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>قفل فعال و تیک ۱۱۷ خورده</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد و تیک پارامتر 117 (مسدودی خروجی بعد از قفل) خورده باشد.
 گام ۲: ورودی را قطع کن تا سیستم بخواهد روی باتری برود.
@@ -1530,85 +1723,85 @@
 گام ۴: باتری هرگز نباید روی خروجی وصل شود؛ رلهٔ خروجی نباید وصل شود.</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>قطع ورودی</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>باتری هرگز روی خروجی سوئیچ نمی‌شود</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>وتو تا رفع قفل</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>رله خروجی وصل نمی‌شود (اندازه‌گیری مستقیم)</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="M14" s="26" t="n"/>
+      <c r="N14" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O14" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P14" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q14" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>IM-011</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>برداشتن تیک ۱۱۷</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد (IM-007).
 گام ۲: پارامتر 117 را صفر کن (block_output_en = 0).
@@ -1616,85 +1809,85 @@
 گام ۴: ولی قفل و چهرهٔ قرمز باید سر جایشان بمانند؛ اسلات 202 همچنان 1 است.</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>block_output_en = ۰</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>وتو برداشته می‌شود ولی قفل و چهرهٔ قرمز باقی می‌ماند</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>latch حفظ</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>اسلات ۲۰۲ همچنان ۱ و خروجی مجاز</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O15" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q15" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>IM-012</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>بودجهٔ سیکل شارژ</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد.
 گام ۲: در حالت قفل، 20 سیکل کامل شارژ را یکی‌یکی بگذران (هر سیکل تا FLOAT واقعی).
@@ -1702,85 +1895,85 @@
 گام ۴: بعد از رسیدن به سقف 118، شارژ همان پک باید مسدود شود: اسلات 201 باید 20 باشد و هیچ‌کدام از دو کانال دیگر شارژ نکنند.</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>cycles ≥ ۱۱۸</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>۲۰ سیکل</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>پس از رسیدن به ۱۱۸ شارژ همان پک مسدود می‌شود</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>مسدودی ماندگار</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>اسلات ۲۰۱ = ۲۰ و هر دو کانال شارژ نمی‌کنند</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="M16" s="26" t="n"/>
+      <c r="N16" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P16" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q16" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>IM-013</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>ریست با تعویض باتری</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>قفل فعال و شمارنده‌ها پر</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال و شمارنده‌ها پر باشند؛ مقادیر اسلات‌های 200 تا 202 را یادداشت کن.
 گام ۲: هر دو نیم‌باتری را کامل جدا کن (باتری نباشد).
@@ -1788,85 +1981,85 @@
 گام ۴: باتری را وصل کن و اسلات‌ها را بخوان: همهٔ شمارنده‌ها و خود قفل باید صفر و ریست شده باشند (هر سه اسلات 200، 201 و 202 صفر).</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>نبود باتری ≥ ۳۰۰۰ms</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>۳ ثانیه</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>همهٔ شمارنده‌ها و قفل ریست می‌شوند</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>ریست یک‌باره</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>اسلات‌های ۲۰۰..۲۰۲ همگی صفر</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O17" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>IM-014</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>جدا شدن کوتاه</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد و مقادیر اسلات‌ها را یادداشت کن.
 گام ۲: باتری را جدا کن ولی کمتر از 3 ثانیه (مثلاً 1 ثانیه) و دوباره وصل کن.
@@ -1874,85 +2067,85 @@
 گام ۴: هیچ ریستی نباید رخ داده باشد؛ اسلات‌ها باید دقیقاً همان مقادیر گام ۱ باشند.</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>نبود باتری &lt; ۳۰۰۰ms</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>۵ تکرار</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>هیچ ریستی رخ نمی‌دهد</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>latch حفظ</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>اسلات‌ها بدون تغییر</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="M18" s="26" t="n"/>
+      <c r="N18" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P18" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q18" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>IM-015</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>بازهٔ پارامترها</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>لینک ESP برقرار</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را برقرار کن.
 گام ۲: برای هر یک از پارامترهای 108 تا 118 و 123 و 124، یک مقدار بیرون از بازهٔ مجاز بفرست (یکی‌یکی، هر کدام یک تبادل).
@@ -1960,85 +2153,85 @@
 گام ۴: هر پارامتر را با GET دوباره بخوان؛ مقدار نهایی باید داخل بازهٔ مجاز باشد.</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>مقادیر خارج از حد</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>یک تبادل برای هرکدام</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>همه رد یا به حد گیره می‌شوند و مقدار اعمال‌شده برگردانده می‌شود</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>بدون مقدار نامعتبر</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>GET هر پارامتر داخل بازهٔ مجاز است</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q19" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>ماندگاری تنظیم‌ها پس از قطع برق</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل متصل</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه روشن و پنل وصل باشد؛ مقادیر فعلی پارامترهای سناریو ۵ را یادداشت کن.
 گام ۲: یک یا چند پارامتر را عوض کن؛ مثلاً پارامتر 108 را 450 میلی‌ولت و پارامتر 112 را 45000 میلی‌ثانیه بگذار و ذخیره کن تا در NVM بنشیند.
@@ -2046,89 +2239,89 @@
 گام ۴: همان پارامترها را از پنل بخوان: هر پارامتر تغییرکرده باید دقیقاً همان مقدار قبل از قطع برق باشد؛ پارامترهای دست‌نخورده باید پیش‌فرض خودشان را نشان دهند، نه اینکه پیش‌فرض کامپایل جای همه را گرفته باشد.</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>مثلاً ۱۰۸ = ۴۵۰mV و ۱۱۲ = ۴۵۰۰۰ms، ذخیره در NVM</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>یک چرخهٔ خاموش/روشن کامل</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>مقادیر ذخیره‌شده پس از روشن‌شدن دوباره خوانده می‌شوند و پیش‌فرض کامپایل جای آن‌ها را نمی‌گیرد</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>ماندگار در فلش</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>هر پارامتر تغییر‌یافته دقیقاً همان مقدار پیش از قطع برق را نشان دهد؛ پارامتر دست‌نخورده پیش‌فرض خود را داشته باشد</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="30" t="inlineStr">
         <is>
           <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="N20" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O20" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P20" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q20" s="29" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>IM-017</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>حداقل یک رویداد شمرده شده یا قفل فعال</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>گام ۱: دست‌کم یک رویداد بساز (events &gt; 0) و اگر می‌توانی قفل را هم فعال کن (latched = 1)؛ هر سه مقدار events و cycles و latched را یادداشت کن.
 گام ۲: تغذیه را کاملاً قطع کن و دوباره وصل کن.
@@ -2136,148 +2329,401 @@
 گام ۴: هر سه باید دقیقاً همان مقادیر قبل از قطع برق باشند.</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>events &gt; 0 و در صورت امکان latched = 1</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>یک چرخهٔ خاموش/روشن کامل</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>شمارش رویداد، شمارش سیکل و وضعیت قفل همان مقدار پیش از قطع برق می‌مانند</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>ماندگار در فلش</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>events / cycles / latched بدون تغییر پس از بوت</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="M21" s="21" t="n"/>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O21" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q21" s="25" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="40.5" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>IM-020</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و ولتاژهای بالا/پایین (vHigh/vLow) را عمداً زباله بگذار.
 گام ۲: آن را 3 ثانیه به Imbalance_Evaluate بده (ورودی‌ها را task_control از قبل صفر می‌کند).
 گام ۳: شمارنده و وضعیت اپیزود را نگاه کن: ماژول باید روی valid گیت بزند و هیچ اپیزود کاذبی نباید ساخته شود.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>ماژول باید روی valid گیت بزند و بدون episode کاذب بماند؛ ورودی‌ها از task_control صفر شده</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>بدون episode کاذب</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" s="26" t="n"/>
+      <c r="L22" s="32" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="M22" s="26" t="n"/>
+      <c r="N22" s="26" t="n"/>
+      <c r="O22" s="28" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="Q23" s="33">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="33">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="33">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="33">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="33">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="33">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="33">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="33">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="33">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="33">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="33">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="33">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="33">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="33">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="33">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="33">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="33">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="33">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="33">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="33">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="33">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="33">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="33">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="33">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="33">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="33">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="33">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="33">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="33">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="33">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="33">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="33">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="33">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="33">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="33">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="33">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="33">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="33">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="33">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="33">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q22"/>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2291,305 +2737,310 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Imbalance</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>حد استراحت</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>۳۰۰mV (پیش‌فرض)</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>شمارش رویداد پس از پایداری</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_REST_LIMIT_MV (۱۰۸) / IMBAL_DEF_REST_LIMIT_MV</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>فقط با گیت زمانی</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>حد دشارژ</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>۵۰۰mV (پیش‌فرض)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>اعمال بلافاصله روی باتری</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_DISCHARGE_LIMIT_MV (۱۰۹)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>بدون گیت زمانی</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>گیت پس از شارژ</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>۱۰ دقیقه</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>پیش از آن بدون قضاوت</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_POST_CHARGE_WAIT_MS (۱۱۰)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>لنگر بوت اگر شارژی تمام نشده</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>گیت حین شارژ</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>۱۰ دقیقه</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>صفر یعنی خاموش</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_IN_CHARGE_WAIT_MS (۱۱۱)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>با همان حد استراحت</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>پایداری</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>۳۰ ثانیه پیوسته</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>یک رویداد</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_STABILITY_MS (۱۱۲)</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>هر اپیزود یک‌بار</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>۱۰۰mV</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>پایان اپیزود</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_HYSTERESIS_MV (۱۱۳)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>ضد نوسان</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>آستانهٔ قفل</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>۱۰ رویداد</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن + بوق + وتو</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_MAX_EVENTS (۱۱۴)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>شمارش ماندگار</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>بودجهٔ سیکل</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>۲۰ سیکل در قفل</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>مسدودی شارژ همان پک</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_MAX_LATCHED_CYCLES (۱۱۸)</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>شارژ در قفل آزاد است</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>ریست تعویض</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>نبود باتری ۳ ثانیه</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>ریست شمارنده‌ها و قفل</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>IMBAL_ABSENT_RESET_MS</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>تعویض واقعی باتری</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>اسلات‌های ماندگار</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>۲۰۰ رویداد، ۲۰۱ سیکل، ۲۰۲ قفل</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>بقا پس از قطع برق</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>IMBAL_SLOT_*_ID</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>فقط پخش NVM</t>
         </is>
@@ -2603,6 +3054,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2625,154 +3077,172 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Imbalance</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="34" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="34" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="34" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="34" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="34" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="34" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="34" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="34" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>DEF-IM-001</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>تنظیم‌های ذخیره‌شدهٔ سناریو ۵ با هر بار روشن‌شدن به پیش‌فرض کامپایل برمی‌گشت</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>یک پارامتر ۱۰۸..۱۱۸ را از پنل تغییر و ذخیره کن؛ تغذیه را قطع و وصل کن؛ همان پارامتر را بخوان</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>مقدار ذخیره‌شده باقی بماند</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>مقدار پیش‌فرض کامپایل خوانده می‌شد</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>تست هاست host_test_imbalance.c (بلوک رگرسیون v1.81)</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>ممیزی ۲۰۲۶-۱۰-۰۶</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>func__Imbalance_Init() در imbalance.c کل جدول پارامتر را بی‌قید به پیش‌فرض برمی‌گرداند، در حالی که بازپخش NVM پیش از آن اجرا می‌شود</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="34" t="inlineStr">
         <is>
           <t>اصلاح شد</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t>با func__Imbalance_SeedDefaultsOnce() پیش‌فرض‌ها فقط یک‌بار نوشته می‌شوند؛ تست هاست با ۵۰۴۱ بررسی و ۰ خطا قبول شد — تأیید نهایی منوط به تست روی برد</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2780,6 +3250,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2792,203 +3263,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Imbalance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Imbalance — سناریوی ۵ عدم‌توازن دو نیم‌باتری</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>2026-10-05 (1.0 — ساخته‌شده در ممیزی کل برنامه)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + بار نامتقارن قابل تنظیم + کرنومتر</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="17">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="17">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="17">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="17">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -3002,6 +3475,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3013,70 +3487,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -3090,7 +3571,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3102,55 +3583,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول عدم‌توازن (سناریوی ۵)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>Imbalance_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -3163,6 +3645,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,6 +137,13 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -213,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -330,6 +340,12 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2387,320 +2403,247 @@
       </c>
     </row>
     <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>IM-020</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>snapshot zeroing</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و ولتاژهای بالا/پایین (vHigh/vLow) را عمداً زباله بگذار.
-گام ۲: آن را 3 ثانیه به Imbalance_Evaluate بده (ورودی‌ها را task_control از قبل صفر می‌کند).
-گام ۳: شمارنده و وضعیت اپیزود را نگاه کن: ماژول باید روی valid گیت بزند و هیچ اپیزود کاذبی نباید ساخته شود.</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>ماژول باید روی valid گیت بزند و بدون episode کاذب بماند؛ ورودی‌ها از task_control صفر شده</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="26" t="inlineStr">
-        <is>
-          <t>بدون episode کاذب</t>
-        </is>
-      </c>
-      <c r="K22" s="26" t="n"/>
-      <c r="L22" s="32" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M22" s="26" t="n"/>
-      <c r="N22" s="26" t="n"/>
-      <c r="O22" s="28" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="29" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q22" s="33">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="33">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="33">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="33">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="33">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="33">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="33">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="33">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="33">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="33">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="33">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="33">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="33">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="33">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="33">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="33">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="33">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="33">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="33">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="33">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="33">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="33">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="33">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="33">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="33">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="33">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="33">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="33">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="33">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="33">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="33">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="33">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="33">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="33">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="33">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="33">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="33">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="33">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="33">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="33">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="Q62" s="33">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q22"/>
+  <autoFilter ref="A4:Q61"/>
   <dataValidations count="2">
     <dataValidation sqref="C5:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
@@ -2710,10 +2653,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId4"/>
+    <hyperlink ref="E8" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
+    <hyperlink ref="E15" location="'برنامه تست'!A11"/>
+    <hyperlink ref="M20" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2721,6 +2664,342 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>IM-020</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و ولتاژهای بالا/پایین (vHigh/vLow) را عمداً زباله بگذار.
+گام ۲: آن را 3 ثانیه به Imbalance_Evaluate بده (ورودی‌ها را task_control از قبل صفر می‌کند).
+گام ۳: شمارنده و وضعیت اپیزود را نگاه کن: ماژول باید روی valid گیت بزند و هیچ اپیزود کاذبی نباید ساخته شود.</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>ماژول باید روی valid گیت بزند و بدون episode کاذب بماند؛ ورودی‌ها از task_control صفر شده</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>بدون episode کاذب</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="n"/>
+      <c r="L5" s="32" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="n"/>
+      <c r="N5" s="26" t="n"/>
+      <c r="O5" s="28" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="33">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="33">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="33">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="33">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="33">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="33">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="33">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="33">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="33">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="33">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="33">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="33">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="33">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="33">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="33">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="33">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="33">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="33">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="33">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="33">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3051,7 +3330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3238,16 +3517,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId4"/>
+    <hyperlink ref="A4" location="'برنامه تست'!A5"/>
+    <hyperlink ref="B4" location="'برنامه تست'!A20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3472,7 +3751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3568,7 +3847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -807,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1541,111 +1544,25 @@
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>IM-008</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>چشمک قفل</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
+          <t>IM-009</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>بوق ساعتی</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t>گام ۱: قفل را فعال نگه دار (IM-007).
-گام ۲: پارامتر 123 (دورهٔ چشمک) را 1000 میلی‌ثانیه و پارامتر 124 (سهم روشنی) را 50 درصد بگذار.
-گام ۳: با کرنومتر یا اسیلوسکوپ یک دورهٔ کامل چشمک قرمز را اندازه بگیر و مدت روشنی را هم بخوان.
-گام ۴: در 60 ثانیه چند دوره را چک کن: دوره باید 1000 میلی‌ثانیه و روشنی 50 درصد باشد، با خطای حداکثر ±5 درصد.</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>۱۰۰۰ms و ۵۰٪</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>۶۰ ثانیه</t>
-        </is>
-      </c>
-      <c r="H12" s="26" t="inlineStr">
-        <is>
-          <t>چشمک قرمز با همان دوره و duty</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>پایدار</t>
-        </is>
-      </c>
-      <c r="J12" s="26" t="inlineStr">
-        <is>
-          <t>اندازه‌گیری با کرنومتر یا اسیلوسکوپ در ±۵٪</t>
-        </is>
-      </c>
-      <c r="K12" s="26" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O12" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q12" s="29" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>IM-009</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>بوق ساعتی</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>قفل فعال</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد.
 گام ۲: برای کوتاه شدن تست می‌توانی پارامتر 115 (دورهٔ بوق) را موقتاً کوچک کنی، وگرنه یک ساعت کامل باید صبر کنی.
@@ -1653,85 +1570,85 @@
 گام ۴: باید یک بوق کوتاه شنیده و دیده شود و طولش برابر پارامتر 116 باشد.</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>دورهٔ ۱۱۵</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>یک دوره</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>یک بوق کوتاه به طول ۱۱۶</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>تکرارشونده</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>بوق دیده و شنیده می‌شود و طولش مطابق ۱۱۶ است</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O13" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>IM-010</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>وتوی خروجی</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>قفل فعال و تیک ۱۱۷ خورده</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد و تیک پارامتر 117 (مسدودی خروجی بعد از قفل) خورده باشد.
 گام ۲: ورودی را قطع کن تا سیستم بخواهد روی باتری برود.
@@ -1739,85 +1656,85 @@
 گام ۴: باتری هرگز نباید روی خروجی وصل شود؛ رلهٔ خروجی نباید وصل شود.</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>قطع ورودی</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>باتری هرگز روی خروجی سوئیچ نمی‌شود</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t>وتو تا رفع قفل</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J13" s="26" t="inlineStr">
         <is>
           <t>رله خروجی وصل نمی‌شود (اندازه‌گیری مستقیم)</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="26" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O14" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P14" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q14" s="29" t="inlineStr">
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P13" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q13" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>IM-011</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>برداشتن تیک ۱۱۷</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد (IM-007).
 گام ۲: پارامتر 117 را صفر کن (block_output_en = 0).
@@ -1825,85 +1742,85 @@
 گام ۴: ولی قفل و چهرهٔ قرمز باید سر جایشان بمانند؛ اسلات 202 همچنان 1 است.</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>block_output_en = ۰</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>۳۰ ثانیه</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>وتو برداشته می‌شود ولی قفل و چهرهٔ قرمز باقی می‌ماند</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>latch حفظ</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>اسلات ۲۰۲ همچنان ۱ و خروجی مجاز</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O15" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q14" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>IM-012</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>بودجهٔ سیکل شارژ</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد.
 گام ۲: در حالت قفل، 20 سیکل کامل شارژ را یکی‌یکی بگذران (هر سیکل تا FLOAT واقعی).
@@ -1911,85 +1828,85 @@
 گام ۴: بعد از رسیدن به سقف 118، شارژ همان پک باید مسدود شود: اسلات 201 باید 20 باشد و هیچ‌کدام از دو کانال دیگر شارژ نکنند.</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>cycles ≥ ۱۱۸</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>۲۰ سیکل</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>پس از رسیدن به ۱۱۸ شارژ همان پک مسدود می‌شود</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>مسدودی ماندگار</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J15" s="26" t="inlineStr">
         <is>
           <t>اسلات ۲۰۱ = ۲۰ و هر دو کانال شارژ نمی‌کنند</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="29" t="inlineStr">
+      <c r="M15" s="26" t="n"/>
+      <c r="N15" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O15" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P15" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q15" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>IM-013</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>ریست با تعویض باتری</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>قفل فعال و شمارنده‌ها پر</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال و شمارنده‌ها پر باشند؛ مقادیر اسلات‌های 200 تا 202 را یادداشت کن.
 گام ۲: هر دو نیم‌باتری را کامل جدا کن (باتری نباشد).
@@ -1997,85 +1914,85 @@
 گام ۴: باتری را وصل کن و اسلات‌ها را بخوان: همهٔ شمارنده‌ها و خود قفل باید صفر و ریست شده باشند (هر سه اسلات 200، 201 و 202 صفر).</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>نبود باتری ≥ ۳۰۰۰ms</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>۳ ثانیه</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>همهٔ شمارنده‌ها و قفل ریست می‌شوند</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>ریست یک‌باره</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>اسلات‌های ۲۰۰..۲۰۲ همگی صفر</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O17" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P17" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O16" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q16" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>IM-014</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>جدا شدن کوتاه</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>گام ۱: قفل فعال باشد و مقادیر اسلات‌ها را یادداشت کن.
 گام ۲: باتری را جدا کن ولی کمتر از 3 ثانیه (مثلاً 1 ثانیه) و دوباره وصل کن.
@@ -2083,85 +2000,85 @@
 گام ۴: هیچ ریستی نباید رخ داده باشد؛ اسلات‌ها باید دقیقاً همان مقادیر گام ۱ باشند.</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>نبود باتری &lt; ۳۰۰۰ms</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>۵ تکرار</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>هیچ ریستی رخ نمی‌دهد</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>latch حفظ</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="J17" s="26" t="inlineStr">
         <is>
           <t>اسلات‌ها بدون تغییر</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L17" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="26" t="n"/>
-      <c r="N18" s="26" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O18" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P18" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q18" s="29" t="inlineStr">
+      <c r="M17" s="26" t="n"/>
+      <c r="N17" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P17" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q17" s="29" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>IM-015</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>بازهٔ پارامترها</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>لینک ESP برقرار</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را برقرار کن.
 گام ۲: برای هر یک از پارامترهای 108 تا 118 و 123 و 124، یک مقدار بیرون از بازهٔ مجاز بفرست (یکی‌یکی، هر کدام یک تبادل).
@@ -2169,85 +2086,85 @@
 گام ۴: هر پارامتر را با GET دوباره بخوان؛ مقدار نهایی باید داخل بازهٔ مجاز باشد.</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>مقادیر خارج از حد</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>یک تبادل برای هرکدام</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>همه رد یا به حد گیره می‌شوند و مقدار اعمال‌شده برگردانده می‌شود</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>بدون مقدار نامعتبر</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>GET هر پارامتر داخل بازهٔ مجاز است</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L18" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O19" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P19" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>ماندگاری تنظیم‌ها پس از قطع برق</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>دستگاه روشن و پنل متصل</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه روشن و پنل وصل باشد؛ مقادیر فعلی پارامترهای سناریو ۵ را یادداشت کن.
 گام ۲: یک یا چند پارامتر را عوض کن؛ مثلاً پارامتر 108 را 450 میلی‌ولت و پارامتر 112 را 45000 میلی‌ثانیه بگذار و ذخیره کن تا در NVM بنشیند.
@@ -2255,89 +2172,89 @@
 گام ۴: همان پارامترها را از پنل بخوان: هر پارامتر تغییرکرده باید دقیقاً همان مقدار قبل از قطع برق باشد؛ پارامترهای دست‌نخورده باید پیش‌فرض خودشان را نشان دهند، نه اینکه پیش‌فرض کامپایل جای همه را گرفته باشد.</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>مثلاً ۱۰۸ = ۴۵۰mV و ۱۱۲ = ۴۵۰۰۰ms، ذخیره در NVM</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>یک چرخهٔ خاموش/روشن کامل</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>مقادیر ذخیره‌شده پس از روشن‌شدن دوباره خوانده می‌شوند و پیش‌فرض کامپایل جای آن‌ها را نمی‌گیرد</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>ماندگار در فلش</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>هر پارامتر تغییر‌یافته دقیقاً همان مقدار پیش از قطع برق را نشان دهد؛ پارامتر دست‌نخورده پیش‌فرض خود را داشته باشد</t>
         </is>
       </c>
-      <c r="K20" s="26" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="30" t="inlineStr">
+      <c r="M19" s="30" t="inlineStr">
         <is>
           <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
         </is>
       </c>
-      <c r="N20" s="26" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O20" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P20" s="28" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q20" s="29" t="inlineStr">
+      <c r="N19" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P19" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q19" s="29" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>IM-017</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>حداقل یک رویداد شمرده شده یا قفل فعال</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>گام ۱: دست‌کم یک رویداد بساز (events &gt; 0) و اگر می‌توانی قفل را هم فعال کن (latched = 1)؛ هر سه مقدار events و cycles و latched را یادداشت کن.
 گام ۲: تغذیه را کاملاً قطع کن و دوباره وصل کن.
@@ -2345,305 +2262,309 @@
 گام ۴: هر سه باید دقیقاً همان مقادیر قبل از قطع برق باشند.</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>events &gt; 0 و در صورت امکان latched = 1</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>یک چرخهٔ خاموش/روشن کامل</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>شمارش رویداد، شمارش سیکل و وضعیت قفل همان مقدار پیش از قطع برق می‌مانند</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>ماندگار در فلش</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>events / cycles / latched بدون تغییر پس از بوت</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O21" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P21" s="23" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A5</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q20" s="25" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="Q21" s="33">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="40.5" customHeight="1">
       <c r="Q22" s="33">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="33">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="33">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="33">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="33">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="33">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="33">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="33">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="33">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="33">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="33">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="33">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="33">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="33">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="33">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="33">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="33">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="33">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="33">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="33">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="33">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="33">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="33">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="33">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="33">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="33">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="33">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="33">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="33">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="33">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="33">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="33">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="33">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="33">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="33">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="33">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="33">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="33">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="33">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Q61" s="33">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q61"/>
+  <autoFilter ref="A4:Q60"/>
   <dataValidations count="2">
     <dataValidation sqref="C5:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
@@ -2654,9 +2575,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E8" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
-    <hyperlink ref="E15" location="'برنامه تست'!A11"/>
-    <hyperlink ref="M20" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E14" location="'برنامه تست'!A11"/>
+    <hyperlink ref="M19" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2664,6 +2584,358 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>IM-008</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>چشمک قفل</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>قفل فعال</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: قفل را فعال نگه دار (IM-007).
+گام ۲: پارامتر 123 (دورهٔ چشمک) را 1000 میلی‌ثانیه و پارامتر 124 (سهم روشنی) را 50 درصد بگذار.
+گام ۳: با کرنومتر یا اسیلوسکوپ یک دورهٔ کامل چشمک قرمز را اندازه بگیر و مدت روشنی را هم بخوان.
+گام ۴: در 60 ثانیه چند دوره را چک کن: دوره باید 1000 میلی‌ثانیه و روشنی 50 درصد باشد، با خطای حداکثر ±5 درصد.</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>۱۰۰۰ms و ۵۰٪</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>۶۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>چشمک قرمز با همان دوره و duty</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>پایدار</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>اندازه‌گیری با کرنومتر یا اسیلوسکوپ در ±۵٪</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="n"/>
+      <c r="N5" s="26" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O5" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="28" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q5" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="33">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="33">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="33">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="33">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="33">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="33">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="33">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="33">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="33">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="33">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="33">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="33">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="33">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="33">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="33">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="33">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="33">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="33">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="33">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="33">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" location="'برنامه تست'!A11"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2999,7 +3271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3330,7 +3602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3518,7 +3790,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" location="'برنامه تست'!A5"/>
-    <hyperlink ref="B4" location="'برنامه تست'!A20"/>
+    <hyperlink ref="B4" location="'برنامه تست'!A19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
   </hyperlinks>
@@ -3526,7 +3798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3751,7 +4023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3847,7 +4119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -958,40 +958,39 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>بیش از ۱۰ دقیقه از پایان شارژ گذشته</t>
+          <t>دو باتری ۱۲ ولت وصل است؛ دستگاه خاموش و بیکار (نه شارژ، نه بار)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: صبر کن دست‌کم 10 دقیقه از پایان شارژ گذشته باشد (گیت زمانی استراحت تمام شده باشد) و شمارندهٔ رویداد (events) فعلی را از پنل یادداشت کن.
-گام ۲: با بار نامتقارن روی دو نیم‌باتری، اختلاف ولتاژ دو نیم را بالای 300 میلی‌ولت ببر.
-گام ۳: اختلاف را 30 ثانیه پیوسته بالای حد نگه دار.
-گام ۴: در پنل ببین: دقیقاً یک رویداد شمرده شده باشد (events = قبلی + 1).</t>
+          <t>گام ۱: یکی از باتری‌ها را با یک لامپ ۱۲ ولت کمی خالی کن تا از آن یکی ضعیف‌تر شود.
+گام ۲: باتری‌ها را سر جا وصل کن و دستگاه را نیم ساعت بیکار بگذار.
+گام ۳: در پنل ببین رویداد عدم‌توازن شمرده شده یا نه.</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>|اختلاف| &gt; ۳۰۰mV</t>
+          <t>یک نیم ضعیف‌تر در حالت استراحت</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>۳۰ ثانیه</t>
+          <t>نیم ساعت</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>یک رویداد شمرده می‌شود</t>
+          <t>اختلاف دو باتری در استراحت دیده و یک رویداد شمرده می‌شود</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>شمارنده ماندگار</t>
+          <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>events = قبلی + ۱ در پنل</t>
+          <t>شمرده‌شدن رویداد = قبول؛ نشمردن با اختلاف واضح = رد</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -1044,40 +1043,38 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>شارژ تازه تمام شده</t>
+          <t>باتری‌ها تازه شارژشان تمام شده است</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>گام ۱: یک شارژ را تازه تمام کن و شمارندهٔ events را یادداشت کن.
-گام ۲: بلافاصله بعد از پایان شارژ، اختلاف دو نیم را بالای 300 میلی‌ولت ببر و نگه دار.
-گام ۳: تا دقیقهٔ 10 بعد از پایان شارژ نگاه کن: هیچ رویدادی نباید شمرده شود (گیت استراحت هنوز بسته است).
-گام ۴: وقتی 10 دقیقه گذشت و اختلاف هنوز بالاست، شمارش باید از همان‌جا شروع شود.</t>
+          <t>گام ۱: درست بعد از تمام‌شدن شارژ، یک باتری را کمی ضعیف کن (لامپ ۱۲ ولت).
+گام ۲: در همان دقایق اول پنل را چک کن.</t>
         </is>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>|اختلاف| &gt; ۳۰۰mV</t>
+          <t>اختلاف بلافاصله بعد از شارژ</t>
         </is>
       </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
-          <t>تا دقیقهٔ ۱۰</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>تا پیش از ۱۰ دقیقه هیچ رویدادی شمرده نمی‌شود</t>
+          <t>درست بعد از شارژ رویداد حساب نمی‌شود؛ دستگاه اول فرصت استراحت و جاافتادن می‌دهد</t>
         </is>
       </c>
       <c r="I6" s="26" t="inlineStr">
         <is>
-          <t>بدون شمارش</t>
+          <t>بدون رویداد زودهنگام</t>
         </is>
       </c>
       <c r="J6" s="26" t="inlineStr">
         <is>
-          <t>events بدون تغییر تا سپری‌شدن مهلت پارامتر 110 (پیش‌فرض 10 دقیقه، یعنی 600000 میلی‌ثانیه) از پایان شارژ</t>
+          <t>حساب‌نشدن در فرصت اول = قبول؛ رویداد فوری بعد شارژ = رد</t>
         </is>
       </c>
       <c r="K6" s="26" t="inlineStr">
@@ -1130,40 +1127,39 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>خروجی روی باتری</t>
+          <t>دستگاه روی باتری دارد به یک بار واقعی کار می‌کند</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: خروجی را روی باتری بگذار (در حال دشارژ باشد) و شمارندهٔ events را یادداشت کن.
-گام ۲: حین دشارژ اختلاف دو نیم را بالای 500 میلی‌ولت ببر.
-گام ۳: 30 ثانیه نگه دار.
-گام ۴: چون روی باتری هستیم، بدون نیاز به گیت زمانی 10 دقیقه‌ای باید یک رویداد شمرده شود (events = قبلی + 1).</t>
+          <t>گام ۱: حین کار، باتری‌ای که ضعیف‌تر است را زیر نظر بگیر (از اول یکی را کمی خالی‌تر وصل کن).
+گام ۲: بگذار دستگاه مدتی با بار کار کند.
+گام ۳: شمارندهٔ رویداد را در پنل چک کن.</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>|اختلاف| &gt; ۵۰۰mV و onBattery</t>
+          <t>دو باتری نابرابر زیر بار واقعی</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>۳۰ ثانیه</t>
+          <t>نیم ساعت</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>بدون نیاز به گیت زمانی، رویداد شمرده می‌شود</t>
+          <t>اختلاف زیر بار هم دیده و رویداد شمرده می‌شود</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>شمارنده ماندگار</t>
+          <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>events = قبلی + ۱</t>
+          <t>شمرده‌شدن زیر بار = قبول؛ فقط در استراحت شمردن = رد</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -1216,40 +1212,39 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>یک اپیزود فعال</t>
-        </is>
-      </c>
-      <c r="E8" s="30" t="inlineStr">
-        <is>
-          <t>گام ۱: یک اپیزود فعال بساز (اختلاف بالای حد مثل IM-001) و events را یادداشت کن.
-گام ۲: اختلاف را دقیقاً به زیر «حد منهای 100 میلی‌ولت» بیاور تا اپیزود بسته شود.
-گام ۳: دوباره اختلاف را بالای حد ببر تا اپیزود دوم شروع شود.
-گام ۴: این رفت‌وبرگشت را 2 چرخه انجام بده؛ هر اپیزود باید فقط یک‌بار شمرده شود (در مجموع دقیقاً +1 برای هر اپیزود).</t>
+          <t>یک اپیزود عدم‌توازن در جریان است (اختلاف دو باتری نزدیک مرز تمام‌شدن)</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: اختلاف دو باتری را آرام کم کن (باتری ضعیف را کمی شارژ یا با سالم‌تر عوض کن).
+گام ۲: بعد کمی دوباره اختلاف بساز و کم کن.
+گام ۳: شمارنده و وضعیت اپیزود را در پنل نگاه کن.</t>
         </is>
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>عبور از حد و بازگشت</t>
+          <t>کم و زیاد کردن آرام اختلاف دور مرز پایان</t>
         </is>
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>۲ چرخه</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>هر اپیزود فقط یک‌بار شمرده می‌شود</t>
+          <t>اپیزود با هر تغییر کوچک باز و بسته نمی‌شود؛ پایانش تمیز و یک‌باره است</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t>بدون شمارش مضاعف</t>
+          <t>پایان پایدار</t>
         </is>
       </c>
       <c r="J8" s="26" t="inlineStr">
         <is>
-          <t>events دقیقاً +۱ به ازای هر اپیزود</t>
+          <t>پایان تمیز = قبول؛ باز و بسته‌شدن تندتند = رد</t>
         </is>
       </c>
       <c r="K8" s="26" t="inlineStr">
@@ -1302,39 +1297,38 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>اختلاف نزدیک حد</t>
+          <t>به‌جای یک باتری منبع آزمایشگاهی گذاشته‌ای تا ولتاژش را بازی بدهی</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: اختلاف دو نیم را به نزدیک حد برسان (در بازهٔ 200 تا 300 میلی‌ولت، یعنی داخل هیسترزیس).
-گام ۲: 60 ثانیه همان‌جا نگه دار و events را نگاه کن.
-گام ۳: نه رویداد تازه‌ای باید شمرده شود نه اپیزود به‌صورت نوسانی باز و بسته شود؛ events باید بی‌تغییر بماند.</t>
+          <t>گام ۱: ولتاژ منبع را دور مرز اختلاف مجاز، کم‌کم بالا و پایین کن.
+گام ۲: شمارندهٔ رویداد را در پنل زیر نظر بگیر.</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>۲۰۰..۳۰۰mV</t>
+          <t>نوسان ولتاژ یک نیم دور مرز</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>۶۰ ثانیه</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>نه رویداد تازه نه پایان نوسانی اپیزود</t>
+          <t>با نوسان‌های کوچک شمارنده بالا نمی‌رود؛ فقط اختلاف واقعی و ماندگار شمرده می‌شود</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>پایدار</t>
+          <t>بدون رویداد کاذب</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>events بدون تغییر</t>
+          <t>ثابت‌ماندن شمارنده = قبول؛ شمردن با هر نوسان = رد</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -1385,42 +1379,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>events &gt; 0</t>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>چند رویداد عدم‌توازن را با IM-001 ساخته‌ای و شمرده شده‌اند</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>گام ۱: چند رویداد بساز تا events بزرگ‌تر از صفر شود و مقدارش را یادداشت کن.
-گام ۲: برق برد را کاملاً قطع کن و دوباره وصل کن.
-گام ۳: بعد از بوت، events را در پنل بخوان: باید دقیقاً همان مقدار قبل از قطع باشد (از NVM برگشته، ریست نشده).
-گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر بار همان عدد را باید ببینی.</t>
+          <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
+گام ۲: دوباره روشن کن و شمارنده را در پنل بخوان.</t>
         </is>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>قطع کامل تغذیه</t>
+          <t>قطع و وصل کامل برق</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">
         <is>
-          <t>۳ بار</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>شمارنده از NVM بازمی‌گردد و ادامه می‌یابد (ریست نمی‌شود)</t>
+          <t>شمارندهٔ رویدادها بعد از روشن‌شدن سر جایش هست و از صفر شروع نشده</t>
         </is>
       </c>
       <c r="I10" s="26" t="inlineStr">
         <is>
-          <t>اسلات ۲۰۰ ماندگار</t>
+          <t>ماندگار در قطع برق</t>
         </is>
       </c>
       <c r="J10" s="26" t="inlineStr">
         <is>
-          <t>events پس از بوت برابر پیش از قطع</t>
+          <t>حفظ شمارنده = قبول؛ صفر شدن = رد</t>
         </is>
       </c>
       <c r="K10" s="26" t="inlineStr">
@@ -1473,40 +1465,39 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>events = ۹</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>گام ۱: شمارندهٔ events را به 9 برسان.
-گام ۲: یک رویداد دیگر بساز تا به 10 برسد (رویداد دهم).
-گام ۳: به چراغ‌ها نگاه کن: قفل باید فعال شده باشد؛ LED قرمز چشمک‌زن و سبز و زرد خاموش.
-گام ۴: در پنل چک کن اسلات 202 برابر 1 باشد و چشمک قرمز مطابق پارامترهای 123 (دوره) و 124 (سهم روشنی) باشد.</t>
+          <t>دو باتری نابرابر داری؛ برای زود دیدن نتیجه از پنل حدّ رویدادهای مجاز را موقتاً روی یک بگذار</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>گام ۱: یک رویداد عدم‌توازن بساز (مثل IM-001).
+گام ۲: وقتی قفل شد چراغ‌ها را ببین: فقط قرمز چشمک می‌زند، سبز و زرد خاموش‌اند.
+گام ۳: حدّ را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>events ≥ ۱۱۴</t>
+          <t>رویداد عدم‌توازن با حدّ موقتِ یک</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>یک رویداد</t>
+          <t>نیم ساعت</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>قفل فعال: LED قرمز چشمک‌زن، سبز و زرد خاموش</t>
+          <t>قفل عدم‌توازن می‌نشیند: قرمز چشمک‌زنِ تنها، بدون سبز و زرد</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>latch ماندگار</t>
+          <t>قفل تا تعویض باتری</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>اسلات ۲۰۲ = ۱ و چهرهٔ LED مطابق ۱۲۳/۱۲۴</t>
+          <t>نشستن قفل با همان چهره = قبول؛ قفل‌نشدن یا چهرهٔ اشتباه = رد</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -1557,42 +1548,41 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>قفل فعال</t>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>قفل عدم‌توازن فعال است (IM-007)؛ از پنل دورهٔ بوق قفل را موقتاً کوتاه کرده‌ای</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: قفل فعال باشد.
-گام ۲: برای کوتاه شدن تست می‌توانی پارامتر 115 (دورهٔ بوق) را موقتاً کوچک کنی، وگرنه یک ساعت کامل باید صبر کنی.
-گام ۳: یک دورهٔ کامل (پارامتر 115) منتظر بمان.
-گام ۴: باید یک بوق کوتاه شنیده و دیده شود و طولش برابر پارامتر 116 باشد.</t>
+          <t>گام ۱: با کرنومتر صبر کن تا وقت بوق برسد.
+گام ۲: به بوق و چراغ قرمز دقت کن.
+گام ۳: دورهٔ بوق را به مقدار واقعی برگردان.</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>دورهٔ ۱۱۵</t>
+          <t>قفل فعال با دورهٔ بوق کوتاه‌شده</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>یک دوره</t>
+          <t>چند دقیقه</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>یک بوق کوتاه به طول ۱۱۶</t>
+          <t>سر وقت، یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>تکرارشونده</t>
+          <t>بوق دوره‌ای در قفل</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t>بوق دیده و شنیده می‌شود و طولش مطابق ۱۱۶ است</t>
+          <t>بوق سر وقت = قبول؛ بی‌بوقی یا بوق به‌هم‌ریخته = رد</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -1645,40 +1635,39 @@
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
-          <t>قفل فعال و تیک ۱۱۷ خورده</t>
+          <t>قفل عدم‌توازن فعال است و از پنل گزینهٔ «قطع خروجی هنگام قفل» روشن است؛ یک بار روی خروجی داری</t>
         </is>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>گام ۱: قفل فعال باشد و تیک پارامتر 117 (مسدودی خروجی بعد از قفل) خورده باشد.
-گام ۲: ورودی را قطع کن تا سیستم بخواهد روی باتری برود.
-گام ۳: 30 ثانیه رلهٔ خروجی را مستقیم اندازه بگیر.
-گام ۴: باتری هرگز نباید روی خروجی وصل شود؛ رلهٔ خروجی نباید وصل شود.</t>
+          <t>گام ۱: برق شهر را بکش.
+گام ۲: بار را نگاه کن؛ نباید از این باتری روشن شود.
+گام ۳: برق شهر را برگردان.</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>قطع ورودی</t>
+          <t>قطع برق شهر در قفل با وتوی خروجی</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>۳۰ ثانیه</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>باتری هرگز روی خروجی سوئیچ نمی‌شود</t>
+          <t>باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود</t>
         </is>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t>وتو تا رفع قفل</t>
+          <t>وتو تا پاک‌شدن قفل</t>
         </is>
       </c>
       <c r="J13" s="26" t="inlineStr">
         <is>
-          <t>رله خروجی وصل نمی‌شود (اندازه‌گیری مستقیم)</t>
+          <t>روشن‌نشدن بار از باتری قفل‌شده = قبول؛ آمدن باتری روی خروجی = رد</t>
         </is>
       </c>
       <c r="K13" s="26" t="inlineStr">
@@ -1731,40 +1720,38 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>قفل فعال</t>
-        </is>
-      </c>
-      <c r="E14" s="31" t="inlineStr">
-        <is>
-          <t>گام ۱: قفل فعال باشد (IM-007).
-گام ۲: پارامتر 117 را صفر کن (block_output_en = 0).
-گام ۳: 30 ثانیه نگاه کن: وتوی خروجی باید برداشته شود و خروجی مجاز شود.
-گام ۴: ولی قفل و چهرهٔ قرمز باید سر جایشان بمانند؛ اسلات 202 همچنان 1 است.</t>
+          <t>قفل عدم‌توازن فعال است؛ گزینهٔ قطع خروجی را از پنل خاموش می‌کنی</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>گام ۱: تیک قطع خروجی را از پنل بردار.
+گام ۲: برق شهر را بکش و بار را نگاه کن.</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>block_output_en = ۰</t>
+          <t>برداشتن تیک قطع خروجی در قفل</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>۳۰ ثانیه</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>وتو برداشته می‌شود ولی قفل و چهرهٔ قرمز باقی می‌ماند</t>
+          <t>این بار باتری روی خروجی می‌آید و بار کار می‌کند، هرچند قفل هنوز هست</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>latch حفظ</t>
+          <t>وتو تابع تیک پنل</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>اسلات ۲۰۲ همچنان ۱ و خروجی مجاز</t>
+          <t>کارکردن خروجی با تیک خاموش = قبول؛ وتوی همیشگی = رد</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -1817,40 +1804,38 @@
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
-          <t>قفل فعال</t>
+          <t>قفل عدم‌توازن فعال است و شارژ باتری قفل‌شده هنوز اجازه دارد</t>
         </is>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>گام ۱: قفل فعال باشد.
-گام ۲: در حالت قفل، 20 سیکل کامل شارژ را یکی‌یکی بگذران (هر سیکل تا FLOAT واقعی).
-گام ۳: شمارندهٔ سیکل‌ها را نگاه کن که به پارامتر 118 برسد.
-گام ۴: بعد از رسیدن به سقف 118، شارژ همان پک باید مسدود شود: اسلات 201 باید 20 باشد و هیچ‌کدام از دو کانال دیگر شارژ نکنند.</t>
+          <t>گام ۱: چند چرخهٔ شارژ کامل روی همان باتری انجام بده.
+گام ۲: بعد از هر چرخه ببین شارژ هنوز شروع می‌شود یا نه.</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>cycles ≥ ۱۱۸</t>
+          <t>چند چرخهٔ شارژ پشت سر هم در قفل</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>۲۰ سیکل</t>
+          <t>چند چرخهٔ شارژ</t>
         </is>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>پس از رسیدن به ۱۱۸ شارژ همان پک مسدود می‌شود</t>
+          <t>بعد از تمام‌شدن بودجهٔ چرخه‌های مجاز، شارژ آن باتری هم دیگر شروع نمی‌شود</t>
         </is>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
-          <t>مسدودی ماندگار</t>
+          <t>توقف شارژ بعد از بودجه</t>
         </is>
       </c>
       <c r="J15" s="26" t="inlineStr">
         <is>
-          <t>اسلات ۲۰۱ = ۲۰ و هر دو کانال شارژ نمی‌کنند</t>
+          <t>توقف بعد از چرخه‌های مجاز = قبول؛ شارژ بی‌نهایت در قفل = رد</t>
         </is>
       </c>
       <c r="K15" s="26" t="inlineStr">
@@ -1903,40 +1888,38 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>قفل فعال و شمارنده‌ها پر</t>
+          <t>قفل عدم‌توازن فعال است و چراغ قرمز چشمک می‌زند</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: قفل فعال و شمارنده‌ها پر باشند؛ مقادیر اسلات‌های 200 تا 202 را یادداشت کن.
-گام ۲: هر دو نیم‌باتری را کامل جدا کن (باتری نباشد).
-گام ۳: دقیقاً 3 ثانیهٔ کامل جدا نگه دار.
-گام ۴: باتری را وصل کن و اسلات‌ها را بخوان: همهٔ شمارنده‌ها و خود قفل باید صفر و ریست شده باشند (هر سه اسلات 200، 201 و 202 صفر).</t>
+          <t>گام ۱: هر دو باتری را با دو باتری سالم و هم‌شارژ عوض کن.
+گام ۲: چند دقیقه صبر کن و چراغ‌ها را ببین.</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>نبود باتری ≥ ۳۰۰۰ms</t>
+          <t>تعویض واقعی هر دو باتری</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>۳ ثانیه</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>همهٔ شمارنده‌ها و قفل ریست می‌شوند</t>
+          <t>قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>ریست یک‌باره</t>
+          <t>پاک‌شدن خودکار با تعویض</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t>اسلات‌های ۲۰۰..۲۰۲ همگی صفر</t>
+          <t>پاک‌شدن خودکار = قبول؛ ماندن قفل با باتری سالم = رد</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -1989,40 +1972,39 @@
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t>قفل فعال</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: قفل فعال باشد و مقادیر اسلات‌ها را یادداشت کن.
-گام ۲: باتری را جدا کن ولی کمتر از 3 ثانیه (مثلاً 1 ثانیه) و دوباره وصل کن.
-گام ۳: این کار را 5 بار تکرار کن.
-گام ۴: هیچ ریستی نباید رخ داده باشد؛ اسلات‌ها باید دقیقاً همان مقادیر گام ۱ باشند.</t>
+          <t>قفل عدم‌توازن فعال است</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: باتری‌ها را فقط چند ثانیه جدا کن و سریع وصل کن.
+گام ۲: چراغ‌ها را ببین؛ قفل باید سر جایش باشد.
+گام ۳: حالا تعویض واقعی (IM-013) انجام بده و تفاوت را ببین.</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>نبود باتری &lt; ۳۰۰۰ms</t>
+          <t>جدا کردن کوتاه در برابر تعویض واقعی</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>۵ تکرار</t>
+          <t>ربع ساعت</t>
         </is>
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>هیچ ریستی رخ نمی‌دهد</t>
+          <t>قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند</t>
         </is>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>latch حفظ</t>
+          <t>قفل در برابر قطع کوتاه مقاوم</t>
         </is>
       </c>
       <c r="J17" s="26" t="inlineStr">
         <is>
-          <t>اسلات‌ها بدون تغییر</t>
+          <t>ماندن قفل بعد قطع کوتاه = قبول؛ پاک‌شدن با قطع کوتاه = رد</t>
         </is>
       </c>
       <c r="K17" s="26" t="inlineStr">
@@ -2075,40 +2057,38 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>لینک ESP برقرار</t>
+          <t>پنل باز است و تنظیم‌های عدم‌توازن را می‌بینی</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را برقرار کن.
-گام ۲: برای هر یک از پارامترهای 108 تا 118 و 123 و 124، یک مقدار بیرون از بازهٔ مجاز بفرست (یکی‌یکی، هر کدام یک تبادل).
-گام ۳: پاسخ برد را بخوان: هر مقدار یا باید رد شود یا به نزدیک‌ترین حد مجاز گیره (clamp) شود و مقدار اعمال‌شده برگردانده شود.
-گام ۴: هر پارامتر را با GET دوباره بخوان؛ مقدار نهایی باید داخل بازهٔ مجاز باشد.</t>
+          <t>گام ۱: از پنل یک حدّ ناممکن بفرست (مثلاً اختلاف مجاز خیلی بزرگ یا منفیِ معادل).
+گام ۲: مقدار ذخیره‌شده را دوباره از پنل بخوان.</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>مقادیر خارج از حد</t>
+          <t>فرستادن مقدار بیرون بازه از پنل</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>یک تبادل برای هرکدام</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>همه رد یا به حد گیره می‌شوند و مقدار اعمال‌شده برگردانده می‌شود</t>
+          <t>دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>بدون مقدار نامعتبر</t>
+          <t>حفظ مقدار قبلی</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t>GET هر پارامتر داخل بازهٔ مجاز است</t>
+          <t>رد شدن مقدار خراب = قبول؛ ذخیره‌شدن مقدار ناممکن = رد</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -2161,40 +2141,39 @@
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
-          <t>دستگاه روشن و پنل متصل</t>
+          <t>پنل باز است</t>
         </is>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>گام ۱: دستگاه روشن و پنل وصل باشد؛ مقادیر فعلی پارامترهای سناریو ۵ را یادداشت کن.
-گام ۲: یک یا چند پارامتر را عوض کن؛ مثلاً پارامتر 108 را 450 میلی‌ولت و پارامتر 112 را 45000 میلی‌ثانیه بگذار و ذخیره کن تا در NVM بنشیند.
-گام ۳: تغذیه را کاملاً قطع کن و دوباره وصل کن.
-گام ۴: همان پارامترها را از پنل بخوان: هر پارامتر تغییرکرده باید دقیقاً همان مقدار قبل از قطع برق باشد؛ پارامترهای دست‌نخورده باید پیش‌فرض خودشان را نشان دهند، نه اینکه پیش‌فرض کامپایل جای همه را گرفته باشد.</t>
+          <t>گام ۱: یک تنظیم عدم‌توازن را از پنل عوض کن (مثلاً اختلاف مجاز).
+گام ۲: برق دستگاه را کامل قطع و دوباره وصل کن.
+گام ۳: تنظیم را از پنل دوباره بخوان.</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>مثلاً ۱۰۸ = ۴۵۰mV و ۱۱۲ = ۴۵۰۰۰ms، ذخیره در NVM</t>
+          <t>تغییر تنظیم و قطع‌ووصل برق</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>یک چرخهٔ خاموش/روشن کامل</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>مقادیر ذخیره‌شده پس از روشن‌شدن دوباره خوانده می‌شوند و پیش‌فرض کامپایل جای آن‌ها را نمی‌گیرد</t>
+          <t>همان تنظیم تازه بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
-          <t>ماندگار در فلش</t>
+          <t>ماندگار در قطع برق</t>
         </is>
       </c>
       <c r="J19" s="26" t="inlineStr">
         <is>
-          <t>هر پارامتر تغییر‌یافته دقیقاً همان مقدار پیش از قطع برق را نشان دهد؛ پارامتر دست‌نخورده پیش‌فرض خود را داشته باشد</t>
+          <t>حفظ تنظیم = قبول؛ برگشت به مقدار قبلی = رد</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr">
@@ -2251,40 +2230,38 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>حداقل یک رویداد شمرده شده یا قفل فعال</t>
+          <t>قفل عدم‌توازن فعال و شمارنده چند رویداد دارد</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>گام ۱: دست‌کم یک رویداد بساز (events &gt; 0) و اگر می‌توانی قفل را هم فعال کن (latched = 1)؛ هر سه مقدار events و cycles و latched را یادداشت کن.
-گام ۲: تغذیه را کاملاً قطع کن و دوباره وصل کن.
-گام ۳: بعد از بوت شمارنده‌ها و وضعیت قفل را در پنل بخوان.
-گام ۴: هر سه باید دقیقاً همان مقادیر قبل از قطع برق باشند.</t>
+          <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
+گام ۲: روشن کن و چراغ‌ها و شمارنده را چک کن.</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>events &gt; 0 و در صورت امکان latched = 1</t>
+          <t>قطع و وصل برق در قفل</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>یک چرخهٔ خاموش/روشن کامل</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>شمارش رویداد، شمارش سیکل و وضعیت قفل همان مقدار پیش از قطع برق می‌مانند</t>
+          <t>قفل و شمارنده بعد از روشن‌شدن دقیقاً سر جایشان‌اند</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>ماندگار در فلش</t>
+          <t>ماندگار در قطع برق</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t>events / cycles / latched بدون تغییر پس از بوت</t>
+          <t>حفظ هر دو = قبول؛ پاک‌شدن با قطع برق = رد</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -2574,8 +2551,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E8" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E14" location="'برنامه تست'!A11"/>
+    <hyperlink ref="D10" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E11" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D12" location="'برنامه تست'!A11"/>
+    <hyperlink ref="E17" location="'برنامه تست'!A16"/>
     <hyperlink ref="M19" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -147,6 +147,53 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -226,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -350,6 +397,81 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -723,73 +845,73 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Imbalance</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Imbalance | سناریوی ۵: قضاوت عدم‌توازن دو نیم‌باتری با شمارش ماندگار رویداد و قفل</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>سناریوی ۵: پایش قدرمطلق اختلاف دو نیم‌باتری ۱۲ ولتی |v_bat_high - v_bat_low| و قضاوت عدم‌توازن با شمارش ماندگار رویداد.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>ماژول منطق خالص است: همهٔ ورودی‌ها و زمان جاری از بیرون می‌آیند و هیچ وابستگی به BSP یا RTOS ندارد؛ سیم‌بندی در task_control.c است.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>گیت زمانی: حد استراحت (۱۰۸) فقط در استراحت و پس از ۱۱۰ از پایان شارژ، و حین شارژ پس از ۱۱۱؛ در دشارژ حد ۱۰۹ بلافاصله اعمال می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>رویداد = فراتر از حد به‌طور پیوسته برای ۱۱۲؛ پایان اپیزود با هیسترزیس ۱۱۳؛ هر اپیزود فقط یک‌بار شمرده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>رویدادها ≥ ۱۱۴ → قفل: قرمز چشمک‌زن + بوق ساعتی + وتوی خروجی (در صورت تیک ۱۱۷)؛ ۱۱۸ سیکل شارژ در قفل → مسدودی شارژ.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>نبود باتری برای ۳ ثانیهٔ پیوسته = تعویض واقعی → ریست خودکار همهٔ شمارنده‌ها و قفل.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>شمارنده‌ها در اسلات‌های ۲۰۰..۲۰۲ ماندگارند و با قطع برق پاک نمی‌شوند. تست Host جایگزین تست برد نیست.</t>
         </is>
@@ -833,1709 +955,2397 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Imbalance</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
+      <c r="D1" s="53" t="n"/>
+      <c r="E1" s="53" t="n"/>
+      <c r="F1" s="53" t="n"/>
+      <c r="G1" s="53" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="53" t="n"/>
+      <c r="J1" s="53" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="53" t="n"/>
+      <c r="M1" s="53" t="n"/>
+      <c r="N1" s="53" t="n"/>
+      <c r="O1" s="53" t="n"/>
+      <c r="P1" s="53" t="n"/>
+      <c r="Q1" s="53" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="53" t="n"/>
+      <c r="L2" s="53" t="n"/>
+      <c r="M2" s="53" t="n"/>
+      <c r="N2" s="53" t="n"/>
+      <c r="O2" s="53" t="n"/>
+      <c r="P2" s="53" t="n"/>
+      <c r="Q2" s="53" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="53" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="15" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="15" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>IM-001</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>آستانهٔ استراحت</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>دو باتری ۱۲ ولت وصل است؛ دستگاه خاموش و بیکار (نه شارژ، نه بار)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="56" t="inlineStr">
         <is>
           <t>گام ۱: یکی از باتری‌ها را با یک لامپ ۱۲ ولت کمی خالی کن تا از آن یکی ضعیف‌تر شود.
 گام ۲: باتری‌ها را سر جا وصل کن و دستگاه را نیم ساعت بیکار بگذار.
 گام ۳: در پنل ببین رویداد عدم‌توازن شمرده شده یا نه.</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
         <is>
           <t>یک نیم ضعیف‌تر در حالت استراحت</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>اختلاف دو باتری در استراحت دیده و یک رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="56" t="inlineStr">
         <is>
           <t>شمرده‌شدن رویداد = قبول؛ نشمردن با اختلاف واضح = رد</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="M5" s="56" t="n"/>
+      <c r="N5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>IM-002</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>گیت زمانی پس از شارژ</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>باتری‌ها تازه شارژشان تمام شده است</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>گام ۱: درست بعد از تمام‌شدن شارژ، یک باتری را کمی ضعیف کن (لامپ ۱۲ ولت).
 گام ۲: در همان دقایق اول پنل را چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="63" t="inlineStr">
         <is>
           <t>اختلاف بلافاصله بعد از شارژ</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>درست بعد از شارژ رویداد حساب نمی‌شود؛ دستگاه اول فرصت استراحت و جاافتادن می‌دهد</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="61" t="inlineStr">
         <is>
           <t>بدون رویداد زودهنگام</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="J6" s="61" t="inlineStr">
         <is>
           <t>حساب‌نشدن در فرصت اول = قبول؛ رویداد فوری بعد شارژ = رد</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="26" t="n"/>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="M6" s="61" t="n"/>
+      <c r="N6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="O6" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="28" t="inlineStr">
+      <c r="P6" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
+      <c r="Q6" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>IM-003</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>آستانهٔ دشارژ</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>دستگاه روی باتری دارد به یک بار واقعی کار می‌کند</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="56" t="inlineStr">
         <is>
           <t>گام ۱: حین کار، باتری‌ای که ضعیف‌تر است را زیر نظر بگیر (از اول یکی را کمی خالی‌تر وصل کن).
 گام ۲: بگذار دستگاه مدتی با بار کار کند.
 گام ۳: شمارندهٔ رویداد را در پنل چک کن.</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>دو باتری نابرابر زیر بار واقعی</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>اختلاف زیر بار هم دیده و رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="56" t="inlineStr">
         <is>
           <t>شمرده‌شدن زیر بار = قبول؛ فقط در استراحت شمردن = رد</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="M7" s="56" t="n"/>
+      <c r="N7" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="23" t="inlineStr">
+      <c r="P7" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>IM-004</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>هیسترزیس پایان اپیزود</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>یک اپیزود عدم‌توازن در جریان است (اختلاف دو باتری نزدیک مرز تمام‌شدن)</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>گام ۱: اختلاف دو باتری را آرام کم کن (باتری ضعیف را کمی شارژ یا با سالم‌تر عوض کن).
 گام ۲: بعد کمی دوباره اختلاف بساز و کم کن.
 گام ۳: شمارنده و وضعیت اپیزود را در پنل نگاه کن.</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="63" t="inlineStr">
         <is>
           <t>کم و زیاد کردن آرام اختلاف دور مرز پایان</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="61" t="inlineStr">
         <is>
           <t>اپیزود با هر تغییر کوچک باز و بسته نمی‌شود؛ پایانش تمیز و یک‌باره است</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="61" t="inlineStr">
         <is>
           <t>پایان پایدار</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="J8" s="61" t="inlineStr">
         <is>
           <t>پایان تمیز = قبول؛ باز و بسته‌شدن تندتند = رد</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="26" t="inlineStr">
+      <c r="M8" s="61" t="n"/>
+      <c r="N8" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="28" t="inlineStr">
+      <c r="P8" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q8" s="29" t="inlineStr">
+      <c r="Q8" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>IM-005</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>نوسان دور حد</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>به‌جای یک باتری منبع آزمایشگاهی گذاشته‌ای تا ولتاژش را بازی بدهی</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را دور مرز اختلاف مجاز، کم‌کم بالا و پایین کن.
 گام ۲: شمارندهٔ رویداد را در پنل زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>نوسان ولتاژ یک نیم دور مرز</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>با نوسان‌های کوچک شمارنده بالا نمی‌رود؛ فقط اختلاف واقعی و ماندگار شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="56" t="inlineStr">
         <is>
           <t>بدون رویداد کاذب</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="56" t="inlineStr">
         <is>
           <t>ثابت‌ماندن شمارنده = قبول؛ شمردن با هر نوسان = رد</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="M9" s="56" t="n"/>
+      <c r="N9" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="O9" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P9" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="Q9" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>IM-006</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="65" t="inlineStr">
         <is>
           <t>چند رویداد عدم‌توازن را با IM-001 ساخته‌ای و شمرده شده‌اند</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="61" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: دوباره روشن کن و شمارنده را در پنل بخوان.</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="63" t="inlineStr">
         <is>
           <t>قطع و وصل کامل برق</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="61" t="inlineStr">
         <is>
           <t>شمارندهٔ رویدادها بعد از روشن‌شدن سر جایش هست و از صفر شروع نشده</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="61" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>حفظ شمارنده = قبول؛ صفر شدن = رد</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="26" t="inlineStr">
+      <c r="M10" s="61" t="n"/>
+      <c r="N10" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O10" s="28" t="inlineStr">
+      <c r="O10" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="28" t="inlineStr">
+      <c r="P10" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q10" s="29" t="inlineStr">
+      <c r="Q10" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>IM-007</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>قفل شدن</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>دو باتری نابرابر داری؛ برای زود دیدن نتیجه از پنل حدّ رویدادهای مجاز را موقتاً روی یک بگذار</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="66" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد عدم‌توازن بساز (مثل IM-001).
 گام ۲: وقتی قفل شد چراغ‌ها را ببین: فقط قرمز چشمک می‌زند، سبز و زرد خاموش‌اند.
 گام ۳: حدّ را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>رویداد عدم‌توازن با حدّ موقتِ یک</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن می‌نشیند: قرمز چشمک‌زنِ تنها، بدون سبز و زرد</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="56" t="inlineStr">
         <is>
           <t>قفل تا تعویض باتری</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="56" t="inlineStr">
         <is>
           <t>نشستن قفل با همان چهره = قبول؛ قفل‌نشدن یا چهرهٔ اشتباه = رد</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="M11" s="56" t="n"/>
+      <c r="N11" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O11" s="23" t="inlineStr">
+      <c r="O11" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="23" t="inlineStr">
+      <c r="P11" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="Q11" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>IM-009</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>بوق ساعتی</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است (IM-007)؛ از پنل دورهٔ بوق قفل را موقتاً کوتاه کرده‌ای</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="56" t="inlineStr">
         <is>
           <t>گام ۱: با کرنومتر صبر کن تا وقت بوق برسد.
 گام ۲: به بوق و چراغ قرمز دقت کن.
 گام ۳: دورهٔ بوق را به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="58" t="inlineStr">
         <is>
           <t>قفل فعال با دورهٔ بوق کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>چند دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="56" t="inlineStr">
         <is>
           <t>سر وقت، یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="56" t="inlineStr">
         <is>
           <t>بوق دوره‌ای در قفل</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="56" t="inlineStr">
         <is>
           <t>بوق سر وقت = قبول؛ بی‌بوقی یا بوق به‌هم‌ریخته = رد</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="M12" s="56" t="n"/>
+      <c r="N12" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="O12" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P12" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="Q12" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>IM-010</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>وتوی خروجی</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است و از پنل گزینهٔ «قطع خروجی هنگام قفل» روشن است؛ یک بار روی خروجی داری</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="61" t="inlineStr">
         <is>
           <t>گام ۱: برق شهر را بکش.
 گام ۲: بار را نگاه کن؛ نباید از این باتری روشن شود.
 گام ۳: برق شهر را برگردان.</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="63" t="inlineStr">
         <is>
           <t>قطع برق شهر در قفل با وتوی خروجی</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="61" t="inlineStr">
         <is>
           <t>باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="61" t="inlineStr">
         <is>
           <t>وتو تا پاک‌شدن قفل</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="61" t="inlineStr">
         <is>
           <t>روشن‌نشدن بار از باتری قفل‌شده = قبول؛ آمدن باتری روی خروجی = رد</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="26" t="n"/>
-      <c r="N13" s="26" t="inlineStr">
+      <c r="M13" s="61" t="n"/>
+      <c r="N13" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O13" s="28" t="inlineStr">
+      <c r="O13" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="28" t="inlineStr">
+      <c r="P13" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q13" s="29" t="inlineStr">
+      <c r="Q13" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>IM-011</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
         <is>
           <t>برداشتن تیک ۱۱۷</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="56" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است؛ گزینهٔ قطع خروجی را از پنل خاموش می‌کنی</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="56" t="inlineStr">
         <is>
           <t>گام ۱: تیک قطع خروجی را از پنل بردار.
 گام ۲: برق شهر را بکش و بار را نگاه کن.</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
         <is>
           <t>برداشتن تیک قطع خروجی در قفل</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="56" t="inlineStr">
         <is>
           <t>این بار باتری روی خروجی می‌آید و بار کار می‌کند، هرچند قفل هنوز هست</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="56" t="inlineStr">
         <is>
           <t>وتو تابع تیک پنل</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="56" t="inlineStr">
         <is>
           <t>کارکردن خروجی با تیک خاموش = قبول؛ وتوی همیشگی = رد</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="M14" s="56" t="n"/>
+      <c r="N14" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O14" s="23" t="inlineStr">
+      <c r="O14" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="23" t="inlineStr">
+      <c r="P14" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="Q14" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>IM-012</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>بودجهٔ سیکل شارژ</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است و شارژ باتری قفل‌شده هنوز اجازه دارد</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="61" t="inlineStr">
         <is>
           <t>گام ۱: چند چرخهٔ شارژ کامل روی همان باتری انجام بده.
 گام ۲: بعد از هر چرخه ببین شارژ هنوز شروع می‌شود یا نه.</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="63" t="inlineStr">
         <is>
           <t>چند چرخهٔ شارژ پشت سر هم در قفل</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="63" t="inlineStr">
         <is>
           <t>چند چرخهٔ شارژ</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="61" t="inlineStr">
         <is>
           <t>بعد از تمام‌شدن بودجهٔ چرخه‌های مجاز، شارژ آن باتری هم دیگر شروع نمی‌شود</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="61" t="inlineStr">
         <is>
           <t>توقف شارژ بعد از بودجه</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="61" t="inlineStr">
         <is>
           <t>توقف بعد از چرخه‌های مجاز = قبول؛ شارژ بی‌نهایت در قفل = رد</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="26" t="n"/>
-      <c r="N15" s="26" t="inlineStr">
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O15" s="28" t="inlineStr">
+      <c r="O15" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="28" t="inlineStr">
+      <c r="P15" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q15" s="29" t="inlineStr">
+      <c r="Q15" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>IM-013</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="56" t="inlineStr">
         <is>
           <t>ریست با تعویض باتری</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="56" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است و چراغ قرمز چشمک می‌زند</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="56" t="inlineStr">
         <is>
           <t>گام ۱: هر دو باتری را با دو باتری سالم و هم‌شارژ عوض کن.
 گام ۲: چند دقیقه صبر کن و چراغ‌ها را ببین.</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="58" t="inlineStr">
         <is>
           <t>تعویض واقعی هر دو باتری</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="58" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="56" t="inlineStr">
         <is>
           <t>قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="56" t="inlineStr">
         <is>
           <t>پاک‌شدن خودکار با تعویض</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="J16" s="56" t="inlineStr">
         <is>
           <t>پاک‌شدن خودکار = قبول؛ ماندن قفل با باتری سالم = رد</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="M16" s="56" t="n"/>
+      <c r="N16" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O16" s="23" t="inlineStr">
+      <c r="O16" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P16" s="23" t="inlineStr">
+      <c r="P16" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="Q16" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>IM-014</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>جدا شدن کوتاه</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="65" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌ها را فقط چند ثانیه جدا کن و سریع وصل کن.
 گام ۲: چراغ‌ها را ببین؛ قفل باید سر جایش باشد.
 گام ۳: حالا تعویض واقعی (IM-013) انجام بده و تفاوت را ببین.</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="63" t="inlineStr">
         <is>
           <t>جدا کردن کوتاه در برابر تعویض واقعی</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="61" t="inlineStr">
         <is>
           <t>قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="I17" s="61" t="inlineStr">
         <is>
           <t>قفل در برابر قطع کوتاه مقاوم</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="61" t="inlineStr">
         <is>
           <t>ماندن قفل بعد قطع کوتاه = قبول؛ پاک‌شدن با قطع کوتاه = رد</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="26" t="n"/>
-      <c r="N17" s="26" t="inlineStr">
+      <c r="M17" s="61" t="n"/>
+      <c r="N17" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O17" s="28" t="inlineStr">
+      <c r="O17" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P17" s="28" t="inlineStr">
+      <c r="P17" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q17" s="29" t="inlineStr">
+      <c r="Q17" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>IM-015</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="56" t="inlineStr">
         <is>
           <t>بازهٔ پارامترها</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="58" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="56" t="inlineStr">
         <is>
           <t>پنل باز است و تنظیم‌های عدم‌توازن را می‌بینی</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="56" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک حدّ ناممکن بفرست (مثلاً اختلاف مجاز خیلی بزرگ یا منفیِ معادل).
 گام ۲: مقدار ذخیره‌شده را دوباره از پنل بخوان.</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="58" t="inlineStr">
         <is>
           <t>فرستادن مقدار بیرون بازه از پنل</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="56" t="inlineStr">
         <is>
           <t>دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="56" t="inlineStr">
         <is>
           <t>حفظ مقدار قبلی</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J18" s="56" t="inlineStr">
         <is>
           <t>رد شدن مقدار خراب = قبول؛ ذخیره‌شدن مقدار ناممکن = رد</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="M18" s="56" t="n"/>
+      <c r="N18" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O18" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P18" s="23" t="inlineStr">
+      <c r="P18" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="Q18" s="60" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>ماندگاری تنظیم‌ها پس از قطع برق</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>پنل باز است</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>گام ۱: یک تنظیم عدم‌توازن را از پنل عوض کن (مثلاً اختلاف مجاز).
 گام ۲: برق دستگاه را کامل قطع و دوباره وصل کن.
 گام ۳: تنظیم را از پنل دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="63" t="inlineStr">
         <is>
           <t>تغییر تنظیم و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
+      <c r="H19" s="61" t="inlineStr">
         <is>
           <t>همان تنظیم تازه بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="I19" s="61" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="61" t="inlineStr">
         <is>
           <t>حفظ تنظیم = قبول؛ برگشت به مقدار قبلی = رد</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="30" t="inlineStr">
+      <c r="M19" s="65" t="inlineStr">
         <is>
           <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
         </is>
       </c>
-      <c r="N19" s="26" t="inlineStr">
+      <c r="N19" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O19" s="28" t="inlineStr">
+      <c r="O19" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P19" s="28" t="inlineStr">
+      <c r="P19" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q19" s="29" t="inlineStr">
+      <c r="Q19" s="64" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>IM-017</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="56" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="56" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال و شمارنده چند رویداد دارد</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="56" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: روشن کن و چراغ‌ها و شمارنده را چک کن.</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="58" t="inlineStr">
         <is>
           <t>قطع و وصل برق در قفل</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="56" t="inlineStr">
         <is>
           <t>قفل و شمارنده بعد از روشن‌شدن دقیقاً سر جایشان‌اند</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="56" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="J20" s="56" t="inlineStr">
         <is>
           <t>حفظ هر دو = قبول؛ پاک‌شدن با قطع برق = رد</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="K20" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="M20" s="56" t="inlineStr">
         <is>
           <t>'برنامه تست'!A5</t>
         </is>
       </c>
-      <c r="N20" s="21" t="inlineStr">
+      <c r="N20" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O20" s="23" t="inlineStr">
+      <c r="O20" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
+      <c r="P20" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="Q20" s="60" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="Q21" s="33">
+      <c r="A21" s="53" t="n"/>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="53" t="n"/>
+      <c r="H21" s="53" t="n"/>
+      <c r="I21" s="53" t="n"/>
+      <c r="J21" s="53" t="n"/>
+      <c r="K21" s="53" t="n"/>
+      <c r="L21" s="53" t="n"/>
+      <c r="M21" s="53" t="n"/>
+      <c r="N21" s="53" t="n"/>
+      <c r="O21" s="53" t="n"/>
+      <c r="P21" s="53" t="n"/>
+      <c r="Q21" s="67">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="40.5" customHeight="1">
-      <c r="Q22" s="33">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="53" t="n"/>
+      <c r="H22" s="53" t="n"/>
+      <c r="I22" s="53" t="n"/>
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="53" t="n"/>
+      <c r="L22" s="53" t="n"/>
+      <c r="M22" s="53" t="n"/>
+      <c r="N22" s="53" t="n"/>
+      <c r="O22" s="53" t="n"/>
+      <c r="P22" s="53" t="n"/>
+      <c r="Q22" s="67">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="33">
+      <c r="A23" s="53" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="53" t="n"/>
+      <c r="H23" s="53" t="n"/>
+      <c r="I23" s="53" t="n"/>
+      <c r="J23" s="53" t="n"/>
+      <c r="K23" s="53" t="n"/>
+      <c r="L23" s="53" t="n"/>
+      <c r="M23" s="53" t="n"/>
+      <c r="N23" s="53" t="n"/>
+      <c r="O23" s="53" t="n"/>
+      <c r="P23" s="53" t="n"/>
+      <c r="Q23" s="67">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="33">
+      <c r="A24" s="53" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="53" t="n"/>
+      <c r="H24" s="53" t="n"/>
+      <c r="I24" s="53" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="53" t="n"/>
+      <c r="L24" s="53" t="n"/>
+      <c r="M24" s="53" t="n"/>
+      <c r="N24" s="53" t="n"/>
+      <c r="O24" s="53" t="n"/>
+      <c r="P24" s="53" t="n"/>
+      <c r="Q24" s="67">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="33">
+      <c r="A25" s="53" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="53" t="n"/>
+      <c r="H25" s="53" t="n"/>
+      <c r="I25" s="53" t="n"/>
+      <c r="J25" s="53" t="n"/>
+      <c r="K25" s="53" t="n"/>
+      <c r="L25" s="53" t="n"/>
+      <c r="M25" s="53" t="n"/>
+      <c r="N25" s="53" t="n"/>
+      <c r="O25" s="53" t="n"/>
+      <c r="P25" s="53" t="n"/>
+      <c r="Q25" s="67">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="33">
+      <c r="A26" s="53" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="53" t="n"/>
+      <c r="G26" s="53" t="n"/>
+      <c r="H26" s="53" t="n"/>
+      <c r="I26" s="53" t="n"/>
+      <c r="J26" s="53" t="n"/>
+      <c r="K26" s="53" t="n"/>
+      <c r="L26" s="53" t="n"/>
+      <c r="M26" s="53" t="n"/>
+      <c r="N26" s="53" t="n"/>
+      <c r="O26" s="53" t="n"/>
+      <c r="P26" s="53" t="n"/>
+      <c r="Q26" s="67">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="33">
+      <c r="A27" s="53" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="53" t="n"/>
+      <c r="G27" s="53" t="n"/>
+      <c r="H27" s="53" t="n"/>
+      <c r="I27" s="53" t="n"/>
+      <c r="J27" s="53" t="n"/>
+      <c r="K27" s="53" t="n"/>
+      <c r="L27" s="53" t="n"/>
+      <c r="M27" s="53" t="n"/>
+      <c r="N27" s="53" t="n"/>
+      <c r="O27" s="53" t="n"/>
+      <c r="P27" s="53" t="n"/>
+      <c r="Q27" s="67">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="33">
+      <c r="A28" s="53" t="n"/>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="53" t="n"/>
+      <c r="G28" s="53" t="n"/>
+      <c r="H28" s="53" t="n"/>
+      <c r="I28" s="53" t="n"/>
+      <c r="J28" s="53" t="n"/>
+      <c r="K28" s="53" t="n"/>
+      <c r="L28" s="53" t="n"/>
+      <c r="M28" s="53" t="n"/>
+      <c r="N28" s="53" t="n"/>
+      <c r="O28" s="53" t="n"/>
+      <c r="P28" s="53" t="n"/>
+      <c r="Q28" s="67">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="33">
+      <c r="A29" s="53" t="n"/>
+      <c r="B29" s="53" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="53" t="n"/>
+      <c r="H29" s="53" t="n"/>
+      <c r="I29" s="53" t="n"/>
+      <c r="J29" s="53" t="n"/>
+      <c r="K29" s="53" t="n"/>
+      <c r="L29" s="53" t="n"/>
+      <c r="M29" s="53" t="n"/>
+      <c r="N29" s="53" t="n"/>
+      <c r="O29" s="53" t="n"/>
+      <c r="P29" s="53" t="n"/>
+      <c r="Q29" s="67">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="33">
+      <c r="A30" s="53" t="n"/>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
+      <c r="E30" s="53" t="n"/>
+      <c r="F30" s="53" t="n"/>
+      <c r="G30" s="53" t="n"/>
+      <c r="H30" s="53" t="n"/>
+      <c r="I30" s="53" t="n"/>
+      <c r="J30" s="53" t="n"/>
+      <c r="K30" s="53" t="n"/>
+      <c r="L30" s="53" t="n"/>
+      <c r="M30" s="53" t="n"/>
+      <c r="N30" s="53" t="n"/>
+      <c r="O30" s="53" t="n"/>
+      <c r="P30" s="53" t="n"/>
+      <c r="Q30" s="67">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="33">
+      <c r="A31" s="53" t="n"/>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
+      <c r="E31" s="53" t="n"/>
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="53" t="n"/>
+      <c r="H31" s="53" t="n"/>
+      <c r="I31" s="53" t="n"/>
+      <c r="J31" s="53" t="n"/>
+      <c r="K31" s="53" t="n"/>
+      <c r="L31" s="53" t="n"/>
+      <c r="M31" s="53" t="n"/>
+      <c r="N31" s="53" t="n"/>
+      <c r="O31" s="53" t="n"/>
+      <c r="P31" s="53" t="n"/>
+      <c r="Q31" s="67">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="33">
+      <c r="A32" s="53" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+      <c r="E32" s="53" t="n"/>
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="53" t="n"/>
+      <c r="H32" s="53" t="n"/>
+      <c r="I32" s="53" t="n"/>
+      <c r="J32" s="53" t="n"/>
+      <c r="K32" s="53" t="n"/>
+      <c r="L32" s="53" t="n"/>
+      <c r="M32" s="53" t="n"/>
+      <c r="N32" s="53" t="n"/>
+      <c r="O32" s="53" t="n"/>
+      <c r="P32" s="53" t="n"/>
+      <c r="Q32" s="67">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="33">
+      <c r="A33" s="53" t="n"/>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="53" t="n"/>
+      <c r="F33" s="53" t="n"/>
+      <c r="G33" s="53" t="n"/>
+      <c r="H33" s="53" t="n"/>
+      <c r="I33" s="53" t="n"/>
+      <c r="J33" s="53" t="n"/>
+      <c r="K33" s="53" t="n"/>
+      <c r="L33" s="53" t="n"/>
+      <c r="M33" s="53" t="n"/>
+      <c r="N33" s="53" t="n"/>
+      <c r="O33" s="53" t="n"/>
+      <c r="P33" s="53" t="n"/>
+      <c r="Q33" s="67">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="33">
+      <c r="A34" s="53" t="n"/>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+      <c r="E34" s="53" t="n"/>
+      <c r="F34" s="53" t="n"/>
+      <c r="G34" s="53" t="n"/>
+      <c r="H34" s="53" t="n"/>
+      <c r="I34" s="53" t="n"/>
+      <c r="J34" s="53" t="n"/>
+      <c r="K34" s="53" t="n"/>
+      <c r="L34" s="53" t="n"/>
+      <c r="M34" s="53" t="n"/>
+      <c r="N34" s="53" t="n"/>
+      <c r="O34" s="53" t="n"/>
+      <c r="P34" s="53" t="n"/>
+      <c r="Q34" s="67">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="33">
+      <c r="A35" s="53" t="n"/>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="53" t="n"/>
+      <c r="G35" s="53" t="n"/>
+      <c r="H35" s="53" t="n"/>
+      <c r="I35" s="53" t="n"/>
+      <c r="J35" s="53" t="n"/>
+      <c r="K35" s="53" t="n"/>
+      <c r="L35" s="53" t="n"/>
+      <c r="M35" s="53" t="n"/>
+      <c r="N35" s="53" t="n"/>
+      <c r="O35" s="53" t="n"/>
+      <c r="P35" s="53" t="n"/>
+      <c r="Q35" s="67">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="33">
+      <c r="A36" s="53" t="n"/>
+      <c r="B36" s="53" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
+      <c r="E36" s="53" t="n"/>
+      <c r="F36" s="53" t="n"/>
+      <c r="G36" s="53" t="n"/>
+      <c r="H36" s="53" t="n"/>
+      <c r="I36" s="53" t="n"/>
+      <c r="J36" s="53" t="n"/>
+      <c r="K36" s="53" t="n"/>
+      <c r="L36" s="53" t="n"/>
+      <c r="M36" s="53" t="n"/>
+      <c r="N36" s="53" t="n"/>
+      <c r="O36" s="53" t="n"/>
+      <c r="P36" s="53" t="n"/>
+      <c r="Q36" s="67">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="33">
+      <c r="A37" s="53" t="n"/>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53" t="n"/>
+      <c r="G37" s="53" t="n"/>
+      <c r="H37" s="53" t="n"/>
+      <c r="I37" s="53" t="n"/>
+      <c r="J37" s="53" t="n"/>
+      <c r="K37" s="53" t="n"/>
+      <c r="L37" s="53" t="n"/>
+      <c r="M37" s="53" t="n"/>
+      <c r="N37" s="53" t="n"/>
+      <c r="O37" s="53" t="n"/>
+      <c r="P37" s="53" t="n"/>
+      <c r="Q37" s="67">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="33">
+      <c r="A38" s="53" t="n"/>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="H38" s="53" t="n"/>
+      <c r="I38" s="53" t="n"/>
+      <c r="J38" s="53" t="n"/>
+      <c r="K38" s="53" t="n"/>
+      <c r="L38" s="53" t="n"/>
+      <c r="M38" s="53" t="n"/>
+      <c r="N38" s="53" t="n"/>
+      <c r="O38" s="53" t="n"/>
+      <c r="P38" s="53" t="n"/>
+      <c r="Q38" s="67">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="33">
+      <c r="A39" s="53" t="n"/>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="H39" s="53" t="n"/>
+      <c r="I39" s="53" t="n"/>
+      <c r="J39" s="53" t="n"/>
+      <c r="K39" s="53" t="n"/>
+      <c r="L39" s="53" t="n"/>
+      <c r="M39" s="53" t="n"/>
+      <c r="N39" s="53" t="n"/>
+      <c r="O39" s="53" t="n"/>
+      <c r="P39" s="53" t="n"/>
+      <c r="Q39" s="67">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="33">
+      <c r="A40" s="53" t="n"/>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
+      <c r="I40" s="53" t="n"/>
+      <c r="J40" s="53" t="n"/>
+      <c r="K40" s="53" t="n"/>
+      <c r="L40" s="53" t="n"/>
+      <c r="M40" s="53" t="n"/>
+      <c r="N40" s="53" t="n"/>
+      <c r="O40" s="53" t="n"/>
+      <c r="P40" s="53" t="n"/>
+      <c r="Q40" s="67">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="33">
+      <c r="A41" s="53" t="n"/>
+      <c r="B41" s="53" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
+      <c r="E41" s="53" t="n"/>
+      <c r="F41" s="53" t="n"/>
+      <c r="G41" s="53" t="n"/>
+      <c r="H41" s="53" t="n"/>
+      <c r="I41" s="53" t="n"/>
+      <c r="J41" s="53" t="n"/>
+      <c r="K41" s="53" t="n"/>
+      <c r="L41" s="53" t="n"/>
+      <c r="M41" s="53" t="n"/>
+      <c r="N41" s="53" t="n"/>
+      <c r="O41" s="53" t="n"/>
+      <c r="P41" s="53" t="n"/>
+      <c r="Q41" s="67">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="33">
+      <c r="A42" s="53" t="n"/>
+      <c r="B42" s="53" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
+      <c r="E42" s="53" t="n"/>
+      <c r="F42" s="53" t="n"/>
+      <c r="G42" s="53" t="n"/>
+      <c r="H42" s="53" t="n"/>
+      <c r="I42" s="53" t="n"/>
+      <c r="J42" s="53" t="n"/>
+      <c r="K42" s="53" t="n"/>
+      <c r="L42" s="53" t="n"/>
+      <c r="M42" s="53" t="n"/>
+      <c r="N42" s="53" t="n"/>
+      <c r="O42" s="53" t="n"/>
+      <c r="P42" s="53" t="n"/>
+      <c r="Q42" s="67">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="33">
+      <c r="A43" s="53" t="n"/>
+      <c r="B43" s="53" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
+      <c r="E43" s="53" t="n"/>
+      <c r="F43" s="53" t="n"/>
+      <c r="G43" s="53" t="n"/>
+      <c r="H43" s="53" t="n"/>
+      <c r="I43" s="53" t="n"/>
+      <c r="J43" s="53" t="n"/>
+      <c r="K43" s="53" t="n"/>
+      <c r="L43" s="53" t="n"/>
+      <c r="M43" s="53" t="n"/>
+      <c r="N43" s="53" t="n"/>
+      <c r="O43" s="53" t="n"/>
+      <c r="P43" s="53" t="n"/>
+      <c r="Q43" s="67">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="33">
+      <c r="A44" s="53" t="n"/>
+      <c r="B44" s="53" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
+      <c r="E44" s="53" t="n"/>
+      <c r="F44" s="53" t="n"/>
+      <c r="G44" s="53" t="n"/>
+      <c r="H44" s="53" t="n"/>
+      <c r="I44" s="53" t="n"/>
+      <c r="J44" s="53" t="n"/>
+      <c r="K44" s="53" t="n"/>
+      <c r="L44" s="53" t="n"/>
+      <c r="M44" s="53" t="n"/>
+      <c r="N44" s="53" t="n"/>
+      <c r="O44" s="53" t="n"/>
+      <c r="P44" s="53" t="n"/>
+      <c r="Q44" s="67">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="33">
+      <c r="A45" s="53" t="n"/>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
+      <c r="E45" s="53" t="n"/>
+      <c r="F45" s="53" t="n"/>
+      <c r="G45" s="53" t="n"/>
+      <c r="H45" s="53" t="n"/>
+      <c r="I45" s="53" t="n"/>
+      <c r="J45" s="53" t="n"/>
+      <c r="K45" s="53" t="n"/>
+      <c r="L45" s="53" t="n"/>
+      <c r="M45" s="53" t="n"/>
+      <c r="N45" s="53" t="n"/>
+      <c r="O45" s="53" t="n"/>
+      <c r="P45" s="53" t="n"/>
+      <c r="Q45" s="67">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="33">
+      <c r="A46" s="53" t="n"/>
+      <c r="B46" s="53" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
+      <c r="E46" s="53" t="n"/>
+      <c r="F46" s="53" t="n"/>
+      <c r="G46" s="53" t="n"/>
+      <c r="H46" s="53" t="n"/>
+      <c r="I46" s="53" t="n"/>
+      <c r="J46" s="53" t="n"/>
+      <c r="K46" s="53" t="n"/>
+      <c r="L46" s="53" t="n"/>
+      <c r="M46" s="53" t="n"/>
+      <c r="N46" s="53" t="n"/>
+      <c r="O46" s="53" t="n"/>
+      <c r="P46" s="53" t="n"/>
+      <c r="Q46" s="67">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="33">
+      <c r="A47" s="53" t="n"/>
+      <c r="B47" s="53" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
+      <c r="E47" s="53" t="n"/>
+      <c r="F47" s="53" t="n"/>
+      <c r="G47" s="53" t="n"/>
+      <c r="H47" s="53" t="n"/>
+      <c r="I47" s="53" t="n"/>
+      <c r="J47" s="53" t="n"/>
+      <c r="K47" s="53" t="n"/>
+      <c r="L47" s="53" t="n"/>
+      <c r="M47" s="53" t="n"/>
+      <c r="N47" s="53" t="n"/>
+      <c r="O47" s="53" t="n"/>
+      <c r="P47" s="53" t="n"/>
+      <c r="Q47" s="67">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="33">
+      <c r="A48" s="53" t="n"/>
+      <c r="B48" s="53" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
+      <c r="E48" s="53" t="n"/>
+      <c r="F48" s="53" t="n"/>
+      <c r="G48" s="53" t="n"/>
+      <c r="H48" s="53" t="n"/>
+      <c r="I48" s="53" t="n"/>
+      <c r="J48" s="53" t="n"/>
+      <c r="K48" s="53" t="n"/>
+      <c r="L48" s="53" t="n"/>
+      <c r="M48" s="53" t="n"/>
+      <c r="N48" s="53" t="n"/>
+      <c r="O48" s="53" t="n"/>
+      <c r="P48" s="53" t="n"/>
+      <c r="Q48" s="67">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="33">
+      <c r="A49" s="53" t="n"/>
+      <c r="B49" s="53" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
+      <c r="E49" s="53" t="n"/>
+      <c r="F49" s="53" t="n"/>
+      <c r="G49" s="53" t="n"/>
+      <c r="H49" s="53" t="n"/>
+      <c r="I49" s="53" t="n"/>
+      <c r="J49" s="53" t="n"/>
+      <c r="K49" s="53" t="n"/>
+      <c r="L49" s="53" t="n"/>
+      <c r="M49" s="53" t="n"/>
+      <c r="N49" s="53" t="n"/>
+      <c r="O49" s="53" t="n"/>
+      <c r="P49" s="53" t="n"/>
+      <c r="Q49" s="67">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="33">
+      <c r="A50" s="53" t="n"/>
+      <c r="B50" s="53" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
+      <c r="E50" s="53" t="n"/>
+      <c r="F50" s="53" t="n"/>
+      <c r="G50" s="53" t="n"/>
+      <c r="H50" s="53" t="n"/>
+      <c r="I50" s="53" t="n"/>
+      <c r="J50" s="53" t="n"/>
+      <c r="K50" s="53" t="n"/>
+      <c r="L50" s="53" t="n"/>
+      <c r="M50" s="53" t="n"/>
+      <c r="N50" s="53" t="n"/>
+      <c r="O50" s="53" t="n"/>
+      <c r="P50" s="53" t="n"/>
+      <c r="Q50" s="67">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="33">
+      <c r="A51" s="53" t="n"/>
+      <c r="B51" s="53" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
+      <c r="E51" s="53" t="n"/>
+      <c r="F51" s="53" t="n"/>
+      <c r="G51" s="53" t="n"/>
+      <c r="H51" s="53" t="n"/>
+      <c r="I51" s="53" t="n"/>
+      <c r="J51" s="53" t="n"/>
+      <c r="K51" s="53" t="n"/>
+      <c r="L51" s="53" t="n"/>
+      <c r="M51" s="53" t="n"/>
+      <c r="N51" s="53" t="n"/>
+      <c r="O51" s="53" t="n"/>
+      <c r="P51" s="53" t="n"/>
+      <c r="Q51" s="67">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="33">
+      <c r="A52" s="53" t="n"/>
+      <c r="B52" s="53" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
+      <c r="E52" s="53" t="n"/>
+      <c r="F52" s="53" t="n"/>
+      <c r="G52" s="53" t="n"/>
+      <c r="H52" s="53" t="n"/>
+      <c r="I52" s="53" t="n"/>
+      <c r="J52" s="53" t="n"/>
+      <c r="K52" s="53" t="n"/>
+      <c r="L52" s="53" t="n"/>
+      <c r="M52" s="53" t="n"/>
+      <c r="N52" s="53" t="n"/>
+      <c r="O52" s="53" t="n"/>
+      <c r="P52" s="53" t="n"/>
+      <c r="Q52" s="67">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="Q53" s="33">
+      <c r="A53" s="53" t="n"/>
+      <c r="B53" s="53" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
+      <c r="E53" s="53" t="n"/>
+      <c r="F53" s="53" t="n"/>
+      <c r="G53" s="53" t="n"/>
+      <c r="H53" s="53" t="n"/>
+      <c r="I53" s="53" t="n"/>
+      <c r="J53" s="53" t="n"/>
+      <c r="K53" s="53" t="n"/>
+      <c r="L53" s="53" t="n"/>
+      <c r="M53" s="53" t="n"/>
+      <c r="N53" s="53" t="n"/>
+      <c r="O53" s="53" t="n"/>
+      <c r="P53" s="53" t="n"/>
+      <c r="Q53" s="67">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="Q54" s="33">
+      <c r="A54" s="53" t="n"/>
+      <c r="B54" s="53" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
+      <c r="E54" s="53" t="n"/>
+      <c r="F54" s="53" t="n"/>
+      <c r="G54" s="53" t="n"/>
+      <c r="H54" s="53" t="n"/>
+      <c r="I54" s="53" t="n"/>
+      <c r="J54" s="53" t="n"/>
+      <c r="K54" s="53" t="n"/>
+      <c r="L54" s="53" t="n"/>
+      <c r="M54" s="53" t="n"/>
+      <c r="N54" s="53" t="n"/>
+      <c r="O54" s="53" t="n"/>
+      <c r="P54" s="53" t="n"/>
+      <c r="Q54" s="67">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="Q55" s="33">
+      <c r="A55" s="53" t="n"/>
+      <c r="B55" s="53" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
+      <c r="E55" s="53" t="n"/>
+      <c r="F55" s="53" t="n"/>
+      <c r="G55" s="53" t="n"/>
+      <c r="H55" s="53" t="n"/>
+      <c r="I55" s="53" t="n"/>
+      <c r="J55" s="53" t="n"/>
+      <c r="K55" s="53" t="n"/>
+      <c r="L55" s="53" t="n"/>
+      <c r="M55" s="53" t="n"/>
+      <c r="N55" s="53" t="n"/>
+      <c r="O55" s="53" t="n"/>
+      <c r="P55" s="53" t="n"/>
+      <c r="Q55" s="67">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="Q56" s="33">
+      <c r="A56" s="53" t="n"/>
+      <c r="B56" s="53" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
+      <c r="E56" s="53" t="n"/>
+      <c r="F56" s="53" t="n"/>
+      <c r="G56" s="53" t="n"/>
+      <c r="H56" s="53" t="n"/>
+      <c r="I56" s="53" t="n"/>
+      <c r="J56" s="53" t="n"/>
+      <c r="K56" s="53" t="n"/>
+      <c r="L56" s="53" t="n"/>
+      <c r="M56" s="53" t="n"/>
+      <c r="N56" s="53" t="n"/>
+      <c r="O56" s="53" t="n"/>
+      <c r="P56" s="53" t="n"/>
+      <c r="Q56" s="67">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="Q57" s="33">
+      <c r="A57" s="53" t="n"/>
+      <c r="B57" s="53" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
+      <c r="E57" s="53" t="n"/>
+      <c r="F57" s="53" t="n"/>
+      <c r="G57" s="53" t="n"/>
+      <c r="H57" s="53" t="n"/>
+      <c r="I57" s="53" t="n"/>
+      <c r="J57" s="53" t="n"/>
+      <c r="K57" s="53" t="n"/>
+      <c r="L57" s="53" t="n"/>
+      <c r="M57" s="53" t="n"/>
+      <c r="N57" s="53" t="n"/>
+      <c r="O57" s="53" t="n"/>
+      <c r="P57" s="53" t="n"/>
+      <c r="Q57" s="67">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="Q58" s="33">
+      <c r="A58" s="53" t="n"/>
+      <c r="B58" s="53" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
+      <c r="E58" s="53" t="n"/>
+      <c r="F58" s="53" t="n"/>
+      <c r="G58" s="53" t="n"/>
+      <c r="H58" s="53" t="n"/>
+      <c r="I58" s="53" t="n"/>
+      <c r="J58" s="53" t="n"/>
+      <c r="K58" s="53" t="n"/>
+      <c r="L58" s="53" t="n"/>
+      <c r="M58" s="53" t="n"/>
+      <c r="N58" s="53" t="n"/>
+      <c r="O58" s="53" t="n"/>
+      <c r="P58" s="53" t="n"/>
+      <c r="Q58" s="67">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="Q59" s="33">
+      <c r="A59" s="53" t="n"/>
+      <c r="B59" s="53" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
+      <c r="E59" s="53" t="n"/>
+      <c r="F59" s="53" t="n"/>
+      <c r="G59" s="53" t="n"/>
+      <c r="H59" s="53" t="n"/>
+      <c r="I59" s="53" t="n"/>
+      <c r="J59" s="53" t="n"/>
+      <c r="K59" s="53" t="n"/>
+      <c r="L59" s="53" t="n"/>
+      <c r="M59" s="53" t="n"/>
+      <c r="N59" s="53" t="n"/>
+      <c r="O59" s="53" t="n"/>
+      <c r="P59" s="53" t="n"/>
+      <c r="Q59" s="67">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="Q60" s="33">
+      <c r="A60" s="53" t="n"/>
+      <c r="B60" s="53" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
+      <c r="E60" s="53" t="n"/>
+      <c r="F60" s="53" t="n"/>
+      <c r="G60" s="53" t="n"/>
+      <c r="H60" s="53" t="n"/>
+      <c r="I60" s="53" t="n"/>
+      <c r="J60" s="53" t="n"/>
+      <c r="K60" s="53" t="n"/>
+      <c r="L60" s="53" t="n"/>
+      <c r="M60" s="53" t="n"/>
+      <c r="N60" s="53" t="n"/>
+      <c r="O60" s="53" t="n"/>
+      <c r="P60" s="53" t="n"/>
+      <c r="Q60" s="67">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
@@ -2592,129 +3402,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
+      <c r="D1" s="53" t="n"/>
+      <c r="E1" s="53" t="n"/>
+      <c r="F1" s="53" t="n"/>
+      <c r="G1" s="53" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="53" t="n"/>
+      <c r="J1" s="53" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="53" t="n"/>
+      <c r="M1" s="53" t="n"/>
+      <c r="N1" s="53" t="n"/>
+      <c r="O1" s="53" t="n"/>
+      <c r="P1" s="53" t="n"/>
+      <c r="Q1" s="53" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="68" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="53" t="n"/>
+      <c r="L2" s="53" t="n"/>
+      <c r="M2" s="53" t="n"/>
+      <c r="N2" s="53" t="n"/>
+      <c r="O2" s="53" t="n"/>
+      <c r="P2" s="53" t="n"/>
+      <c r="Q2" s="53" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="53" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="53" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="15" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="15" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>IM-008</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>چشمک قفل</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>قفل فعال</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="65" t="inlineStr">
         <is>
           <t>گام ۱: قفل را فعال نگه دار (IM-007).
 گام ۲: پارامتر 123 (دورهٔ چشمک) را 1000 میلی‌ثانیه و پارامتر 124 (سهم روشنی) را 50 درصد بگذار.
@@ -2722,179 +3582,499 @@
 گام ۴: در 60 ثانیه چند دوره را چک کن: دوره باید 1000 میلی‌ثانیه و روشنی 50 درصد باشد، با خطای حداکثر ±5 درصد.</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>۱۰۰۰ms و ۵۰٪</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>۶۰ ثانیه</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>چشمک قرمز با همان دوره و duty</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="61" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr">
         <is>
           <t>اندازه‌گیری با کرنومتر یا اسیلوسکوپ در ±۵٪</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="26" t="n"/>
-      <c r="N5" s="26" t="inlineStr">
+      <c r="M5" s="61" t="n"/>
+      <c r="N5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O5" s="28" t="inlineStr">
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="28" t="inlineStr">
+      <c r="P5" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="29" t="inlineStr">
+      <c r="Q5" s="64" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="33">
+      <c r="A6" s="53" t="n"/>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="53" t="n"/>
+      <c r="I6" s="53" t="n"/>
+      <c r="J6" s="53" t="n"/>
+      <c r="K6" s="53" t="n"/>
+      <c r="L6" s="53" t="n"/>
+      <c r="M6" s="53" t="n"/>
+      <c r="N6" s="53" t="n"/>
+      <c r="O6" s="53" t="n"/>
+      <c r="P6" s="53" t="n"/>
+      <c r="Q6" s="67">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="33">
+      <c r="A7" s="53" t="n"/>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="53" t="n"/>
+      <c r="I7" s="53" t="n"/>
+      <c r="J7" s="53" t="n"/>
+      <c r="K7" s="53" t="n"/>
+      <c r="L7" s="53" t="n"/>
+      <c r="M7" s="53" t="n"/>
+      <c r="N7" s="53" t="n"/>
+      <c r="O7" s="53" t="n"/>
+      <c r="P7" s="53" t="n"/>
+      <c r="Q7" s="67">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="33">
+      <c r="A8" s="53" t="n"/>
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="53" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="53" t="n"/>
+      <c r="L8" s="53" t="n"/>
+      <c r="M8" s="53" t="n"/>
+      <c r="N8" s="53" t="n"/>
+      <c r="O8" s="53" t="n"/>
+      <c r="P8" s="53" t="n"/>
+      <c r="Q8" s="67">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="33">
+      <c r="A9" s="53" t="n"/>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="53" t="n"/>
+      <c r="I9" s="53" t="n"/>
+      <c r="J9" s="53" t="n"/>
+      <c r="K9" s="53" t="n"/>
+      <c r="L9" s="53" t="n"/>
+      <c r="M9" s="53" t="n"/>
+      <c r="N9" s="53" t="n"/>
+      <c r="O9" s="53" t="n"/>
+      <c r="P9" s="53" t="n"/>
+      <c r="Q9" s="67">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="33">
+      <c r="A10" s="53" t="n"/>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
+      <c r="I10" s="53" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="53" t="n"/>
+      <c r="L10" s="53" t="n"/>
+      <c r="M10" s="53" t="n"/>
+      <c r="N10" s="53" t="n"/>
+      <c r="O10" s="53" t="n"/>
+      <c r="P10" s="53" t="n"/>
+      <c r="Q10" s="67">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="33">
+      <c r="A11" s="53" t="n"/>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
+      <c r="I11" s="53" t="n"/>
+      <c r="J11" s="53" t="n"/>
+      <c r="K11" s="53" t="n"/>
+      <c r="L11" s="53" t="n"/>
+      <c r="M11" s="53" t="n"/>
+      <c r="N11" s="53" t="n"/>
+      <c r="O11" s="53" t="n"/>
+      <c r="P11" s="53" t="n"/>
+      <c r="Q11" s="67">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="33">
+      <c r="A12" s="53" t="n"/>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
+      <c r="I12" s="53" t="n"/>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="53" t="n"/>
+      <c r="L12" s="53" t="n"/>
+      <c r="M12" s="53" t="n"/>
+      <c r="N12" s="53" t="n"/>
+      <c r="O12" s="53" t="n"/>
+      <c r="P12" s="53" t="n"/>
+      <c r="Q12" s="67">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="33">
+      <c r="A13" s="53" t="n"/>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="53" t="n"/>
+      <c r="I13" s="53" t="n"/>
+      <c r="J13" s="53" t="n"/>
+      <c r="K13" s="53" t="n"/>
+      <c r="L13" s="53" t="n"/>
+      <c r="M13" s="53" t="n"/>
+      <c r="N13" s="53" t="n"/>
+      <c r="O13" s="53" t="n"/>
+      <c r="P13" s="53" t="n"/>
+      <c r="Q13" s="67">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="33">
+      <c r="A14" s="53" t="n"/>
+      <c r="B14" s="53" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="53" t="n"/>
+      <c r="H14" s="53" t="n"/>
+      <c r="I14" s="53" t="n"/>
+      <c r="J14" s="53" t="n"/>
+      <c r="K14" s="53" t="n"/>
+      <c r="L14" s="53" t="n"/>
+      <c r="M14" s="53" t="n"/>
+      <c r="N14" s="53" t="n"/>
+      <c r="O14" s="53" t="n"/>
+      <c r="P14" s="53" t="n"/>
+      <c r="Q14" s="67">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="33">
+      <c r="A15" s="53" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="53" t="n"/>
+      <c r="H15" s="53" t="n"/>
+      <c r="I15" s="53" t="n"/>
+      <c r="J15" s="53" t="n"/>
+      <c r="K15" s="53" t="n"/>
+      <c r="L15" s="53" t="n"/>
+      <c r="M15" s="53" t="n"/>
+      <c r="N15" s="53" t="n"/>
+      <c r="O15" s="53" t="n"/>
+      <c r="P15" s="53" t="n"/>
+      <c r="Q15" s="67">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="33">
+      <c r="A16" s="53" t="n"/>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
+      <c r="I16" s="53" t="n"/>
+      <c r="J16" s="53" t="n"/>
+      <c r="K16" s="53" t="n"/>
+      <c r="L16" s="53" t="n"/>
+      <c r="M16" s="53" t="n"/>
+      <c r="N16" s="53" t="n"/>
+      <c r="O16" s="53" t="n"/>
+      <c r="P16" s="53" t="n"/>
+      <c r="Q16" s="67">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="33">
+      <c r="A17" s="53" t="n"/>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="53" t="n"/>
+      <c r="H17" s="53" t="n"/>
+      <c r="I17" s="53" t="n"/>
+      <c r="J17" s="53" t="n"/>
+      <c r="K17" s="53" t="n"/>
+      <c r="L17" s="53" t="n"/>
+      <c r="M17" s="53" t="n"/>
+      <c r="N17" s="53" t="n"/>
+      <c r="O17" s="53" t="n"/>
+      <c r="P17" s="53" t="n"/>
+      <c r="Q17" s="67">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="33">
+      <c r="A18" s="53" t="n"/>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
+      <c r="I18" s="53" t="n"/>
+      <c r="J18" s="53" t="n"/>
+      <c r="K18" s="53" t="n"/>
+      <c r="L18" s="53" t="n"/>
+      <c r="M18" s="53" t="n"/>
+      <c r="N18" s="53" t="n"/>
+      <c r="O18" s="53" t="n"/>
+      <c r="P18" s="53" t="n"/>
+      <c r="Q18" s="67">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="33">
+      <c r="A19" s="53" t="n"/>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="53" t="n"/>
+      <c r="H19" s="53" t="n"/>
+      <c r="I19" s="53" t="n"/>
+      <c r="J19" s="53" t="n"/>
+      <c r="K19" s="53" t="n"/>
+      <c r="L19" s="53" t="n"/>
+      <c r="M19" s="53" t="n"/>
+      <c r="N19" s="53" t="n"/>
+      <c r="O19" s="53" t="n"/>
+      <c r="P19" s="53" t="n"/>
+      <c r="Q19" s="67">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="33">
+      <c r="A20" s="53" t="n"/>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="53" t="n"/>
+      <c r="H20" s="53" t="n"/>
+      <c r="I20" s="53" t="n"/>
+      <c r="J20" s="53" t="n"/>
+      <c r="K20" s="53" t="n"/>
+      <c r="L20" s="53" t="n"/>
+      <c r="M20" s="53" t="n"/>
+      <c r="N20" s="53" t="n"/>
+      <c r="O20" s="53" t="n"/>
+      <c r="P20" s="53" t="n"/>
+      <c r="Q20" s="67">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="33">
+      <c r="A21" s="53" t="n"/>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="53" t="n"/>
+      <c r="H21" s="53" t="n"/>
+      <c r="I21" s="53" t="n"/>
+      <c r="J21" s="53" t="n"/>
+      <c r="K21" s="53" t="n"/>
+      <c r="L21" s="53" t="n"/>
+      <c r="M21" s="53" t="n"/>
+      <c r="N21" s="53" t="n"/>
+      <c r="O21" s="53" t="n"/>
+      <c r="P21" s="53" t="n"/>
+      <c r="Q21" s="67">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="33">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="53" t="n"/>
+      <c r="H22" s="53" t="n"/>
+      <c r="I22" s="53" t="n"/>
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="53" t="n"/>
+      <c r="L22" s="53" t="n"/>
+      <c r="M22" s="53" t="n"/>
+      <c r="N22" s="53" t="n"/>
+      <c r="O22" s="53" t="n"/>
+      <c r="P22" s="53" t="n"/>
+      <c r="Q22" s="67">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="33">
+      <c r="A23" s="53" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="53" t="n"/>
+      <c r="H23" s="53" t="n"/>
+      <c r="I23" s="53" t="n"/>
+      <c r="J23" s="53" t="n"/>
+      <c r="K23" s="53" t="n"/>
+      <c r="L23" s="53" t="n"/>
+      <c r="M23" s="53" t="n"/>
+      <c r="N23" s="53" t="n"/>
+      <c r="O23" s="53" t="n"/>
+      <c r="P23" s="53" t="n"/>
+      <c r="Q23" s="67">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="33">
+      <c r="A24" s="53" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="53" t="n"/>
+      <c r="H24" s="53" t="n"/>
+      <c r="I24" s="53" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="53" t="n"/>
+      <c r="L24" s="53" t="n"/>
+      <c r="M24" s="53" t="n"/>
+      <c r="N24" s="53" t="n"/>
+      <c r="O24" s="53" t="n"/>
+      <c r="P24" s="53" t="n"/>
+      <c r="Q24" s="67">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="33">
+      <c r="A25" s="53" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="53" t="n"/>
+      <c r="H25" s="53" t="n"/>
+      <c r="I25" s="53" t="n"/>
+      <c r="J25" s="53" t="n"/>
+      <c r="K25" s="53" t="n"/>
+      <c r="L25" s="53" t="n"/>
+      <c r="M25" s="53" t="n"/>
+      <c r="N25" s="53" t="n"/>
+      <c r="O25" s="53" t="n"/>
+      <c r="P25" s="53" t="n"/>
+      <c r="Q25" s="67">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -2944,296 +4124,666 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
+      <c r="D1" s="53" t="n"/>
+      <c r="E1" s="53" t="n"/>
+      <c r="F1" s="53" t="n"/>
+      <c r="G1" s="53" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="53" t="n"/>
+      <c r="J1" s="53" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="53" t="n"/>
+      <c r="M1" s="53" t="n"/>
+      <c r="N1" s="53" t="n"/>
+      <c r="O1" s="53" t="n"/>
+      <c r="P1" s="53" t="n"/>
+      <c r="Q1" s="53" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="45" t="inlineStr">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="68" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="53" t="n"/>
+      <c r="L2" s="53" t="n"/>
+      <c r="M2" s="53" t="n"/>
+      <c r="N2" s="53" t="n"/>
+      <c r="O2" s="53" t="n"/>
+      <c r="P2" s="53" t="n"/>
+      <c r="Q2" s="53" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="53" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="53" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="15" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="15" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>IM-020</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و ولتاژهای بالا/پایین (vHigh/vLow) را عمداً زباله بگذار.
 گام ۲: آن را 3 ثانیه به Imbalance_Evaluate بده (ورودی‌ها را task_control از قبل صفر می‌کند).
 گام ۳: شمارنده و وضعیت اپیزود را نگاه کن: ماژول باید روی valid گیت بزند و هیچ اپیزود کاذبی نباید ساخته شود.</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>ماژول باید روی valid گیت بزند و بدون episode کاذب بماند؛ ورودی‌ها از task_control صفر شده</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr">
         <is>
           <t>بدون episode کاذب</t>
         </is>
       </c>
-      <c r="K5" s="26" t="n"/>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="K5" s="61" t="n"/>
+      <c r="L5" s="69" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M5" s="26" t="n"/>
-      <c r="N5" s="26" t="n"/>
-      <c r="O5" s="28" t="inlineStr">
+      <c r="M5" s="61" t="n"/>
+      <c r="N5" s="61" t="n"/>
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" s="28" t="n"/>
-      <c r="Q5" s="29" t="inlineStr">
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="64" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="33">
+      <c r="A6" s="53" t="n"/>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="53" t="n"/>
+      <c r="I6" s="53" t="n"/>
+      <c r="J6" s="53" t="n"/>
+      <c r="K6" s="53" t="n"/>
+      <c r="L6" s="53" t="n"/>
+      <c r="M6" s="53" t="n"/>
+      <c r="N6" s="53" t="n"/>
+      <c r="O6" s="53" t="n"/>
+      <c r="P6" s="53" t="n"/>
+      <c r="Q6" s="67">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="33">
+      <c r="A7" s="53" t="n"/>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="53" t="n"/>
+      <c r="I7" s="53" t="n"/>
+      <c r="J7" s="53" t="n"/>
+      <c r="K7" s="53" t="n"/>
+      <c r="L7" s="53" t="n"/>
+      <c r="M7" s="53" t="n"/>
+      <c r="N7" s="53" t="n"/>
+      <c r="O7" s="53" t="n"/>
+      <c r="P7" s="53" t="n"/>
+      <c r="Q7" s="67">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="33">
+      <c r="A8" s="53" t="n"/>
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="53" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="53" t="n"/>
+      <c r="L8" s="53" t="n"/>
+      <c r="M8" s="53" t="n"/>
+      <c r="N8" s="53" t="n"/>
+      <c r="O8" s="53" t="n"/>
+      <c r="P8" s="53" t="n"/>
+      <c r="Q8" s="67">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="33">
+      <c r="A9" s="53" t="n"/>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="53" t="n"/>
+      <c r="I9" s="53" t="n"/>
+      <c r="J9" s="53" t="n"/>
+      <c r="K9" s="53" t="n"/>
+      <c r="L9" s="53" t="n"/>
+      <c r="M9" s="53" t="n"/>
+      <c r="N9" s="53" t="n"/>
+      <c r="O9" s="53" t="n"/>
+      <c r="P9" s="53" t="n"/>
+      <c r="Q9" s="67">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="33">
+      <c r="A10" s="53" t="n"/>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
+      <c r="I10" s="53" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="53" t="n"/>
+      <c r="L10" s="53" t="n"/>
+      <c r="M10" s="53" t="n"/>
+      <c r="N10" s="53" t="n"/>
+      <c r="O10" s="53" t="n"/>
+      <c r="P10" s="53" t="n"/>
+      <c r="Q10" s="67">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="33">
+      <c r="A11" s="53" t="n"/>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
+      <c r="I11" s="53" t="n"/>
+      <c r="J11" s="53" t="n"/>
+      <c r="K11" s="53" t="n"/>
+      <c r="L11" s="53" t="n"/>
+      <c r="M11" s="53" t="n"/>
+      <c r="N11" s="53" t="n"/>
+      <c r="O11" s="53" t="n"/>
+      <c r="P11" s="53" t="n"/>
+      <c r="Q11" s="67">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="33">
+      <c r="A12" s="53" t="n"/>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
+      <c r="I12" s="53" t="n"/>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="53" t="n"/>
+      <c r="L12" s="53" t="n"/>
+      <c r="M12" s="53" t="n"/>
+      <c r="N12" s="53" t="n"/>
+      <c r="O12" s="53" t="n"/>
+      <c r="P12" s="53" t="n"/>
+      <c r="Q12" s="67">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="33">
+      <c r="A13" s="53" t="n"/>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="53" t="n"/>
+      <c r="I13" s="53" t="n"/>
+      <c r="J13" s="53" t="n"/>
+      <c r="K13" s="53" t="n"/>
+      <c r="L13" s="53" t="n"/>
+      <c r="M13" s="53" t="n"/>
+      <c r="N13" s="53" t="n"/>
+      <c r="O13" s="53" t="n"/>
+      <c r="P13" s="53" t="n"/>
+      <c r="Q13" s="67">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="33">
+      <c r="A14" s="53" t="n"/>
+      <c r="B14" s="53" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="53" t="n"/>
+      <c r="H14" s="53" t="n"/>
+      <c r="I14" s="53" t="n"/>
+      <c r="J14" s="53" t="n"/>
+      <c r="K14" s="53" t="n"/>
+      <c r="L14" s="53" t="n"/>
+      <c r="M14" s="53" t="n"/>
+      <c r="N14" s="53" t="n"/>
+      <c r="O14" s="53" t="n"/>
+      <c r="P14" s="53" t="n"/>
+      <c r="Q14" s="67">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="33">
+      <c r="A15" s="53" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="53" t="n"/>
+      <c r="H15" s="53" t="n"/>
+      <c r="I15" s="53" t="n"/>
+      <c r="J15" s="53" t="n"/>
+      <c r="K15" s="53" t="n"/>
+      <c r="L15" s="53" t="n"/>
+      <c r="M15" s="53" t="n"/>
+      <c r="N15" s="53" t="n"/>
+      <c r="O15" s="53" t="n"/>
+      <c r="P15" s="53" t="n"/>
+      <c r="Q15" s="67">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="33">
+      <c r="A16" s="53" t="n"/>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
+      <c r="I16" s="53" t="n"/>
+      <c r="J16" s="53" t="n"/>
+      <c r="K16" s="53" t="n"/>
+      <c r="L16" s="53" t="n"/>
+      <c r="M16" s="53" t="n"/>
+      <c r="N16" s="53" t="n"/>
+      <c r="O16" s="53" t="n"/>
+      <c r="P16" s="53" t="n"/>
+      <c r="Q16" s="67">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="33">
+      <c r="A17" s="53" t="n"/>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="53" t="n"/>
+      <c r="H17" s="53" t="n"/>
+      <c r="I17" s="53" t="n"/>
+      <c r="J17" s="53" t="n"/>
+      <c r="K17" s="53" t="n"/>
+      <c r="L17" s="53" t="n"/>
+      <c r="M17" s="53" t="n"/>
+      <c r="N17" s="53" t="n"/>
+      <c r="O17" s="53" t="n"/>
+      <c r="P17" s="53" t="n"/>
+      <c r="Q17" s="67">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="33">
+      <c r="A18" s="53" t="n"/>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
+      <c r="I18" s="53" t="n"/>
+      <c r="J18" s="53" t="n"/>
+      <c r="K18" s="53" t="n"/>
+      <c r="L18" s="53" t="n"/>
+      <c r="M18" s="53" t="n"/>
+      <c r="N18" s="53" t="n"/>
+      <c r="O18" s="53" t="n"/>
+      <c r="P18" s="53" t="n"/>
+      <c r="Q18" s="67">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="33">
+      <c r="A19" s="53" t="n"/>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="53" t="n"/>
+      <c r="H19" s="53" t="n"/>
+      <c r="I19" s="53" t="n"/>
+      <c r="J19" s="53" t="n"/>
+      <c r="K19" s="53" t="n"/>
+      <c r="L19" s="53" t="n"/>
+      <c r="M19" s="53" t="n"/>
+      <c r="N19" s="53" t="n"/>
+      <c r="O19" s="53" t="n"/>
+      <c r="P19" s="53" t="n"/>
+      <c r="Q19" s="67">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="33">
+      <c r="A20" s="53" t="n"/>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="53" t="n"/>
+      <c r="H20" s="53" t="n"/>
+      <c r="I20" s="53" t="n"/>
+      <c r="J20" s="53" t="n"/>
+      <c r="K20" s="53" t="n"/>
+      <c r="L20" s="53" t="n"/>
+      <c r="M20" s="53" t="n"/>
+      <c r="N20" s="53" t="n"/>
+      <c r="O20" s="53" t="n"/>
+      <c r="P20" s="53" t="n"/>
+      <c r="Q20" s="67">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="33">
+      <c r="A21" s="53" t="n"/>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="53" t="n"/>
+      <c r="H21" s="53" t="n"/>
+      <c r="I21" s="53" t="n"/>
+      <c r="J21" s="53" t="n"/>
+      <c r="K21" s="53" t="n"/>
+      <c r="L21" s="53" t="n"/>
+      <c r="M21" s="53" t="n"/>
+      <c r="N21" s="53" t="n"/>
+      <c r="O21" s="53" t="n"/>
+      <c r="P21" s="53" t="n"/>
+      <c r="Q21" s="67">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="33">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="53" t="n"/>
+      <c r="H22" s="53" t="n"/>
+      <c r="I22" s="53" t="n"/>
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="53" t="n"/>
+      <c r="L22" s="53" t="n"/>
+      <c r="M22" s="53" t="n"/>
+      <c r="N22" s="53" t="n"/>
+      <c r="O22" s="53" t="n"/>
+      <c r="P22" s="53" t="n"/>
+      <c r="Q22" s="67">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="33">
+      <c r="A23" s="53" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="53" t="n"/>
+      <c r="H23" s="53" t="n"/>
+      <c r="I23" s="53" t="n"/>
+      <c r="J23" s="53" t="n"/>
+      <c r="K23" s="53" t="n"/>
+      <c r="L23" s="53" t="n"/>
+      <c r="M23" s="53" t="n"/>
+      <c r="N23" s="53" t="n"/>
+      <c r="O23" s="53" t="n"/>
+      <c r="P23" s="53" t="n"/>
+      <c r="Q23" s="67">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="33">
+      <c r="A24" s="53" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="53" t="n"/>
+      <c r="H24" s="53" t="n"/>
+      <c r="I24" s="53" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="53" t="n"/>
+      <c r="L24" s="53" t="n"/>
+      <c r="M24" s="53" t="n"/>
+      <c r="N24" s="53" t="n"/>
+      <c r="O24" s="53" t="n"/>
+      <c r="P24" s="53" t="n"/>
+      <c r="Q24" s="67">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="33">
+      <c r="A25" s="53" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="53" t="n"/>
+      <c r="H25" s="53" t="n"/>
+      <c r="I25" s="53" t="n"/>
+      <c r="J25" s="53" t="n"/>
+      <c r="K25" s="53" t="n"/>
+      <c r="L25" s="53" t="n"/>
+      <c r="M25" s="53" t="n"/>
+      <c r="N25" s="53" t="n"/>
+      <c r="O25" s="53" t="n"/>
+      <c r="P25" s="53" t="n"/>
+      <c r="Q25" s="67">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -3268,309 +4818,315 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Imbalance</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="48" t="n"/>
+      <c r="C1" s="48" t="n"/>
+      <c r="D1" s="48" t="n"/>
+      <c r="E1" s="48" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="70" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="70" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>حد استراحت</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>۳۰۰mV (پیش‌فرض)</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>شمارش رویداد پس از پایداری</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_REST_LIMIT_MV (۱۰۸) / IMBAL_DEF_REST_LIMIT_MV</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>فقط با گیت زمانی</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>حد دشارژ</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>۵۰۰mV (پیش‌فرض)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>اعمال بلافاصله روی باتری</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_DISCHARGE_LIMIT_MV (۱۰۹)</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="71" t="inlineStr">
         <is>
           <t>بدون گیت زمانی</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>گیت پس از شارژ</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>۱۰ دقیقه</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>پیش از آن بدون قضاوت</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_POST_CHARGE_WAIT_MS (۱۱۰)</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="71" t="inlineStr">
         <is>
           <t>لنگر بوت اگر شارژی تمام نشده</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>گیت حین شارژ</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>۱۰ دقیقه</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>صفر یعنی خاموش</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_IN_CHARGE_WAIT_MS (۱۱۱)</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="71" t="inlineStr">
         <is>
           <t>با همان حد استراحت</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>پایداری</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>۳۰ ثانیه پیوسته</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>یک رویداد</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_STABILITY_MS (۱۱۲)</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="71" t="inlineStr">
         <is>
           <t>هر اپیزود یک‌بار</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>هیسترزیس</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>۱۰۰mV</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>پایان اپیزود</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_HYSTERESIS_MV (۱۱۳)</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="71" t="inlineStr">
         <is>
           <t>ضد نوسان</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>آستانهٔ قفل</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>۱۰ رویداد</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن + بوق + وتو</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_MAX_EVENTS (۱۱۴)</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="71" t="inlineStr">
         <is>
           <t>شمارش ماندگار</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>بودجهٔ سیکل</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>۲۰ سیکل در قفل</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>مسدودی شارژ همان پک</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>IMBAL_PARAM_MAX_LATCHED_CYCLES (۱۱۸)</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <t>شارژ در قفل آزاد است</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>ریست تعویض</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>نبود باتری ۳ ثانیه</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>ریست شمارنده‌ها و قفل</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>IMBAL_ABSENT_RESET_MS</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="71" t="inlineStr">
         <is>
           <t>تعویض واقعی باتری</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>اسلات‌های ماندگار</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>۲۰۰ رویداد، ۲۰۱ سیکل، ۲۰۲ قفل</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>بقا پس از قطع برق</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>IMBAL_SLOT_*_ID</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="71" t="inlineStr">
         <is>
           <t>فقط پخش NVM</t>
         </is>
@@ -3607,160 +5163,172 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Imbalance</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
+      <c r="D1" s="53" t="n"/>
+      <c r="E1" s="53" t="n"/>
+      <c r="F1" s="53" t="n"/>
+      <c r="G1" s="53" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="53" t="n"/>
+      <c r="J1" s="53" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="53" t="n"/>
+      <c r="M1" s="53" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
-      <c r="K2" s="15" t="n"/>
-      <c r="L2" s="15" t="n"/>
-      <c r="M2" s="15" t="n"/>
+      <c r="B2" s="48" t="n"/>
+      <c r="C2" s="48" t="n"/>
+      <c r="D2" s="48" t="n"/>
+      <c r="E2" s="48" t="n"/>
+      <c r="F2" s="48" t="n"/>
+      <c r="G2" s="48" t="n"/>
+      <c r="H2" s="48" t="n"/>
+      <c r="I2" s="48" t="n"/>
+      <c r="J2" s="48" t="n"/>
+      <c r="K2" s="48" t="n"/>
+      <c r="L2" s="48" t="n"/>
+      <c r="M2" s="48" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="70" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="70" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="34" t="inlineStr">
+      <c r="F3" s="70" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="34" t="inlineStr">
+      <c r="G3" s="70" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="34" t="inlineStr">
+      <c r="H3" s="70" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="34" t="inlineStr">
+      <c r="I3" s="70" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="J3" s="70" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="34" t="inlineStr">
+      <c r="K3" s="70" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="34" t="inlineStr">
+      <c r="L3" s="70" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="34" t="inlineStr">
+      <c r="M3" s="70" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>DEF-IM-001</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="70" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="70" t="inlineStr">
         <is>
           <t>تنظیم‌های ذخیره‌شدهٔ سناریو ۵ با هر بار روشن‌شدن به پیش‌فرض کامپایل برمی‌گشت</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="70" t="inlineStr">
         <is>
           <t>یک پارامتر ۱۰۸..۱۱۸ را از پنل تغییر و ذخیره کن؛ تغذیه را قطع و وصل کن؛ همان پارامتر را بخوان</t>
         </is>
       </c>
-      <c r="G4" s="34" t="inlineStr">
+      <c r="G4" s="70" t="inlineStr">
         <is>
           <t>مقدار ذخیره‌شده باقی بماند</t>
         </is>
       </c>
-      <c r="H4" s="34" t="inlineStr">
+      <c r="H4" s="70" t="inlineStr">
         <is>
           <t>مقدار پیش‌فرض کامپایل خوانده می‌شد</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="73" t="inlineStr">
         <is>
           <t>تست هاست host_test_imbalance.c (بلوک رگرسیون v1.81)</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="J4" s="70" t="inlineStr">
         <is>
           <t>ممیزی ۲۰۲۶-۱۰-۰۶</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="73" t="inlineStr">
         <is>
           <t>func__Imbalance_Init() در imbalance.c کل جدول پارامتر را بی‌قید به پیش‌فرض برمی‌گرداند، در حالی که بازپخش NVM پیش از آن اجرا می‌شود</t>
         </is>
       </c>
-      <c r="L4" s="34" t="inlineStr">
+      <c r="L4" s="70" t="inlineStr">
         <is>
           <t>اصلاح شد</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="70" t="inlineStr">
         <is>
           <t>با func__Imbalance_SeedDefaultsOnce() پیش‌فرض‌ها فقط یک‌بار نوشته می‌شوند؛ تست هاست با ۵۰۴۱ بررسی و ۰ خطا قبول شد — تأیید نهایی منوط به تست روی برد</t>
         </is>
@@ -3793,209 +5361,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Imbalance</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="53" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Imbalance — سناریوی ۵ عدم‌توازن دو نیم‌باتری</t>
         </is>
       </c>
+      <c r="C5" s="53" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>2026-10-05 (1.0 — ساخته‌شده در ممیزی کل برنامه)</t>
         </is>
       </c>
+      <c r="C6" s="53" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="53" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="53" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + بار نامتقارن قابل تنظیم + کرنومتر</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="53" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="n"/>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="74" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="50">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="50">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="50">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="50">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="53" t="n"/>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4017,77 +5609,88 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="53" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="53" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="53" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="53" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="53" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="53" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="53" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="53" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="53" t="n"/>
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="53" t="n"/>
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="53" t="n"/>
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -4113,60 +5716,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول عدم‌توازن (سناریوی ۵)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="53" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Imbalance_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="53" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="53" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="53" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -194,6 +194,10 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -233,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -269,11 +273,12 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -472,6 +477,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -838,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -914,6 +922,14 @@
       <c r="A11" s="50" t="inlineStr">
         <is>
           <t>شمارنده‌ها در اسلات‌های ۲۰۰..۲۰۲ ماندگارند و با قطع برق پاک نمی‌شوند. تست Host جایگزین تست برد نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="76" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1087,7 @@
       </c>
       <c r="J4" s="48" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="48" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="J5" s="56" t="inlineStr">
         <is>
-          <t>شمرده‌شدن رویداد = قبول؛ نشمردن با اختلاف واضح = رد</t>
+          <t>باید ببینید: اختلاف دو باتری در استراحت در پنل دیده می‌شود و یک رویداد شمرده می‌شود. اگر با اختلاف واضح نشمرد، قبول نیست.</t>
         </is>
       </c>
       <c r="K5" s="56" t="inlineStr">
@@ -1189,127 +1205,126 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q5" s="60">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="55" t="inlineStr">
         <is>
-          <t>IM-002</t>
-        </is>
-      </c>
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>گیت زمانی پس از شارژ</t>
-        </is>
-      </c>
-      <c r="C6" s="62" t="inlineStr">
+          <t>IM-003</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>آستانهٔ دشارژ</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
-        <is>
-          <t>باتری‌ها تازه شارژشان تمام شده است</t>
-        </is>
-      </c>
-      <c r="E6" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: درست بعد از تمام‌شدن شارژ، یک باتری را کمی ضعیف کن (لامپ ۱۲ ولت).
-گام ۲: در همان دقایق اول پنل را چک کن.</t>
-        </is>
-      </c>
-      <c r="F6" s="63" t="inlineStr">
-        <is>
-          <t>اختلاف بلافاصله بعد از شارژ</t>
-        </is>
-      </c>
-      <c r="G6" s="63" t="inlineStr">
-        <is>
-          <t>ربع ساعت</t>
-        </is>
-      </c>
-      <c r="H6" s="61" t="inlineStr">
-        <is>
-          <t>درست بعد از شارژ رویداد حساب نمی‌شود؛ دستگاه اول فرصت استراحت و جاافتادن می‌دهد</t>
-        </is>
-      </c>
-      <c r="I6" s="61" t="inlineStr">
-        <is>
-          <t>بدون رویداد زودهنگام</t>
-        </is>
-      </c>
-      <c r="J6" s="61" t="inlineStr">
-        <is>
-          <t>حساب‌نشدن در فرصت اول = قبول؛ رویداد فوری بعد شارژ = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="61" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M6" s="61" t="n"/>
-      <c r="N6" s="61" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O6" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P6" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q6" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
-        <is>
-          <t>IM-003</t>
-        </is>
-      </c>
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>آستانهٔ دشارژ</t>
-        </is>
-      </c>
-      <c r="C7" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="56" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>دستگاه روی باتری دارد به یک بار واقعی کار می‌کند</t>
         </is>
       </c>
-      <c r="E7" s="56" t="inlineStr">
+      <c r="E6" s="56" t="inlineStr">
         <is>
           <t>گام ۱: حین کار، باتری‌ای که ضعیف‌تر است را زیر نظر بگیر (از اول یکی را کمی خالی‌تر وصل کن).
 گام ۲: بگذار دستگاه مدتی با بار کار کند.
 گام ۳: شمارندهٔ رویداد را در پنل چک کن.</t>
         </is>
       </c>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>دو باتری نابرابر زیر بار واقعی</t>
+        </is>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>نیم ساعت</t>
+        </is>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>اختلاف زیر بار هم دیده و رویداد شمرده می‌شود</t>
+        </is>
+      </c>
+      <c r="I6" s="56" t="inlineStr">
+        <is>
+          <t>رویداد در شمارنده می‌ماند</t>
+        </is>
+      </c>
+      <c r="J6" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: اختلاف زیر بار هم دیده و رویداد شمرده می‌شود. اگر فقط در استراحت شمرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="56" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="56" t="n"/>
+      <c r="N6" s="56" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O6" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q6" s="60">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>IM-007</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>قفل شدن</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>دو باتری نابرابر داری؛ برای زود دیدن نتیجه از پنل حدّ رویدادهای مجاز را موقتاً روی یک بگذار</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>گام ۱: یک رویداد عدم‌توازن بساز (مثل IM-001).
+گام ۲: وقتی قفل شد چراغ‌ها را ببین: فقط قرمز چشمک می‌زند، سبز و زرد خاموش‌اند.
+گام ۳: حدّ را از پنل به مقدار واقعی برگردان.</t>
+        </is>
+      </c>
       <c r="F7" s="58" t="inlineStr">
         <is>
-          <t>دو باتری نابرابر زیر بار واقعی</t>
+          <t>رویداد عدم‌توازن با حدّ موقتِ یک</t>
         </is>
       </c>
       <c r="G7" s="58" t="inlineStr">
@@ -1319,17 +1334,17 @@
       </c>
       <c r="H7" s="56" t="inlineStr">
         <is>
-          <t>اختلاف زیر بار هم دیده و رویداد شمرده می‌شود</t>
+          <t>قفل عدم‌توازن می‌نشیند: قرمز چشمک‌زنِ تنها، بدون سبز و زرد</t>
         </is>
       </c>
       <c r="I7" s="56" t="inlineStr">
         <is>
-          <t>رویداد در شمارنده می‌ماند</t>
+          <t>قفل تا تعویض باتری</t>
         </is>
       </c>
       <c r="J7" s="56" t="inlineStr">
         <is>
-          <t>شمرده‌شدن زیر بار = قبول؛ فقط در استراحت شمردن = رد</t>
+          <t>باید ببینید: قفل می‌نشیند؛ فقط قرمز چشمک می‌زند و سبز و زرد خاموش‌اند. اگر قفل نشد یا چهره اشتباه بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K7" s="56" t="inlineStr">
@@ -1358,518 +1373,510 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q7" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q7" s="60">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="55" t="inlineStr">
         <is>
+          <t>IM-010</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>وتوی خروجی</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>قفل عدم‌توازن فعال است و از پنل گزینهٔ «قطع خروجی هنگام قفل» روشن است؛ یک بار روی خروجی داری</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: برق شهر را بکش.
+گام ۲: بار را نگاه کن؛ نباید از این باتری روشن شود.
+گام ۳: برق شهر را برگردان.</t>
+        </is>
+      </c>
+      <c r="F8" s="63" t="inlineStr">
+        <is>
+          <t>قطع برق شهر در قفل با وتوی خروجی</t>
+        </is>
+      </c>
+      <c r="G8" s="63" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H8" s="61" t="inlineStr">
+        <is>
+          <t>باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود</t>
+        </is>
+      </c>
+      <c r="I8" s="61" t="inlineStr">
+        <is>
+          <t>وتو تا پاک‌شدن قفل</t>
+        </is>
+      </c>
+      <c r="J8" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود. اگر بار از باتری قفل‌شده روشن شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K8" s="61" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L8" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="61" t="n"/>
+      <c r="N8" s="61" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O8" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q8" s="64">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>IM-013</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>ریست با تعویض باتری</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>قفل عدم‌توازن فعال است و چراغ قرمز چشمک می‌زند</t>
+        </is>
+      </c>
+      <c r="E9" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: هر دو باتری را با دو باتری سالم و هم‌شارژ عوض کن.
+گام ۲: چند دقیقه صبر کن و چراغ‌ها را ببین.</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>تعویض واقعی هر دو باتری</t>
+        </is>
+      </c>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>ربع ساعت</t>
+        </is>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I9" s="56" t="inlineStr">
+        <is>
+          <t>پاک‌شدن خودکار با تعویض</t>
+        </is>
+      </c>
+      <c r="J9" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: با تعویض باتری قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد. اگر با باتری سالم قفل ماند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K9" s="56" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="56" t="n"/>
+      <c r="N9" s="56" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O9" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q9" s="60">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>IM-002</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>گیت زمانی پس از شارژ</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>باتری‌ها تازه شارژشان تمام شده است</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: درست بعد از تمام‌شدن شارژ، یک باتری را کمی ضعیف کن (لامپ ۱۲ ولت).
+گام ۲: در همان دقایق اول پنل را چک کن.</t>
+        </is>
+      </c>
+      <c r="F10" s="63" t="inlineStr">
+        <is>
+          <t>اختلاف بلافاصله بعد از شارژ</t>
+        </is>
+      </c>
+      <c r="G10" s="63" t="inlineStr">
+        <is>
+          <t>ربع ساعت</t>
+        </is>
+      </c>
+      <c r="H10" s="61" t="inlineStr">
+        <is>
+          <t>درست بعد از شارژ رویداد حساب نمی‌شود؛ دستگاه اول فرصت استراحت و جاافتادن می‌دهد</t>
+        </is>
+      </c>
+      <c r="I10" s="61" t="inlineStr">
+        <is>
+          <t>بدون رویداد زودهنگام</t>
+        </is>
+      </c>
+      <c r="J10" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: درست بعد از شارژ رویدادی حساب نمی‌شود و دستگاه اول فرصت استراحت می‌دهد. اگر فوری بعد از شارژ رویداد شمرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K10" s="61" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L10" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M10" s="61" t="n"/>
+      <c r="N10" s="61" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O10" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q10" s="64">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
           <t>IM-004</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>هیسترزیس پایان اپیزود</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>یک اپیزود عدم‌توازن در جریان است (اختلاف دو باتری نزدیک مرز تمام‌شدن)</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>گام ۱: اختلاف دو باتری را آرام کم کن (باتری ضعیف را کمی شارژ یا با سالم‌تر عوض کن).
 گام ۲: بعد کمی دوباره اختلاف بساز و کم کن.
 گام ۳: شمارنده و وضعیت اپیزود را در پنل نگاه کن.</t>
         </is>
       </c>
-      <c r="F8" s="63" t="inlineStr">
+      <c r="F11" s="63" t="inlineStr">
         <is>
           <t>کم و زیاد کردن آرام اختلاف دور مرز پایان</t>
         </is>
       </c>
-      <c r="G8" s="63" t="inlineStr">
+      <c r="G11" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H8" s="61" t="inlineStr">
+      <c r="H11" s="61" t="inlineStr">
         <is>
           <t>اپیزود با هر تغییر کوچک باز و بسته نمی‌شود؛ پایانش تمیز و یک‌باره است</t>
         </is>
       </c>
-      <c r="I8" s="61" t="inlineStr">
+      <c r="I11" s="61" t="inlineStr">
         <is>
           <t>پایان پایدار</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
-        <is>
-          <t>پایان تمیز = قبول؛ باز و بسته‌شدن تندتند = رد</t>
-        </is>
-      </c>
-      <c r="K8" s="61" t="inlineStr">
+      <c r="J11" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: اپیزود با هر تغییر کوچک باز و بسته نمی‌شود و پایانش تمیز و یک‌باره است. اگر تندتند باز و بسته شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K11" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="59" t="inlineStr">
+      <c r="L11" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="61" t="n"/>
-      <c r="N8" s="61" t="inlineStr">
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O8" s="63" t="inlineStr">
+      <c r="O11" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="63" t="inlineStr">
+      <c r="P11" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q8" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="55" t="inlineStr">
-        <is>
-          <t>IM-005</t>
-        </is>
-      </c>
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>نوسان دور حد</t>
-        </is>
-      </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="Q11" s="64">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>IM-006</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>ماندگاری شمارنده</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
-        <is>
-          <t>به‌جای یک باتری منبع آزمایشگاهی گذاشته‌ای تا ولتاژش را بازی بدهی</t>
-        </is>
-      </c>
-      <c r="E9" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ منبع را دور مرز اختلاف مجاز، کم‌کم بالا و پایین کن.
-گام ۲: شمارندهٔ رویداد را در پنل زیر نظر بگیر.</t>
-        </is>
-      </c>
-      <c r="F9" s="58" t="inlineStr">
-        <is>
-          <t>نوسان ولتاژ یک نیم دور مرز</t>
-        </is>
-      </c>
-      <c r="G9" s="58" t="inlineStr">
-        <is>
-          <t>ربع ساعت</t>
-        </is>
-      </c>
-      <c r="H9" s="56" t="inlineStr">
-        <is>
-          <t>با نوسان‌های کوچک شمارنده بالا نمی‌رود؛ فقط اختلاف واقعی و ماندگار شمرده می‌شود</t>
-        </is>
-      </c>
-      <c r="I9" s="56" t="inlineStr">
-        <is>
-          <t>بدون رویداد کاذب</t>
-        </is>
-      </c>
-      <c r="J9" s="56" t="inlineStr">
-        <is>
-          <t>ثابت‌ماندن شمارنده = قبول؛ شمردن با هر نوسان = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="56" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="56" t="n"/>
-      <c r="N9" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O9" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q9" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
-        <is>
-          <t>IM-006</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="inlineStr">
-        <is>
-          <t>ماندگاری شمارنده</t>
-        </is>
-      </c>
-      <c r="C10" s="62" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="65" t="inlineStr">
+      <c r="D12" s="65" t="inlineStr">
         <is>
           <t>چند رویداد عدم‌توازن را با IM-001 ساخته‌ای و شمرده شده‌اند</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E12" s="61" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: دوباره روشن کن و شمارنده را در پنل بخوان.</t>
         </is>
       </c>
-      <c r="F10" s="63" t="inlineStr">
+      <c r="F12" s="63" t="inlineStr">
         <is>
           <t>قطع و وصل کامل برق</t>
         </is>
       </c>
-      <c r="G10" s="63" t="inlineStr">
+      <c r="G12" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="61" t="inlineStr">
+      <c r="H12" s="61" t="inlineStr">
         <is>
           <t>شمارندهٔ رویدادها بعد از روشن‌شدن سر جایش هست و از صفر شروع نشده</t>
         </is>
       </c>
-      <c r="I10" s="61" t="inlineStr">
+      <c r="I12" s="61" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
-        <is>
-          <t>حفظ شمارنده = قبول؛ صفر شدن = رد</t>
-        </is>
-      </c>
-      <c r="K10" s="61" t="inlineStr">
+      <c r="J12" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: شمارندهٔ رویدادها بعد از خاموش و روشن‌کردن سر جایش است و از صفر شروع نشده. اگر صفر شده بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K12" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="59" t="inlineStr">
+      <c r="L12" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="61" t="n"/>
-      <c r="N10" s="61" t="inlineStr">
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O10" s="63" t="inlineStr">
+      <c r="O12" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="63" t="inlineStr">
+      <c r="P12" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q10" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>IM-007</t>
-        </is>
-      </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>قفل شدن</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D11" s="56" t="inlineStr">
-        <is>
-          <t>دو باتری نابرابر داری؛ برای زود دیدن نتیجه از پنل حدّ رویدادهای مجاز را موقتاً روی یک بگذار</t>
-        </is>
-      </c>
-      <c r="E11" s="66" t="inlineStr">
-        <is>
-          <t>گام ۱: یک رویداد عدم‌توازن بساز (مثل IM-001).
-گام ۲: وقتی قفل شد چراغ‌ها را ببین: فقط قرمز چشمک می‌زند، سبز و زرد خاموش‌اند.
-گام ۳: حدّ را از پنل به مقدار واقعی برگردان.</t>
-        </is>
-      </c>
-      <c r="F11" s="58" t="inlineStr">
-        <is>
-          <t>رویداد عدم‌توازن با حدّ موقتِ یک</t>
-        </is>
-      </c>
-      <c r="G11" s="58" t="inlineStr">
-        <is>
-          <t>نیم ساعت</t>
-        </is>
-      </c>
-      <c r="H11" s="56" t="inlineStr">
-        <is>
-          <t>قفل عدم‌توازن می‌نشیند: قرمز چشمک‌زنِ تنها، بدون سبز و زرد</t>
-        </is>
-      </c>
-      <c r="I11" s="56" t="inlineStr">
-        <is>
-          <t>قفل تا تعویض باتری</t>
-        </is>
-      </c>
-      <c r="J11" s="56" t="inlineStr">
-        <is>
-          <t>نشستن قفل با همان چهره = قبول؛ قفل‌نشدن یا چهرهٔ اشتباه = رد</t>
-        </is>
-      </c>
-      <c r="K11" s="56" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="56" t="n"/>
-      <c r="N11" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O11" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q11" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="Q12" s="64">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>IM-009</t>
         </is>
       </c>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>بوق ساعتی</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="66" t="inlineStr">
+      <c r="D13" s="66" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است (IM-007)؛ از پنل دورهٔ بوق قفل را موقتاً کوتاه کرده‌ای</t>
         </is>
       </c>
-      <c r="E12" s="56" t="inlineStr">
+      <c r="E13" s="56" t="inlineStr">
         <is>
           <t>گام ۱: با کرنومتر صبر کن تا وقت بوق برسد.
 گام ۲: به بوق و چراغ قرمز دقت کن.
 گام ۳: دورهٔ بوق را به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F12" s="58" t="inlineStr">
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>قفل فعال با دورهٔ بوق کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G12" s="58" t="inlineStr">
+      <c r="G13" s="58" t="inlineStr">
         <is>
           <t>چند دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="56" t="inlineStr">
+      <c r="H13" s="56" t="inlineStr">
         <is>
           <t>سر وقت، یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I12" s="56" t="inlineStr">
+      <c r="I13" s="56" t="inlineStr">
         <is>
           <t>بوق دوره‌ای در قفل</t>
         </is>
       </c>
-      <c r="J12" s="56" t="inlineStr">
-        <is>
-          <t>بوق سر وقت = قبول؛ بی‌بوقی یا بوق به‌هم‌ریخته = رد</t>
-        </is>
-      </c>
-      <c r="K12" s="56" t="inlineStr">
+      <c r="J13" s="56" t="inlineStr">
+        <is>
+          <t>باید بشنوید و ببینید: سر وقت یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند. اگر بوق نیامد یا به‌هم‌ریخته بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K13" s="56" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="59" t="inlineStr">
+      <c r="L13" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="56" t="n"/>
-      <c r="N12" s="56" t="inlineStr">
+      <c r="M13" s="56" t="n"/>
+      <c r="N13" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O12" s="58" t="inlineStr">
+      <c r="O13" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="58" t="inlineStr">
+      <c r="P13" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q12" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
-        <is>
-          <t>IM-010</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="inlineStr">
-        <is>
-          <t>وتوی خروجی</t>
-        </is>
-      </c>
-      <c r="C13" s="62" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D13" s="61" t="inlineStr">
-        <is>
-          <t>قفل عدم‌توازن فعال است و از پنل گزینهٔ «قطع خروجی هنگام قفل» روشن است؛ یک بار روی خروجی داری</t>
-        </is>
-      </c>
-      <c r="E13" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: برق شهر را بکش.
-گام ۲: بار را نگاه کن؛ نباید از این باتری روشن شود.
-گام ۳: برق شهر را برگردان.</t>
-        </is>
-      </c>
-      <c r="F13" s="63" t="inlineStr">
-        <is>
-          <t>قطع برق شهر در قفل با وتوی خروجی</t>
-        </is>
-      </c>
-      <c r="G13" s="63" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H13" s="61" t="inlineStr">
-        <is>
-          <t>باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود</t>
-        </is>
-      </c>
-      <c r="I13" s="61" t="inlineStr">
-        <is>
-          <t>وتو تا پاک‌شدن قفل</t>
-        </is>
-      </c>
-      <c r="J13" s="61" t="inlineStr">
-        <is>
-          <t>روشن‌نشدن بار از باتری قفل‌شده = قبول؛ آمدن باتری روی خروجی = رد</t>
-        </is>
-      </c>
-      <c r="K13" s="61" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L13" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="61" t="n"/>
-      <c r="N13" s="61" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O13" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q13" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q13" s="60">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
@@ -1921,7 +1928,7 @@
       </c>
       <c r="J14" s="56" t="inlineStr">
         <is>
-          <t>کارکردن خروجی با تیک خاموش = قبول؛ وتوی همیشگی = رد</t>
+          <t>باید ببینید: با برداشتن تیک، باتری روی خروجی می‌آید و بار کار می‌کند هرچند قفل هنوز هست. اگر وتو همیشگی ماند، قبول نیست.</t>
         </is>
       </c>
       <c r="K14" s="56" t="inlineStr">
@@ -1950,10 +1957,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q14" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q14" s="60">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
@@ -1969,7 +1975,7 @@
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D15" s="61" t="inlineStr">
@@ -2005,7 +2011,7 @@
       </c>
       <c r="J15" s="61" t="inlineStr">
         <is>
-          <t>توقف بعد از چرخه‌های مجاز = قبول؛ شارژ بی‌نهایت در قفل = رد</t>
+          <t>باید ببینید: بعد از تمام‌شدن چرخه‌های مجاز، شارژ آن باتری دیگر شروع نمی‌شود. اگر بی‌نهایت شارژ شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K15" s="61" t="inlineStr">
@@ -2034,384 +2040,383 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q15" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q15" s="64">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="55" t="inlineStr">
         <is>
-          <t>IM-013</t>
-        </is>
-      </c>
-      <c r="B16" s="56" t="inlineStr">
-        <is>
-          <t>ریست با تعویض باتری</t>
-        </is>
-      </c>
-      <c r="C16" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t>قفل عدم‌توازن فعال است و چراغ قرمز چشمک می‌زند</t>
-        </is>
-      </c>
-      <c r="E16" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: هر دو باتری را با دو باتری سالم و هم‌شارژ عوض کن.
-گام ۲: چند دقیقه صبر کن و چراغ‌ها را ببین.</t>
-        </is>
-      </c>
-      <c r="F16" s="58" t="inlineStr">
-        <is>
-          <t>تعویض واقعی هر دو باتری</t>
-        </is>
-      </c>
-      <c r="G16" s="58" t="inlineStr">
-        <is>
-          <t>ربع ساعت</t>
-        </is>
-      </c>
-      <c r="H16" s="56" t="inlineStr">
-        <is>
-          <t>قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد</t>
-        </is>
-      </c>
-      <c r="I16" s="56" t="inlineStr">
-        <is>
-          <t>پاک‌شدن خودکار با تعویض</t>
-        </is>
-      </c>
-      <c r="J16" s="56" t="inlineStr">
-        <is>
-          <t>پاک‌شدن خودکار = قبول؛ ماندن قفل با باتری سالم = رد</t>
-        </is>
-      </c>
-      <c r="K16" s="56" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L16" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="56" t="n"/>
-      <c r="N16" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="55" t="inlineStr">
-        <is>
           <t>IM-014</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>جدا شدن کوتاه</t>
         </is>
       </c>
-      <c r="C17" s="63" t="inlineStr">
+      <c r="C16" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr">
+      <c r="D16" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است</t>
         </is>
       </c>
-      <c r="E17" s="65" t="inlineStr">
+      <c r="E16" s="65" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌ها را فقط چند ثانیه جدا کن و سریع وصل کن.
 گام ۲: چراغ‌ها را ببین؛ قفل باید سر جایش باشد.
 گام ۳: حالا تعویض واقعی (IM-013) انجام بده و تفاوت را ببین.</t>
         </is>
       </c>
-      <c r="F17" s="63" t="inlineStr">
+      <c r="F16" s="63" t="inlineStr">
         <is>
           <t>جدا کردن کوتاه در برابر تعویض واقعی</t>
         </is>
       </c>
-      <c r="G17" s="63" t="inlineStr">
+      <c r="G16" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H17" s="61" t="inlineStr">
+      <c r="H16" s="61" t="inlineStr">
         <is>
           <t>قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند</t>
         </is>
       </c>
-      <c r="I17" s="61" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>قفل در برابر قطع کوتاه مقاوم</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
-        <is>
-          <t>ماندن قفل بعد قطع کوتاه = قبول؛ پاک‌شدن با قطع کوتاه = رد</t>
-        </is>
-      </c>
-      <c r="K17" s="61" t="inlineStr">
+      <c r="J16" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند. اگر با قطع کوتاه پاک شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K16" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="59" t="inlineStr">
+      <c r="L16" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="61" t="n"/>
-      <c r="N17" s="61" t="inlineStr">
+      <c r="M16" s="61" t="n"/>
+      <c r="N16" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O17" s="63" t="inlineStr">
+      <c r="O16" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P17" s="63" t="inlineStr">
+      <c r="P16" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q17" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="55" t="inlineStr">
-        <is>
-          <t>IM-015</t>
-        </is>
-      </c>
-      <c r="B18" s="56" t="inlineStr">
-        <is>
-          <t>بازهٔ پارامترها</t>
-        </is>
-      </c>
-      <c r="C18" s="58" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D18" s="56" t="inlineStr">
-        <is>
-          <t>پنل باز است و تنظیم‌های عدم‌توازن را می‌بینی</t>
-        </is>
-      </c>
-      <c r="E18" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل یک حدّ ناممکن بفرست (مثلاً اختلاف مجاز خیلی بزرگ یا منفیِ معادل).
-گام ۲: مقدار ذخیره‌شده را دوباره از پنل بخوان.</t>
-        </is>
-      </c>
-      <c r="F18" s="58" t="inlineStr">
-        <is>
-          <t>فرستادن مقدار بیرون بازه از پنل</t>
-        </is>
-      </c>
-      <c r="G18" s="58" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H18" s="56" t="inlineStr">
-        <is>
-          <t>دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند</t>
-        </is>
-      </c>
-      <c r="I18" s="56" t="inlineStr">
-        <is>
-          <t>حفظ مقدار قبلی</t>
-        </is>
-      </c>
-      <c r="J18" s="56" t="inlineStr">
-        <is>
-          <t>رد شدن مقدار خراب = قبول؛ ذخیره‌شدن مقدار ناممکن = رد</t>
-        </is>
-      </c>
-      <c r="K18" s="56" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L18" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M18" s="56" t="n"/>
-      <c r="N18" s="56" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O18" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P18" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q18" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="Q16" s="64">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>IM-016</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>ماندگاری تنظیم‌ها پس از قطع برق</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>پنل باز است</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E17" s="61" t="inlineStr">
         <is>
           <t>گام ۱: یک تنظیم عدم‌توازن را از پنل عوض کن (مثلاً اختلاف مجاز).
 گام ۲: برق دستگاه را کامل قطع و دوباره وصل کن.
 گام ۳: تنظیم را از پنل دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F19" s="63" t="inlineStr">
+      <c r="F17" s="63" t="inlineStr">
         <is>
           <t>تغییر تنظیم و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G19" s="63" t="inlineStr">
+      <c r="G17" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="61" t="inlineStr">
+      <c r="H17" s="61" t="inlineStr">
         <is>
           <t>همان تنظیم تازه بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
-      <c r="I19" s="61" t="inlineStr">
+      <c r="I17" s="61" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
-        <is>
-          <t>حفظ تنظیم = قبول؛ برگشت به مقدار قبلی = رد</t>
-        </is>
-      </c>
-      <c r="K19" s="61" t="inlineStr">
+      <c r="J17" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: همان تنظیم تازه بعد از خاموش و روشن‌کردن سر جاست. اگر به مقدار قبلی برگشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K17" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="L17" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="65" t="inlineStr">
+        <is>
+          <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
+        </is>
+      </c>
+      <c r="N17" s="61" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O17" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P17" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q17" s="64">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>IM-017</t>
+        </is>
+      </c>
+      <c r="B18" s="56" t="inlineStr">
+        <is>
+          <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
+        </is>
+      </c>
+      <c r="C18" s="57" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t>قفل عدم‌توازن فعال و شمارنده چند رویداد دارد</t>
+        </is>
+      </c>
+      <c r="E18" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
+گام ۲: روشن کن و چراغ‌ها و شمارنده را چک کن.</t>
+        </is>
+      </c>
+      <c r="F18" s="58" t="inlineStr">
+        <is>
+          <t>قطع و وصل برق در قفل</t>
+        </is>
+      </c>
+      <c r="G18" s="58" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H18" s="56" t="inlineStr">
+        <is>
+          <t>قفل و شمارنده بعد از روشن‌شدن دقیقاً سر جایشان‌اند</t>
+        </is>
+      </c>
+      <c r="I18" s="56" t="inlineStr">
+        <is>
+          <t>ماندگار در قطع برق</t>
+        </is>
+      </c>
+      <c r="J18" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: قفل و شمارنده بعد از خاموش و روشن‌کردن دقیقاً سر جایشان‌اند. اگر با قطع برق پاک شدند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K18" s="56" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L18" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="56" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A5</t>
+        </is>
+      </c>
+      <c r="N18" s="56" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O18" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P18" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q18" s="60">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>IM-005</t>
+        </is>
+      </c>
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>نوسان دور حد</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>به‌جای یک باتری منبع آزمایشگاهی گذاشته‌ای تا ولتاژش را بازی بدهی</t>
+        </is>
+      </c>
+      <c r="E19" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را دور مرز اختلاف مجاز، کم‌کم بالا و پایین کن.
+گام ۲: شمارندهٔ رویداد را در پنل زیر نظر بگیر.</t>
+        </is>
+      </c>
+      <c r="F19" s="58" t="inlineStr">
+        <is>
+          <t>نوسان ولتاژ یک نیم دور مرز</t>
+        </is>
+      </c>
+      <c r="G19" s="58" t="inlineStr">
+        <is>
+          <t>ربع ساعت</t>
+        </is>
+      </c>
+      <c r="H19" s="56" t="inlineStr">
+        <is>
+          <t>با نوسان‌های کوچک شمارنده بالا نمی‌رود؛ فقط اختلاف واقعی و ماندگار شمرده می‌شود</t>
+        </is>
+      </c>
+      <c r="I19" s="56" t="inlineStr">
+        <is>
+          <t>بدون رویداد کاذب</t>
+        </is>
+      </c>
+      <c r="J19" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: با نوسان‌های کوچک شمارنده بالا نمی‌رود و فقط اختلاف واقعی و ماندگار شمرده می‌شود. اگر با هر نوسان شمرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K19" s="56" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
       <c r="L19" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="65" t="inlineStr">
-        <is>
-          <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
-        </is>
-      </c>
-      <c r="N19" s="61" t="inlineStr">
+      <c r="M19" s="56" t="n"/>
+      <c r="N19" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O19" s="63" t="inlineStr">
+      <c r="O19" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P19" s="63" t="inlineStr">
+      <c r="P19" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q19" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
+      <c r="Q19" s="60">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="55" t="inlineStr">
         <is>
-          <t>IM-017</t>
+          <t>IM-015</t>
         </is>
       </c>
       <c r="B20" s="56" t="inlineStr">
         <is>
-          <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
-        </is>
-      </c>
-      <c r="C20" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>بازهٔ پارامترها</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>پایین</t>
         </is>
       </c>
       <c r="D20" s="56" t="inlineStr">
         <is>
-          <t>قفل عدم‌توازن فعال و شمارنده چند رویداد دارد</t>
+          <t>پنل باز است و تنظیم‌های عدم‌توازن را می‌بینی</t>
         </is>
       </c>
       <c r="E20" s="56" t="inlineStr">
         <is>
-          <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
-گام ۲: روشن کن و چراغ‌ها و شمارنده را چک کن.</t>
+          <t>گام ۱: از پنل یک حدّ ناممکن بفرست (مثلاً اختلاف مجاز خیلی بزرگ یا منفیِ معادل).
+گام ۲: مقدار ذخیره‌شده را دوباره از پنل بخوان.</t>
         </is>
       </c>
       <c r="F20" s="58" t="inlineStr">
         <is>
-          <t>قطع و وصل برق در قفل</t>
+          <t>فرستادن مقدار بیرون بازه از پنل</t>
         </is>
       </c>
       <c r="G20" s="58" t="inlineStr">
@@ -2421,17 +2426,17 @@
       </c>
       <c r="H20" s="56" t="inlineStr">
         <is>
-          <t>قفل و شمارنده بعد از روشن‌شدن دقیقاً سر جایشان‌اند</t>
+          <t>دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند</t>
         </is>
       </c>
       <c r="I20" s="56" t="inlineStr">
         <is>
-          <t>ماندگار در قطع برق</t>
+          <t>حفظ مقدار قبلی</t>
         </is>
       </c>
       <c r="J20" s="56" t="inlineStr">
         <is>
-          <t>حفظ هر دو = قبول؛ پاک‌شدن با قطع برق = رد</t>
+          <t>باید ببینید: دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند. اگر مقدار ناممکن ذخیره شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K20" s="56" t="inlineStr">
@@ -2444,11 +2449,7 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="56" t="inlineStr">
-        <is>
-          <t>'برنامه تست'!A5</t>
-        </is>
-      </c>
+      <c r="M20" s="56" t="n"/>
       <c r="N20" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
@@ -2464,908 +2465,787 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q20" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="53" t="n"/>
-      <c r="B21" s="53" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
-      <c r="E21" s="53" t="n"/>
-      <c r="F21" s="53" t="n"/>
-      <c r="G21" s="53" t="n"/>
-      <c r="H21" s="53" t="n"/>
-      <c r="I21" s="53" t="n"/>
-      <c r="J21" s="53" t="n"/>
-      <c r="K21" s="53" t="n"/>
-      <c r="L21" s="53" t="n"/>
-      <c r="M21" s="53" t="n"/>
-      <c r="N21" s="53" t="n"/>
-      <c r="O21" s="53" t="n"/>
-      <c r="P21" s="53" t="n"/>
-      <c r="Q21" s="67">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="53" t="n"/>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53" t="n"/>
-      <c r="G22" s="53" t="n"/>
-      <c r="H22" s="53" t="n"/>
-      <c r="I22" s="53" t="n"/>
-      <c r="J22" s="53" t="n"/>
-      <c r="K22" s="53" t="n"/>
-      <c r="L22" s="53" t="n"/>
-      <c r="M22" s="53" t="n"/>
-      <c r="N22" s="53" t="n"/>
-      <c r="O22" s="53" t="n"/>
-      <c r="P22" s="53" t="n"/>
-      <c r="Q22" s="67">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
+      <c r="Q20" s="60">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="77" t="n"/>
+      <c r="B21" s="77" t="n"/>
+      <c r="C21" s="77" t="n"/>
+      <c r="D21" s="77" t="n"/>
+      <c r="E21" s="77" t="n"/>
+      <c r="F21" s="77" t="n"/>
+      <c r="G21" s="77" t="n"/>
+      <c r="H21" s="77" t="n"/>
+      <c r="I21" s="77" t="n"/>
+      <c r="J21" s="77" t="n"/>
+      <c r="K21" s="77" t="n"/>
+      <c r="L21" s="77" t="n"/>
+      <c r="M21" s="77" t="n"/>
+      <c r="N21" s="77" t="n"/>
+      <c r="O21" s="77" t="n"/>
+      <c r="P21" s="77" t="n"/>
+      <c r="Q21" s="78" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="77" t="n"/>
+      <c r="B22" s="77" t="n"/>
+      <c r="C22" s="77" t="n"/>
+      <c r="D22" s="77" t="n"/>
+      <c r="E22" s="77" t="n"/>
+      <c r="F22" s="77" t="n"/>
+      <c r="G22" s="77" t="n"/>
+      <c r="H22" s="77" t="n"/>
+      <c r="I22" s="77" t="n"/>
+      <c r="J22" s="77" t="n"/>
+      <c r="K22" s="77" t="n"/>
+      <c r="L22" s="77" t="n"/>
+      <c r="M22" s="77" t="n"/>
+      <c r="N22" s="77" t="n"/>
+      <c r="O22" s="77" t="n"/>
+      <c r="P22" s="77" t="n"/>
+      <c r="Q22" s="78" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="n"/>
-      <c r="B23" s="53" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
-      <c r="E23" s="53" t="n"/>
-      <c r="F23" s="53" t="n"/>
-      <c r="G23" s="53" t="n"/>
-      <c r="H23" s="53" t="n"/>
-      <c r="I23" s="53" t="n"/>
-      <c r="J23" s="53" t="n"/>
-      <c r="K23" s="53" t="n"/>
-      <c r="L23" s="53" t="n"/>
-      <c r="M23" s="53" t="n"/>
-      <c r="N23" s="53" t="n"/>
-      <c r="O23" s="53" t="n"/>
-      <c r="P23" s="53" t="n"/>
-      <c r="Q23" s="67">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="A23" s="77" t="n"/>
+      <c r="B23" s="77" t="n"/>
+      <c r="C23" s="77" t="n"/>
+      <c r="D23" s="77" t="n"/>
+      <c r="E23" s="77" t="n"/>
+      <c r="F23" s="77" t="n"/>
+      <c r="G23" s="77" t="n"/>
+      <c r="H23" s="77" t="n"/>
+      <c r="I23" s="77" t="n"/>
+      <c r="J23" s="77" t="n"/>
+      <c r="K23" s="77" t="n"/>
+      <c r="L23" s="77" t="n"/>
+      <c r="M23" s="77" t="n"/>
+      <c r="N23" s="77" t="n"/>
+      <c r="O23" s="77" t="n"/>
+      <c r="P23" s="77" t="n"/>
+      <c r="Q23" s="78" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="n"/>
-      <c r="B24" s="53" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
-      <c r="G24" s="53" t="n"/>
-      <c r="H24" s="53" t="n"/>
-      <c r="I24" s="53" t="n"/>
-      <c r="J24" s="53" t="n"/>
-      <c r="K24" s="53" t="n"/>
-      <c r="L24" s="53" t="n"/>
-      <c r="M24" s="53" t="n"/>
-      <c r="N24" s="53" t="n"/>
-      <c r="O24" s="53" t="n"/>
-      <c r="P24" s="53" t="n"/>
-      <c r="Q24" s="67">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="A24" s="77" t="n"/>
+      <c r="B24" s="77" t="n"/>
+      <c r="C24" s="77" t="n"/>
+      <c r="D24" s="77" t="n"/>
+      <c r="E24" s="77" t="n"/>
+      <c r="F24" s="77" t="n"/>
+      <c r="G24" s="77" t="n"/>
+      <c r="H24" s="77" t="n"/>
+      <c r="I24" s="77" t="n"/>
+      <c r="J24" s="77" t="n"/>
+      <c r="K24" s="77" t="n"/>
+      <c r="L24" s="77" t="n"/>
+      <c r="M24" s="77" t="n"/>
+      <c r="N24" s="77" t="n"/>
+      <c r="O24" s="77" t="n"/>
+      <c r="P24" s="77" t="n"/>
+      <c r="Q24" s="78" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="n"/>
-      <c r="B25" s="53" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
-      <c r="E25" s="53" t="n"/>
-      <c r="F25" s="53" t="n"/>
-      <c r="G25" s="53" t="n"/>
-      <c r="H25" s="53" t="n"/>
-      <c r="I25" s="53" t="n"/>
-      <c r="J25" s="53" t="n"/>
-      <c r="K25" s="53" t="n"/>
-      <c r="L25" s="53" t="n"/>
-      <c r="M25" s="53" t="n"/>
-      <c r="N25" s="53" t="n"/>
-      <c r="O25" s="53" t="n"/>
-      <c r="P25" s="53" t="n"/>
-      <c r="Q25" s="67">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A25" s="77" t="n"/>
+      <c r="B25" s="77" t="n"/>
+      <c r="C25" s="77" t="n"/>
+      <c r="D25" s="77" t="n"/>
+      <c r="E25" s="77" t="n"/>
+      <c r="F25" s="77" t="n"/>
+      <c r="G25" s="77" t="n"/>
+      <c r="H25" s="77" t="n"/>
+      <c r="I25" s="77" t="n"/>
+      <c r="J25" s="77" t="n"/>
+      <c r="K25" s="77" t="n"/>
+      <c r="L25" s="77" t="n"/>
+      <c r="M25" s="77" t="n"/>
+      <c r="N25" s="77" t="n"/>
+      <c r="O25" s="77" t="n"/>
+      <c r="P25" s="77" t="n"/>
+      <c r="Q25" s="78" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="n"/>
-      <c r="B26" s="53" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
-      <c r="E26" s="53" t="n"/>
-      <c r="F26" s="53" t="n"/>
-      <c r="G26" s="53" t="n"/>
-      <c r="H26" s="53" t="n"/>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="53" t="n"/>
-      <c r="K26" s="53" t="n"/>
-      <c r="L26" s="53" t="n"/>
-      <c r="M26" s="53" t="n"/>
-      <c r="N26" s="53" t="n"/>
-      <c r="O26" s="53" t="n"/>
-      <c r="P26" s="53" t="n"/>
-      <c r="Q26" s="67">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A26" s="77" t="n"/>
+      <c r="B26" s="77" t="n"/>
+      <c r="C26" s="77" t="n"/>
+      <c r="D26" s="77" t="n"/>
+      <c r="E26" s="77" t="n"/>
+      <c r="F26" s="77" t="n"/>
+      <c r="G26" s="77" t="n"/>
+      <c r="H26" s="77" t="n"/>
+      <c r="I26" s="77" t="n"/>
+      <c r="J26" s="77" t="n"/>
+      <c r="K26" s="77" t="n"/>
+      <c r="L26" s="77" t="n"/>
+      <c r="M26" s="77" t="n"/>
+      <c r="N26" s="77" t="n"/>
+      <c r="O26" s="77" t="n"/>
+      <c r="P26" s="77" t="n"/>
+      <c r="Q26" s="78" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="n"/>
-      <c r="B27" s="53" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
-      <c r="E27" s="53" t="n"/>
-      <c r="F27" s="53" t="n"/>
-      <c r="G27" s="53" t="n"/>
-      <c r="H27" s="53" t="n"/>
-      <c r="I27" s="53" t="n"/>
-      <c r="J27" s="53" t="n"/>
-      <c r="K27" s="53" t="n"/>
-      <c r="L27" s="53" t="n"/>
-      <c r="M27" s="53" t="n"/>
-      <c r="N27" s="53" t="n"/>
-      <c r="O27" s="53" t="n"/>
-      <c r="P27" s="53" t="n"/>
-      <c r="Q27" s="67">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A27" s="77" t="n"/>
+      <c r="B27" s="77" t="n"/>
+      <c r="C27" s="77" t="n"/>
+      <c r="D27" s="77" t="n"/>
+      <c r="E27" s="77" t="n"/>
+      <c r="F27" s="77" t="n"/>
+      <c r="G27" s="77" t="n"/>
+      <c r="H27" s="77" t="n"/>
+      <c r="I27" s="77" t="n"/>
+      <c r="J27" s="77" t="n"/>
+      <c r="K27" s="77" t="n"/>
+      <c r="L27" s="77" t="n"/>
+      <c r="M27" s="77" t="n"/>
+      <c r="N27" s="77" t="n"/>
+      <c r="O27" s="77" t="n"/>
+      <c r="P27" s="77" t="n"/>
+      <c r="Q27" s="78" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="n"/>
-      <c r="B28" s="53" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
-      <c r="E28" s="53" t="n"/>
-      <c r="F28" s="53" t="n"/>
-      <c r="G28" s="53" t="n"/>
-      <c r="H28" s="53" t="n"/>
-      <c r="I28" s="53" t="n"/>
-      <c r="J28" s="53" t="n"/>
-      <c r="K28" s="53" t="n"/>
-      <c r="L28" s="53" t="n"/>
-      <c r="M28" s="53" t="n"/>
-      <c r="N28" s="53" t="n"/>
-      <c r="O28" s="53" t="n"/>
-      <c r="P28" s="53" t="n"/>
-      <c r="Q28" s="67">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A28" s="77" t="n"/>
+      <c r="B28" s="77" t="n"/>
+      <c r="C28" s="77" t="n"/>
+      <c r="D28" s="77" t="n"/>
+      <c r="E28" s="77" t="n"/>
+      <c r="F28" s="77" t="n"/>
+      <c r="G28" s="77" t="n"/>
+      <c r="H28" s="77" t="n"/>
+      <c r="I28" s="77" t="n"/>
+      <c r="J28" s="77" t="n"/>
+      <c r="K28" s="77" t="n"/>
+      <c r="L28" s="77" t="n"/>
+      <c r="M28" s="77" t="n"/>
+      <c r="N28" s="77" t="n"/>
+      <c r="O28" s="77" t="n"/>
+      <c r="P28" s="77" t="n"/>
+      <c r="Q28" s="78" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="n"/>
-      <c r="B29" s="53" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
-      <c r="E29" s="53" t="n"/>
-      <c r="F29" s="53" t="n"/>
-      <c r="G29" s="53" t="n"/>
-      <c r="H29" s="53" t="n"/>
-      <c r="I29" s="53" t="n"/>
-      <c r="J29" s="53" t="n"/>
-      <c r="K29" s="53" t="n"/>
-      <c r="L29" s="53" t="n"/>
-      <c r="M29" s="53" t="n"/>
-      <c r="N29" s="53" t="n"/>
-      <c r="O29" s="53" t="n"/>
-      <c r="P29" s="53" t="n"/>
-      <c r="Q29" s="67">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A29" s="77" t="n"/>
+      <c r="B29" s="77" t="n"/>
+      <c r="C29" s="77" t="n"/>
+      <c r="D29" s="77" t="n"/>
+      <c r="E29" s="77" t="n"/>
+      <c r="F29" s="77" t="n"/>
+      <c r="G29" s="77" t="n"/>
+      <c r="H29" s="77" t="n"/>
+      <c r="I29" s="77" t="n"/>
+      <c r="J29" s="77" t="n"/>
+      <c r="K29" s="77" t="n"/>
+      <c r="L29" s="77" t="n"/>
+      <c r="M29" s="77" t="n"/>
+      <c r="N29" s="77" t="n"/>
+      <c r="O29" s="77" t="n"/>
+      <c r="P29" s="77" t="n"/>
+      <c r="Q29" s="78" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="n"/>
-      <c r="B30" s="53" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
-      <c r="E30" s="53" t="n"/>
-      <c r="F30" s="53" t="n"/>
-      <c r="G30" s="53" t="n"/>
-      <c r="H30" s="53" t="n"/>
-      <c r="I30" s="53" t="n"/>
-      <c r="J30" s="53" t="n"/>
-      <c r="K30" s="53" t="n"/>
-      <c r="L30" s="53" t="n"/>
-      <c r="M30" s="53" t="n"/>
-      <c r="N30" s="53" t="n"/>
-      <c r="O30" s="53" t="n"/>
-      <c r="P30" s="53" t="n"/>
-      <c r="Q30" s="67">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A30" s="77" t="n"/>
+      <c r="B30" s="77" t="n"/>
+      <c r="C30" s="77" t="n"/>
+      <c r="D30" s="77" t="n"/>
+      <c r="E30" s="77" t="n"/>
+      <c r="F30" s="77" t="n"/>
+      <c r="G30" s="77" t="n"/>
+      <c r="H30" s="77" t="n"/>
+      <c r="I30" s="77" t="n"/>
+      <c r="J30" s="77" t="n"/>
+      <c r="K30" s="77" t="n"/>
+      <c r="L30" s="77" t="n"/>
+      <c r="M30" s="77" t="n"/>
+      <c r="N30" s="77" t="n"/>
+      <c r="O30" s="77" t="n"/>
+      <c r="P30" s="77" t="n"/>
+      <c r="Q30" s="78" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="n"/>
-      <c r="B31" s="53" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
-      <c r="E31" s="53" t="n"/>
-      <c r="F31" s="53" t="n"/>
-      <c r="G31" s="53" t="n"/>
-      <c r="H31" s="53" t="n"/>
-      <c r="I31" s="53" t="n"/>
-      <c r="J31" s="53" t="n"/>
-      <c r="K31" s="53" t="n"/>
-      <c r="L31" s="53" t="n"/>
-      <c r="M31" s="53" t="n"/>
-      <c r="N31" s="53" t="n"/>
-      <c r="O31" s="53" t="n"/>
-      <c r="P31" s="53" t="n"/>
-      <c r="Q31" s="67">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A31" s="77" t="n"/>
+      <c r="B31" s="77" t="n"/>
+      <c r="C31" s="77" t="n"/>
+      <c r="D31" s="77" t="n"/>
+      <c r="E31" s="77" t="n"/>
+      <c r="F31" s="77" t="n"/>
+      <c r="G31" s="77" t="n"/>
+      <c r="H31" s="77" t="n"/>
+      <c r="I31" s="77" t="n"/>
+      <c r="J31" s="77" t="n"/>
+      <c r="K31" s="77" t="n"/>
+      <c r="L31" s="77" t="n"/>
+      <c r="M31" s="77" t="n"/>
+      <c r="N31" s="77" t="n"/>
+      <c r="O31" s="77" t="n"/>
+      <c r="P31" s="77" t="n"/>
+      <c r="Q31" s="78" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="n"/>
-      <c r="B32" s="53" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
-      <c r="E32" s="53" t="n"/>
-      <c r="F32" s="53" t="n"/>
-      <c r="G32" s="53" t="n"/>
-      <c r="H32" s="53" t="n"/>
-      <c r="I32" s="53" t="n"/>
-      <c r="J32" s="53" t="n"/>
-      <c r="K32" s="53" t="n"/>
-      <c r="L32" s="53" t="n"/>
-      <c r="M32" s="53" t="n"/>
-      <c r="N32" s="53" t="n"/>
-      <c r="O32" s="53" t="n"/>
-      <c r="P32" s="53" t="n"/>
-      <c r="Q32" s="67">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A32" s="77" t="n"/>
+      <c r="B32" s="77" t="n"/>
+      <c r="C32" s="77" t="n"/>
+      <c r="D32" s="77" t="n"/>
+      <c r="E32" s="77" t="n"/>
+      <c r="F32" s="77" t="n"/>
+      <c r="G32" s="77" t="n"/>
+      <c r="H32" s="77" t="n"/>
+      <c r="I32" s="77" t="n"/>
+      <c r="J32" s="77" t="n"/>
+      <c r="K32" s="77" t="n"/>
+      <c r="L32" s="77" t="n"/>
+      <c r="M32" s="77" t="n"/>
+      <c r="N32" s="77" t="n"/>
+      <c r="O32" s="77" t="n"/>
+      <c r="P32" s="77" t="n"/>
+      <c r="Q32" s="78" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="n"/>
-      <c r="B33" s="53" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
-      <c r="E33" s="53" t="n"/>
-      <c r="F33" s="53" t="n"/>
-      <c r="G33" s="53" t="n"/>
-      <c r="H33" s="53" t="n"/>
-      <c r="I33" s="53" t="n"/>
-      <c r="J33" s="53" t="n"/>
-      <c r="K33" s="53" t="n"/>
-      <c r="L33" s="53" t="n"/>
-      <c r="M33" s="53" t="n"/>
-      <c r="N33" s="53" t="n"/>
-      <c r="O33" s="53" t="n"/>
-      <c r="P33" s="53" t="n"/>
-      <c r="Q33" s="67">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A33" s="77" t="n"/>
+      <c r="B33" s="77" t="n"/>
+      <c r="C33" s="77" t="n"/>
+      <c r="D33" s="77" t="n"/>
+      <c r="E33" s="77" t="n"/>
+      <c r="F33" s="77" t="n"/>
+      <c r="G33" s="77" t="n"/>
+      <c r="H33" s="77" t="n"/>
+      <c r="I33" s="77" t="n"/>
+      <c r="J33" s="77" t="n"/>
+      <c r="K33" s="77" t="n"/>
+      <c r="L33" s="77" t="n"/>
+      <c r="M33" s="77" t="n"/>
+      <c r="N33" s="77" t="n"/>
+      <c r="O33" s="77" t="n"/>
+      <c r="P33" s="77" t="n"/>
+      <c r="Q33" s="78" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="n"/>
-      <c r="B34" s="53" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
-      <c r="E34" s="53" t="n"/>
-      <c r="F34" s="53" t="n"/>
-      <c r="G34" s="53" t="n"/>
-      <c r="H34" s="53" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="53" t="n"/>
-      <c r="K34" s="53" t="n"/>
-      <c r="L34" s="53" t="n"/>
-      <c r="M34" s="53" t="n"/>
-      <c r="N34" s="53" t="n"/>
-      <c r="O34" s="53" t="n"/>
-      <c r="P34" s="53" t="n"/>
-      <c r="Q34" s="67">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A34" s="77" t="n"/>
+      <c r="B34" s="77" t="n"/>
+      <c r="C34" s="77" t="n"/>
+      <c r="D34" s="77" t="n"/>
+      <c r="E34" s="77" t="n"/>
+      <c r="F34" s="77" t="n"/>
+      <c r="G34" s="77" t="n"/>
+      <c r="H34" s="77" t="n"/>
+      <c r="I34" s="77" t="n"/>
+      <c r="J34" s="77" t="n"/>
+      <c r="K34" s="77" t="n"/>
+      <c r="L34" s="77" t="n"/>
+      <c r="M34" s="77" t="n"/>
+      <c r="N34" s="77" t="n"/>
+      <c r="O34" s="77" t="n"/>
+      <c r="P34" s="77" t="n"/>
+      <c r="Q34" s="78" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="n"/>
-      <c r="B35" s="53" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
-      <c r="E35" s="53" t="n"/>
-      <c r="F35" s="53" t="n"/>
-      <c r="G35" s="53" t="n"/>
-      <c r="H35" s="53" t="n"/>
-      <c r="I35" s="53" t="n"/>
-      <c r="J35" s="53" t="n"/>
-      <c r="K35" s="53" t="n"/>
-      <c r="L35" s="53" t="n"/>
-      <c r="M35" s="53" t="n"/>
-      <c r="N35" s="53" t="n"/>
-      <c r="O35" s="53" t="n"/>
-      <c r="P35" s="53" t="n"/>
-      <c r="Q35" s="67">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A35" s="77" t="n"/>
+      <c r="B35" s="77" t="n"/>
+      <c r="C35" s="77" t="n"/>
+      <c r="D35" s="77" t="n"/>
+      <c r="E35" s="77" t="n"/>
+      <c r="F35" s="77" t="n"/>
+      <c r="G35" s="77" t="n"/>
+      <c r="H35" s="77" t="n"/>
+      <c r="I35" s="77" t="n"/>
+      <c r="J35" s="77" t="n"/>
+      <c r="K35" s="77" t="n"/>
+      <c r="L35" s="77" t="n"/>
+      <c r="M35" s="77" t="n"/>
+      <c r="N35" s="77" t="n"/>
+      <c r="O35" s="77" t="n"/>
+      <c r="P35" s="77" t="n"/>
+      <c r="Q35" s="78" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="n"/>
-      <c r="B36" s="53" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
-      <c r="G36" s="53" t="n"/>
-      <c r="H36" s="53" t="n"/>
-      <c r="I36" s="53" t="n"/>
-      <c r="J36" s="53" t="n"/>
-      <c r="K36" s="53" t="n"/>
-      <c r="L36" s="53" t="n"/>
-      <c r="M36" s="53" t="n"/>
-      <c r="N36" s="53" t="n"/>
-      <c r="O36" s="53" t="n"/>
-      <c r="P36" s="53" t="n"/>
-      <c r="Q36" s="67">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A36" s="77" t="n"/>
+      <c r="B36" s="77" t="n"/>
+      <c r="C36" s="77" t="n"/>
+      <c r="D36" s="77" t="n"/>
+      <c r="E36" s="77" t="n"/>
+      <c r="F36" s="77" t="n"/>
+      <c r="G36" s="77" t="n"/>
+      <c r="H36" s="77" t="n"/>
+      <c r="I36" s="77" t="n"/>
+      <c r="J36" s="77" t="n"/>
+      <c r="K36" s="77" t="n"/>
+      <c r="L36" s="77" t="n"/>
+      <c r="M36" s="77" t="n"/>
+      <c r="N36" s="77" t="n"/>
+      <c r="O36" s="77" t="n"/>
+      <c r="P36" s="77" t="n"/>
+      <c r="Q36" s="78" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="53" t="n"/>
-      <c r="B37" s="53" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
-      <c r="E37" s="53" t="n"/>
-      <c r="F37" s="53" t="n"/>
-      <c r="G37" s="53" t="n"/>
-      <c r="H37" s="53" t="n"/>
-      <c r="I37" s="53" t="n"/>
-      <c r="J37" s="53" t="n"/>
-      <c r="K37" s="53" t="n"/>
-      <c r="L37" s="53" t="n"/>
-      <c r="M37" s="53" t="n"/>
-      <c r="N37" s="53" t="n"/>
-      <c r="O37" s="53" t="n"/>
-      <c r="P37" s="53" t="n"/>
-      <c r="Q37" s="67">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A37" s="77" t="n"/>
+      <c r="B37" s="77" t="n"/>
+      <c r="C37" s="77" t="n"/>
+      <c r="D37" s="77" t="n"/>
+      <c r="E37" s="77" t="n"/>
+      <c r="F37" s="77" t="n"/>
+      <c r="G37" s="77" t="n"/>
+      <c r="H37" s="77" t="n"/>
+      <c r="I37" s="77" t="n"/>
+      <c r="J37" s="77" t="n"/>
+      <c r="K37" s="77" t="n"/>
+      <c r="L37" s="77" t="n"/>
+      <c r="M37" s="77" t="n"/>
+      <c r="N37" s="77" t="n"/>
+      <c r="O37" s="77" t="n"/>
+      <c r="P37" s="77" t="n"/>
+      <c r="Q37" s="78" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="n"/>
-      <c r="B38" s="53" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
-      <c r="E38" s="53" t="n"/>
-      <c r="F38" s="53" t="n"/>
-      <c r="G38" s="53" t="n"/>
-      <c r="H38" s="53" t="n"/>
-      <c r="I38" s="53" t="n"/>
-      <c r="J38" s="53" t="n"/>
-      <c r="K38" s="53" t="n"/>
-      <c r="L38" s="53" t="n"/>
-      <c r="M38" s="53" t="n"/>
-      <c r="N38" s="53" t="n"/>
-      <c r="O38" s="53" t="n"/>
-      <c r="P38" s="53" t="n"/>
-      <c r="Q38" s="67">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A38" s="77" t="n"/>
+      <c r="B38" s="77" t="n"/>
+      <c r="C38" s="77" t="n"/>
+      <c r="D38" s="77" t="n"/>
+      <c r="E38" s="77" t="n"/>
+      <c r="F38" s="77" t="n"/>
+      <c r="G38" s="77" t="n"/>
+      <c r="H38" s="77" t="n"/>
+      <c r="I38" s="77" t="n"/>
+      <c r="J38" s="77" t="n"/>
+      <c r="K38" s="77" t="n"/>
+      <c r="L38" s="77" t="n"/>
+      <c r="M38" s="77" t="n"/>
+      <c r="N38" s="77" t="n"/>
+      <c r="O38" s="77" t="n"/>
+      <c r="P38" s="77" t="n"/>
+      <c r="Q38" s="78" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="n"/>
-      <c r="B39" s="53" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
-      <c r="E39" s="53" t="n"/>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="53" t="n"/>
-      <c r="H39" s="53" t="n"/>
-      <c r="I39" s="53" t="n"/>
-      <c r="J39" s="53" t="n"/>
-      <c r="K39" s="53" t="n"/>
-      <c r="L39" s="53" t="n"/>
-      <c r="M39" s="53" t="n"/>
-      <c r="N39" s="53" t="n"/>
-      <c r="O39" s="53" t="n"/>
-      <c r="P39" s="53" t="n"/>
-      <c r="Q39" s="67">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A39" s="77" t="n"/>
+      <c r="B39" s="77" t="n"/>
+      <c r="C39" s="77" t="n"/>
+      <c r="D39" s="77" t="n"/>
+      <c r="E39" s="77" t="n"/>
+      <c r="F39" s="77" t="n"/>
+      <c r="G39" s="77" t="n"/>
+      <c r="H39" s="77" t="n"/>
+      <c r="I39" s="77" t="n"/>
+      <c r="J39" s="77" t="n"/>
+      <c r="K39" s="77" t="n"/>
+      <c r="L39" s="77" t="n"/>
+      <c r="M39" s="77" t="n"/>
+      <c r="N39" s="77" t="n"/>
+      <c r="O39" s="77" t="n"/>
+      <c r="P39" s="77" t="n"/>
+      <c r="Q39" s="78" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="n"/>
-      <c r="B40" s="53" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
-      <c r="E40" s="53" t="n"/>
-      <c r="F40" s="53" t="n"/>
-      <c r="G40" s="53" t="n"/>
-      <c r="H40" s="53" t="n"/>
-      <c r="I40" s="53" t="n"/>
-      <c r="J40" s="53" t="n"/>
-      <c r="K40" s="53" t="n"/>
-      <c r="L40" s="53" t="n"/>
-      <c r="M40" s="53" t="n"/>
-      <c r="N40" s="53" t="n"/>
-      <c r="O40" s="53" t="n"/>
-      <c r="P40" s="53" t="n"/>
-      <c r="Q40" s="67">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A40" s="77" t="n"/>
+      <c r="B40" s="77" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
+      <c r="I40" s="77" t="n"/>
+      <c r="J40" s="77" t="n"/>
+      <c r="K40" s="77" t="n"/>
+      <c r="L40" s="77" t="n"/>
+      <c r="M40" s="77" t="n"/>
+      <c r="N40" s="77" t="n"/>
+      <c r="O40" s="77" t="n"/>
+      <c r="P40" s="77" t="n"/>
+      <c r="Q40" s="78" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="n"/>
-      <c r="B41" s="53" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
-      <c r="E41" s="53" t="n"/>
-      <c r="F41" s="53" t="n"/>
-      <c r="G41" s="53" t="n"/>
-      <c r="H41" s="53" t="n"/>
-      <c r="I41" s="53" t="n"/>
-      <c r="J41" s="53" t="n"/>
-      <c r="K41" s="53" t="n"/>
-      <c r="L41" s="53" t="n"/>
-      <c r="M41" s="53" t="n"/>
-      <c r="N41" s="53" t="n"/>
-      <c r="O41" s="53" t="n"/>
-      <c r="P41" s="53" t="n"/>
-      <c r="Q41" s="67">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A41" s="77" t="n"/>
+      <c r="B41" s="77" t="n"/>
+      <c r="C41" s="77" t="n"/>
+      <c r="D41" s="77" t="n"/>
+      <c r="E41" s="77" t="n"/>
+      <c r="F41" s="77" t="n"/>
+      <c r="G41" s="77" t="n"/>
+      <c r="H41" s="77" t="n"/>
+      <c r="I41" s="77" t="n"/>
+      <c r="J41" s="77" t="n"/>
+      <c r="K41" s="77" t="n"/>
+      <c r="L41" s="77" t="n"/>
+      <c r="M41" s="77" t="n"/>
+      <c r="N41" s="77" t="n"/>
+      <c r="O41" s="77" t="n"/>
+      <c r="P41" s="77" t="n"/>
+      <c r="Q41" s="78" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="n"/>
-      <c r="B42" s="53" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
-      <c r="E42" s="53" t="n"/>
-      <c r="F42" s="53" t="n"/>
-      <c r="G42" s="53" t="n"/>
-      <c r="H42" s="53" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="53" t="n"/>
-      <c r="K42" s="53" t="n"/>
-      <c r="L42" s="53" t="n"/>
-      <c r="M42" s="53" t="n"/>
-      <c r="N42" s="53" t="n"/>
-      <c r="O42" s="53" t="n"/>
-      <c r="P42" s="53" t="n"/>
-      <c r="Q42" s="67">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A42" s="77" t="n"/>
+      <c r="B42" s="77" t="n"/>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="n"/>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="n"/>
+      <c r="H42" s="77" t="n"/>
+      <c r="I42" s="77" t="n"/>
+      <c r="J42" s="77" t="n"/>
+      <c r="K42" s="77" t="n"/>
+      <c r="L42" s="77" t="n"/>
+      <c r="M42" s="77" t="n"/>
+      <c r="N42" s="77" t="n"/>
+      <c r="O42" s="77" t="n"/>
+      <c r="P42" s="77" t="n"/>
+      <c r="Q42" s="78" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="n"/>
-      <c r="B43" s="53" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
-      <c r="E43" s="53" t="n"/>
-      <c r="F43" s="53" t="n"/>
-      <c r="G43" s="53" t="n"/>
-      <c r="H43" s="53" t="n"/>
-      <c r="I43" s="53" t="n"/>
-      <c r="J43" s="53" t="n"/>
-      <c r="K43" s="53" t="n"/>
-      <c r="L43" s="53" t="n"/>
-      <c r="M43" s="53" t="n"/>
-      <c r="N43" s="53" t="n"/>
-      <c r="O43" s="53" t="n"/>
-      <c r="P43" s="53" t="n"/>
-      <c r="Q43" s="67">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A43" s="77" t="n"/>
+      <c r="B43" s="77" t="n"/>
+      <c r="C43" s="77" t="n"/>
+      <c r="D43" s="77" t="n"/>
+      <c r="E43" s="77" t="n"/>
+      <c r="F43" s="77" t="n"/>
+      <c r="G43" s="77" t="n"/>
+      <c r="H43" s="77" t="n"/>
+      <c r="I43" s="77" t="n"/>
+      <c r="J43" s="77" t="n"/>
+      <c r="K43" s="77" t="n"/>
+      <c r="L43" s="77" t="n"/>
+      <c r="M43" s="77" t="n"/>
+      <c r="N43" s="77" t="n"/>
+      <c r="O43" s="77" t="n"/>
+      <c r="P43" s="77" t="n"/>
+      <c r="Q43" s="78" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="n"/>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
-      <c r="E44" s="53" t="n"/>
-      <c r="F44" s="53" t="n"/>
-      <c r="G44" s="53" t="n"/>
-      <c r="H44" s="53" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="53" t="n"/>
-      <c r="K44" s="53" t="n"/>
-      <c r="L44" s="53" t="n"/>
-      <c r="M44" s="53" t="n"/>
-      <c r="N44" s="53" t="n"/>
-      <c r="O44" s="53" t="n"/>
-      <c r="P44" s="53" t="n"/>
-      <c r="Q44" s="67">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A44" s="77" t="n"/>
+      <c r="B44" s="77" t="n"/>
+      <c r="C44" s="77" t="n"/>
+      <c r="D44" s="77" t="n"/>
+      <c r="E44" s="77" t="n"/>
+      <c r="F44" s="77" t="n"/>
+      <c r="G44" s="77" t="n"/>
+      <c r="H44" s="77" t="n"/>
+      <c r="I44" s="77" t="n"/>
+      <c r="J44" s="77" t="n"/>
+      <c r="K44" s="77" t="n"/>
+      <c r="L44" s="77" t="n"/>
+      <c r="M44" s="77" t="n"/>
+      <c r="N44" s="77" t="n"/>
+      <c r="O44" s="77" t="n"/>
+      <c r="P44" s="77" t="n"/>
+      <c r="Q44" s="78" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="53" t="n"/>
-      <c r="B45" s="53" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
-      <c r="E45" s="53" t="n"/>
-      <c r="F45" s="53" t="n"/>
-      <c r="G45" s="53" t="n"/>
-      <c r="H45" s="53" t="n"/>
-      <c r="I45" s="53" t="n"/>
-      <c r="J45" s="53" t="n"/>
-      <c r="K45" s="53" t="n"/>
-      <c r="L45" s="53" t="n"/>
-      <c r="M45" s="53" t="n"/>
-      <c r="N45" s="53" t="n"/>
-      <c r="O45" s="53" t="n"/>
-      <c r="P45" s="53" t="n"/>
-      <c r="Q45" s="67">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A45" s="77" t="n"/>
+      <c r="B45" s="77" t="n"/>
+      <c r="C45" s="77" t="n"/>
+      <c r="D45" s="77" t="n"/>
+      <c r="E45" s="77" t="n"/>
+      <c r="F45" s="77" t="n"/>
+      <c r="G45" s="77" t="n"/>
+      <c r="H45" s="77" t="n"/>
+      <c r="I45" s="77" t="n"/>
+      <c r="J45" s="77" t="n"/>
+      <c r="K45" s="77" t="n"/>
+      <c r="L45" s="77" t="n"/>
+      <c r="M45" s="77" t="n"/>
+      <c r="N45" s="77" t="n"/>
+      <c r="O45" s="77" t="n"/>
+      <c r="P45" s="77" t="n"/>
+      <c r="Q45" s="78" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="53" t="n"/>
-      <c r="B46" s="53" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
-      <c r="E46" s="53" t="n"/>
-      <c r="F46" s="53" t="n"/>
-      <c r="G46" s="53" t="n"/>
-      <c r="H46" s="53" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="53" t="n"/>
-      <c r="K46" s="53" t="n"/>
-      <c r="L46" s="53" t="n"/>
-      <c r="M46" s="53" t="n"/>
-      <c r="N46" s="53" t="n"/>
-      <c r="O46" s="53" t="n"/>
-      <c r="P46" s="53" t="n"/>
-      <c r="Q46" s="67">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A46" s="77" t="n"/>
+      <c r="B46" s="77" t="n"/>
+      <c r="C46" s="77" t="n"/>
+      <c r="D46" s="77" t="n"/>
+      <c r="E46" s="77" t="n"/>
+      <c r="F46" s="77" t="n"/>
+      <c r="G46" s="77" t="n"/>
+      <c r="H46" s="77" t="n"/>
+      <c r="I46" s="77" t="n"/>
+      <c r="J46" s="77" t="n"/>
+      <c r="K46" s="77" t="n"/>
+      <c r="L46" s="77" t="n"/>
+      <c r="M46" s="77" t="n"/>
+      <c r="N46" s="77" t="n"/>
+      <c r="O46" s="77" t="n"/>
+      <c r="P46" s="77" t="n"/>
+      <c r="Q46" s="78" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="n"/>
-      <c r="B47" s="53" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
-      <c r="E47" s="53" t="n"/>
-      <c r="F47" s="53" t="n"/>
-      <c r="G47" s="53" t="n"/>
-      <c r="H47" s="53" t="n"/>
-      <c r="I47" s="53" t="n"/>
-      <c r="J47" s="53" t="n"/>
-      <c r="K47" s="53" t="n"/>
-      <c r="L47" s="53" t="n"/>
-      <c r="M47" s="53" t="n"/>
-      <c r="N47" s="53" t="n"/>
-      <c r="O47" s="53" t="n"/>
-      <c r="P47" s="53" t="n"/>
-      <c r="Q47" s="67">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A47" s="77" t="n"/>
+      <c r="B47" s="77" t="n"/>
+      <c r="C47" s="77" t="n"/>
+      <c r="D47" s="77" t="n"/>
+      <c r="E47" s="77" t="n"/>
+      <c r="F47" s="77" t="n"/>
+      <c r="G47" s="77" t="n"/>
+      <c r="H47" s="77" t="n"/>
+      <c r="I47" s="77" t="n"/>
+      <c r="J47" s="77" t="n"/>
+      <c r="K47" s="77" t="n"/>
+      <c r="L47" s="77" t="n"/>
+      <c r="M47" s="77" t="n"/>
+      <c r="N47" s="77" t="n"/>
+      <c r="O47" s="77" t="n"/>
+      <c r="P47" s="77" t="n"/>
+      <c r="Q47" s="78" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="n"/>
-      <c r="B48" s="53" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
-      <c r="G48" s="53" t="n"/>
-      <c r="H48" s="53" t="n"/>
-      <c r="I48" s="53" t="n"/>
-      <c r="J48" s="53" t="n"/>
-      <c r="K48" s="53" t="n"/>
-      <c r="L48" s="53" t="n"/>
-      <c r="M48" s="53" t="n"/>
-      <c r="N48" s="53" t="n"/>
-      <c r="O48" s="53" t="n"/>
-      <c r="P48" s="53" t="n"/>
-      <c r="Q48" s="67">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A48" s="77" t="n"/>
+      <c r="B48" s="77" t="n"/>
+      <c r="C48" s="77" t="n"/>
+      <c r="D48" s="77" t="n"/>
+      <c r="E48" s="77" t="n"/>
+      <c r="F48" s="77" t="n"/>
+      <c r="G48" s="77" t="n"/>
+      <c r="H48" s="77" t="n"/>
+      <c r="I48" s="77" t="n"/>
+      <c r="J48" s="77" t="n"/>
+      <c r="K48" s="77" t="n"/>
+      <c r="L48" s="77" t="n"/>
+      <c r="M48" s="77" t="n"/>
+      <c r="N48" s="77" t="n"/>
+      <c r="O48" s="77" t="n"/>
+      <c r="P48" s="77" t="n"/>
+      <c r="Q48" s="78" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="n"/>
-      <c r="B49" s="53" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
-      <c r="E49" s="53" t="n"/>
-      <c r="F49" s="53" t="n"/>
-      <c r="G49" s="53" t="n"/>
-      <c r="H49" s="53" t="n"/>
-      <c r="I49" s="53" t="n"/>
-      <c r="J49" s="53" t="n"/>
-      <c r="K49" s="53" t="n"/>
-      <c r="L49" s="53" t="n"/>
-      <c r="M49" s="53" t="n"/>
-      <c r="N49" s="53" t="n"/>
-      <c r="O49" s="53" t="n"/>
-      <c r="P49" s="53" t="n"/>
-      <c r="Q49" s="67">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A49" s="77" t="n"/>
+      <c r="B49" s="77" t="n"/>
+      <c r="C49" s="77" t="n"/>
+      <c r="D49" s="77" t="n"/>
+      <c r="E49" s="77" t="n"/>
+      <c r="F49" s="77" t="n"/>
+      <c r="G49" s="77" t="n"/>
+      <c r="H49" s="77" t="n"/>
+      <c r="I49" s="77" t="n"/>
+      <c r="J49" s="77" t="n"/>
+      <c r="K49" s="77" t="n"/>
+      <c r="L49" s="77" t="n"/>
+      <c r="M49" s="77" t="n"/>
+      <c r="N49" s="77" t="n"/>
+      <c r="O49" s="77" t="n"/>
+      <c r="P49" s="77" t="n"/>
+      <c r="Q49" s="78" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="n"/>
-      <c r="B50" s="53" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
-      <c r="E50" s="53" t="n"/>
-      <c r="F50" s="53" t="n"/>
-      <c r="G50" s="53" t="n"/>
-      <c r="H50" s="53" t="n"/>
-      <c r="I50" s="53" t="n"/>
-      <c r="J50" s="53" t="n"/>
-      <c r="K50" s="53" t="n"/>
-      <c r="L50" s="53" t="n"/>
-      <c r="M50" s="53" t="n"/>
-      <c r="N50" s="53" t="n"/>
-      <c r="O50" s="53" t="n"/>
-      <c r="P50" s="53" t="n"/>
-      <c r="Q50" s="67">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A50" s="77" t="n"/>
+      <c r="B50" s="77" t="n"/>
+      <c r="C50" s="77" t="n"/>
+      <c r="D50" s="77" t="n"/>
+      <c r="E50" s="77" t="n"/>
+      <c r="F50" s="77" t="n"/>
+      <c r="G50" s="77" t="n"/>
+      <c r="H50" s="77" t="n"/>
+      <c r="I50" s="77" t="n"/>
+      <c r="J50" s="77" t="n"/>
+      <c r="K50" s="77" t="n"/>
+      <c r="L50" s="77" t="n"/>
+      <c r="M50" s="77" t="n"/>
+      <c r="N50" s="77" t="n"/>
+      <c r="O50" s="77" t="n"/>
+      <c r="P50" s="77" t="n"/>
+      <c r="Q50" s="78" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="n"/>
-      <c r="B51" s="53" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
-      <c r="E51" s="53" t="n"/>
-      <c r="F51" s="53" t="n"/>
-      <c r="G51" s="53" t="n"/>
-      <c r="H51" s="53" t="n"/>
-      <c r="I51" s="53" t="n"/>
-      <c r="J51" s="53" t="n"/>
-      <c r="K51" s="53" t="n"/>
-      <c r="L51" s="53" t="n"/>
-      <c r="M51" s="53" t="n"/>
-      <c r="N51" s="53" t="n"/>
-      <c r="O51" s="53" t="n"/>
-      <c r="P51" s="53" t="n"/>
-      <c r="Q51" s="67">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A51" s="77" t="n"/>
+      <c r="B51" s="77" t="n"/>
+      <c r="C51" s="77" t="n"/>
+      <c r="D51" s="77" t="n"/>
+      <c r="E51" s="77" t="n"/>
+      <c r="F51" s="77" t="n"/>
+      <c r="G51" s="77" t="n"/>
+      <c r="H51" s="77" t="n"/>
+      <c r="I51" s="77" t="n"/>
+      <c r="J51" s="77" t="n"/>
+      <c r="K51" s="77" t="n"/>
+      <c r="L51" s="77" t="n"/>
+      <c r="M51" s="77" t="n"/>
+      <c r="N51" s="77" t="n"/>
+      <c r="O51" s="77" t="n"/>
+      <c r="P51" s="77" t="n"/>
+      <c r="Q51" s="78" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="n"/>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
-      <c r="E52" s="53" t="n"/>
-      <c r="F52" s="53" t="n"/>
-      <c r="G52" s="53" t="n"/>
-      <c r="H52" s="53" t="n"/>
-      <c r="I52" s="53" t="n"/>
-      <c r="J52" s="53" t="n"/>
-      <c r="K52" s="53" t="n"/>
-      <c r="L52" s="53" t="n"/>
-      <c r="M52" s="53" t="n"/>
-      <c r="N52" s="53" t="n"/>
-      <c r="O52" s="53" t="n"/>
-      <c r="P52" s="53" t="n"/>
-      <c r="Q52" s="67">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A52" s="77" t="n"/>
+      <c r="B52" s="77" t="n"/>
+      <c r="C52" s="77" t="n"/>
+      <c r="D52" s="77" t="n"/>
+      <c r="E52" s="77" t="n"/>
+      <c r="F52" s="77" t="n"/>
+      <c r="G52" s="77" t="n"/>
+      <c r="H52" s="77" t="n"/>
+      <c r="I52" s="77" t="n"/>
+      <c r="J52" s="77" t="n"/>
+      <c r="K52" s="77" t="n"/>
+      <c r="L52" s="77" t="n"/>
+      <c r="M52" s="77" t="n"/>
+      <c r="N52" s="77" t="n"/>
+      <c r="O52" s="77" t="n"/>
+      <c r="P52" s="77" t="n"/>
+      <c r="Q52" s="78" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="n"/>
-      <c r="B53" s="53" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
-      <c r="E53" s="53" t="n"/>
-      <c r="F53" s="53" t="n"/>
-      <c r="G53" s="53" t="n"/>
-      <c r="H53" s="53" t="n"/>
-      <c r="I53" s="53" t="n"/>
-      <c r="J53" s="53" t="n"/>
-      <c r="K53" s="53" t="n"/>
-      <c r="L53" s="53" t="n"/>
-      <c r="M53" s="53" t="n"/>
-      <c r="N53" s="53" t="n"/>
-      <c r="O53" s="53" t="n"/>
-      <c r="P53" s="53" t="n"/>
-      <c r="Q53" s="67">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A53" s="77" t="n"/>
+      <c r="B53" s="77" t="n"/>
+      <c r="C53" s="77" t="n"/>
+      <c r="D53" s="77" t="n"/>
+      <c r="E53" s="77" t="n"/>
+      <c r="F53" s="77" t="n"/>
+      <c r="G53" s="77" t="n"/>
+      <c r="H53" s="77" t="n"/>
+      <c r="I53" s="77" t="n"/>
+      <c r="J53" s="77" t="n"/>
+      <c r="K53" s="77" t="n"/>
+      <c r="L53" s="77" t="n"/>
+      <c r="M53" s="77" t="n"/>
+      <c r="N53" s="77" t="n"/>
+      <c r="O53" s="77" t="n"/>
+      <c r="P53" s="77" t="n"/>
+      <c r="Q53" s="78" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="53" t="n"/>
-      <c r="B54" s="53" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
-      <c r="E54" s="53" t="n"/>
-      <c r="F54" s="53" t="n"/>
-      <c r="G54" s="53" t="n"/>
-      <c r="H54" s="53" t="n"/>
-      <c r="I54" s="53" t="n"/>
-      <c r="J54" s="53" t="n"/>
-      <c r="K54" s="53" t="n"/>
-      <c r="L54" s="53" t="n"/>
-      <c r="M54" s="53" t="n"/>
-      <c r="N54" s="53" t="n"/>
-      <c r="O54" s="53" t="n"/>
-      <c r="P54" s="53" t="n"/>
-      <c r="Q54" s="67">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
+      <c r="A54" s="77" t="n"/>
+      <c r="B54" s="77" t="n"/>
+      <c r="C54" s="77" t="n"/>
+      <c r="D54" s="77" t="n"/>
+      <c r="E54" s="77" t="n"/>
+      <c r="F54" s="77" t="n"/>
+      <c r="G54" s="77" t="n"/>
+      <c r="H54" s="77" t="n"/>
+      <c r="I54" s="77" t="n"/>
+      <c r="J54" s="77" t="n"/>
+      <c r="K54" s="77" t="n"/>
+      <c r="L54" s="77" t="n"/>
+      <c r="M54" s="77" t="n"/>
+      <c r="N54" s="77" t="n"/>
+      <c r="O54" s="77" t="n"/>
+      <c r="P54" s="77" t="n"/>
+      <c r="Q54" s="78" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="53" t="n"/>
-      <c r="B55" s="53" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
-      <c r="E55" s="53" t="n"/>
-      <c r="F55" s="53" t="n"/>
-      <c r="G55" s="53" t="n"/>
-      <c r="H55" s="53" t="n"/>
-      <c r="I55" s="53" t="n"/>
-      <c r="J55" s="53" t="n"/>
-      <c r="K55" s="53" t="n"/>
-      <c r="L55" s="53" t="n"/>
-      <c r="M55" s="53" t="n"/>
-      <c r="N55" s="53" t="n"/>
-      <c r="O55" s="53" t="n"/>
-      <c r="P55" s="53" t="n"/>
-      <c r="Q55" s="67">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
+      <c r="A55" s="77" t="n"/>
+      <c r="B55" s="77" t="n"/>
+      <c r="C55" s="77" t="n"/>
+      <c r="D55" s="77" t="n"/>
+      <c r="E55" s="77" t="n"/>
+      <c r="F55" s="77" t="n"/>
+      <c r="G55" s="77" t="n"/>
+      <c r="H55" s="77" t="n"/>
+      <c r="I55" s="77" t="n"/>
+      <c r="J55" s="77" t="n"/>
+      <c r="K55" s="77" t="n"/>
+      <c r="L55" s="77" t="n"/>
+      <c r="M55" s="77" t="n"/>
+      <c r="N55" s="77" t="n"/>
+      <c r="O55" s="77" t="n"/>
+      <c r="P55" s="77" t="n"/>
+      <c r="Q55" s="78" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="n"/>
-      <c r="B56" s="53" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
-      <c r="E56" s="53" t="n"/>
-      <c r="F56" s="53" t="n"/>
-      <c r="G56" s="53" t="n"/>
-      <c r="H56" s="53" t="n"/>
-      <c r="I56" s="53" t="n"/>
-      <c r="J56" s="53" t="n"/>
-      <c r="K56" s="53" t="n"/>
-      <c r="L56" s="53" t="n"/>
-      <c r="M56" s="53" t="n"/>
-      <c r="N56" s="53" t="n"/>
-      <c r="O56" s="53" t="n"/>
-      <c r="P56" s="53" t="n"/>
-      <c r="Q56" s="67">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
+      <c r="A56" s="77" t="n"/>
+      <c r="B56" s="77" t="n"/>
+      <c r="C56" s="77" t="n"/>
+      <c r="D56" s="77" t="n"/>
+      <c r="E56" s="77" t="n"/>
+      <c r="F56" s="77" t="n"/>
+      <c r="G56" s="77" t="n"/>
+      <c r="H56" s="77" t="n"/>
+      <c r="I56" s="77" t="n"/>
+      <c r="J56" s="77" t="n"/>
+      <c r="K56" s="77" t="n"/>
+      <c r="L56" s="77" t="n"/>
+      <c r="M56" s="77" t="n"/>
+      <c r="N56" s="77" t="n"/>
+      <c r="O56" s="77" t="n"/>
+      <c r="P56" s="77" t="n"/>
+      <c r="Q56" s="78" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="53" t="n"/>
-      <c r="B57" s="53" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
-      <c r="E57" s="53" t="n"/>
-      <c r="F57" s="53" t="n"/>
-      <c r="G57" s="53" t="n"/>
-      <c r="H57" s="53" t="n"/>
-      <c r="I57" s="53" t="n"/>
-      <c r="J57" s="53" t="n"/>
-      <c r="K57" s="53" t="n"/>
-      <c r="L57" s="53" t="n"/>
-      <c r="M57" s="53" t="n"/>
-      <c r="N57" s="53" t="n"/>
-      <c r="O57" s="53" t="n"/>
-      <c r="P57" s="53" t="n"/>
-      <c r="Q57" s="67">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
+      <c r="A57" s="77" t="n"/>
+      <c r="B57" s="77" t="n"/>
+      <c r="C57" s="77" t="n"/>
+      <c r="D57" s="77" t="n"/>
+      <c r="E57" s="77" t="n"/>
+      <c r="F57" s="77" t="n"/>
+      <c r="G57" s="77" t="n"/>
+      <c r="H57" s="77" t="n"/>
+      <c r="I57" s="77" t="n"/>
+      <c r="J57" s="77" t="n"/>
+      <c r="K57" s="77" t="n"/>
+      <c r="L57" s="77" t="n"/>
+      <c r="M57" s="77" t="n"/>
+      <c r="N57" s="77" t="n"/>
+      <c r="O57" s="77" t="n"/>
+      <c r="P57" s="77" t="n"/>
+      <c r="Q57" s="78" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="n"/>
-      <c r="B58" s="53" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
-      <c r="E58" s="53" t="n"/>
-      <c r="F58" s="53" t="n"/>
-      <c r="G58" s="53" t="n"/>
-      <c r="H58" s="53" t="n"/>
-      <c r="I58" s="53" t="n"/>
-      <c r="J58" s="53" t="n"/>
-      <c r="K58" s="53" t="n"/>
-      <c r="L58" s="53" t="n"/>
-      <c r="M58" s="53" t="n"/>
-      <c r="N58" s="53" t="n"/>
-      <c r="O58" s="53" t="n"/>
-      <c r="P58" s="53" t="n"/>
-      <c r="Q58" s="67">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
+      <c r="A58" s="77" t="n"/>
+      <c r="B58" s="77" t="n"/>
+      <c r="C58" s="77" t="n"/>
+      <c r="D58" s="77" t="n"/>
+      <c r="E58" s="77" t="n"/>
+      <c r="F58" s="77" t="n"/>
+      <c r="G58" s="77" t="n"/>
+      <c r="H58" s="77" t="n"/>
+      <c r="I58" s="77" t="n"/>
+      <c r="J58" s="77" t="n"/>
+      <c r="K58" s="77" t="n"/>
+      <c r="L58" s="77" t="n"/>
+      <c r="M58" s="77" t="n"/>
+      <c r="N58" s="77" t="n"/>
+      <c r="O58" s="77" t="n"/>
+      <c r="P58" s="77" t="n"/>
+      <c r="Q58" s="78" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="n"/>
-      <c r="B59" s="53" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
-      <c r="E59" s="53" t="n"/>
-      <c r="F59" s="53" t="n"/>
-      <c r="G59" s="53" t="n"/>
-      <c r="H59" s="53" t="n"/>
-      <c r="I59" s="53" t="n"/>
-      <c r="J59" s="53" t="n"/>
-      <c r="K59" s="53" t="n"/>
-      <c r="L59" s="53" t="n"/>
-      <c r="M59" s="53" t="n"/>
-      <c r="N59" s="53" t="n"/>
-      <c r="O59" s="53" t="n"/>
-      <c r="P59" s="53" t="n"/>
-      <c r="Q59" s="67">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
+      <c r="A59" s="77" t="n"/>
+      <c r="B59" s="77" t="n"/>
+      <c r="C59" s="77" t="n"/>
+      <c r="D59" s="77" t="n"/>
+      <c r="E59" s="77" t="n"/>
+      <c r="F59" s="77" t="n"/>
+      <c r="G59" s="77" t="n"/>
+      <c r="H59" s="77" t="n"/>
+      <c r="I59" s="77" t="n"/>
+      <c r="J59" s="77" t="n"/>
+      <c r="K59" s="77" t="n"/>
+      <c r="L59" s="77" t="n"/>
+      <c r="M59" s="77" t="n"/>
+      <c r="N59" s="77" t="n"/>
+      <c r="O59" s="77" t="n"/>
+      <c r="P59" s="77" t="n"/>
+      <c r="Q59" s="78" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="n"/>
-      <c r="B60" s="53" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
-      <c r="G60" s="53" t="n"/>
-      <c r="H60" s="53" t="n"/>
-      <c r="I60" s="53" t="n"/>
-      <c r="J60" s="53" t="n"/>
-      <c r="K60" s="53" t="n"/>
-      <c r="L60" s="53" t="n"/>
-      <c r="M60" s="53" t="n"/>
-      <c r="N60" s="53" t="n"/>
-      <c r="O60" s="53" t="n"/>
-      <c r="P60" s="53" t="n"/>
-      <c r="Q60" s="67">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
+      <c r="A60" s="77" t="n"/>
+      <c r="B60" s="77" t="n"/>
+      <c r="C60" s="77" t="n"/>
+      <c r="D60" s="77" t="n"/>
+      <c r="E60" s="77" t="n"/>
+      <c r="F60" s="77" t="n"/>
+      <c r="G60" s="77" t="n"/>
+      <c r="H60" s="77" t="n"/>
+      <c r="I60" s="77" t="n"/>
+      <c r="J60" s="77" t="n"/>
+      <c r="K60" s="77" t="n"/>
+      <c r="L60" s="77" t="n"/>
+      <c r="M60" s="77" t="n"/>
+      <c r="N60" s="77" t="n"/>
+      <c r="O60" s="77" t="n"/>
+      <c r="P60" s="77" t="n"/>
+      <c r="Q60" s="78" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q60"/>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D10" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E11" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D12" location="'برنامه تست'!A11"/>
-    <hyperlink ref="E17" location="'برنامه تست'!A16"/>
-    <hyperlink ref="M19" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D12" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D13" location="'برنامه تست'!A7"/>
+    <hyperlink ref="E16" location="'برنامه تست'!A9"/>
+    <hyperlink ref="M17" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4087,7 +3967,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E5" location="'برنامه تست'!A11"/>
+    <hyperlink ref="E5" location="'برنامه تست'!A7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5337,7 +5217,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" location="'برنامه تست'!A5"/>
-    <hyperlink ref="B4" location="'برنامه تست'!A19"/>
+    <hyperlink ref="B4" location="'برنامه تست'!A17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
   </hyperlinks>
@@ -5721,8 +5601,6 @@
           <t>ماشین حالت ماژول عدم‌توازن (سناریوی ۵)</t>
         </is>
       </c>
-      <c r="B1" s="53" t="n"/>
-      <c r="C1" s="53" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="53" t="n"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -925,6 +925,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="76" t="inlineStr">
         <is>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="C5" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D5" s="56" t="inlineStr">
@@ -1223,7 +1224,7 @@
       </c>
       <c r="C6" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D6" s="56" t="inlineStr">
@@ -1307,7 +1308,7 @@
       </c>
       <c r="C7" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
@@ -1391,7 +1392,7 @@
       </c>
       <c r="C8" s="62" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="61" t="inlineStr">
@@ -1475,7 +1476,7 @@
       </c>
       <c r="C9" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -879,49 +879,62 @@
     <row r="5">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>سناریوی ۵: پایش قدرمطلق اختلاف دو نیم‌باتری ۱۲ ولتی |v_bat_high - v_bat_low| و قضاوت عدم‌توازن با شمارش ماندگار رویداد.</t>
+          <t>سناریوی ۵: اختلاف ولتاژ دو نیم‌باتری ۱۲ ولتی دائم چک می‌شود.
+اگر اختلاف از حد رد شود، یک «رویداد» شمرده می‌شود. این شمارش ماندگار است و با قطع برق پاک نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="51" t="inlineStr">
         <is>
-          <t>ماژول منطق خالص است: همهٔ ورودی‌ها و زمان جاری از بیرون می‌آیند و هیچ وابستگی به BSP یا RTOS ندارد؛ سیم‌بندی در task_control.c است.</t>
+          <t>این ماژول فقط منطق است و به سخت‌افزار دست نمی‌زند.
+همهٔ ورودی‌ها و زمان از بیرون به آن داده می‌شود.
+وصل‌کردنش به بقیهٔ برنامه در فایل task_control.c است.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="50" t="inlineStr">
         <is>
-          <t>گیت زمانی: حد استراحت (۱۰۸) فقط در استراحت و پس از ۱۱۰ از پایان شارژ، و حین شارژ پس از ۱۱۱؛ در دشارژ حد ۱۰۹ بلافاصله اعمال می‌شود.</t>
+          <t>هر حد، زمان خودش را دارد:
+حد استراحت (شناسهٔ ۱۰۸) فقط وقتی باتری استراحت می‌کند شمرده می‌شود؛ تازه بعد از گذشتن زمان انتظار (شناسهٔ ۱۱۰) از پایان شارژ.
+هنگام شارژ، بعد از زمان انتظار (شناسهٔ ۱۱۱) شمرده می‌شود.
+هنگام خالی‌شدن باتری (دشارژ)، حد دشارژ (شناسهٔ ۱۰۹) همان لحظه اعمال می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>رویداد = فراتر از حد به‌طور پیوسته برای ۱۱۲؛ پایان اپیزود با هیسترزیس ۱۱۳؛ هر اپیزود فقط یک‌بار شمرده می‌شود.</t>
+          <t>یک رویداد وقتی شمرده می‌شود که اختلاف، پیوسته و به اندازهٔ زمان پایداری (شناسهٔ ۱۱۲) بالای حد بماند.
+پایان هر دوره وقتی است که اختلاف به اندازهٔ هیسترزیس (شناسهٔ ۱۱۳) پایین بیاید.
+هر دوره فقط یک بار شمرده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="50" t="inlineStr">
         <is>
-          <t>رویدادها ≥ ۱۱۴ → قفل: قرمز چشمک‌زن + بوق ساعتی + وتوی خروجی (در صورت تیک ۱۱۷)؛ ۱۱۸ سیکل شارژ در قفل → مسدودی شارژ.</t>
+          <t>اگر تعداد رویدادها به حد قفل (شناسهٔ ۱۱۴) برسد، دستگاه قفل می‌کند:
+چراغ قرمز چشمک می‌زند و هر از گاهی بوق می‌آید.
+اگر کلید شناسهٔ ۱۱۷ روشن باشد، خروجی هم قطع می‌شود (وتوی خروجی).
+اگر در حالت قفل، تعداد سیکل شارژ (شناسهٔ ۱۱۸) کامل شود، شارژ هم بسته می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="50" t="inlineStr">
         <is>
-          <t>نبود باتری برای ۳ ثانیهٔ پیوسته = تعویض واقعی → ریست خودکار همهٔ شمارنده‌ها و قفل.</t>
+          <t>اگر باتری ۳ ثانیه پشت سر هم نباشد، یعنی باتری عوض شده است.
+آن وقت همهٔ شمارنده‌ها و قفل خودکار از نو شروع می‌شوند.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="50" t="inlineStr">
         <is>
-          <t>شمارنده‌ها در اسلات‌های ۲۰۰..۲۰۲ ماندگارند و با قطع برق پاک نمی‌شوند. تست Host جایگزین تست برد نیست.</t>
+          <t>شمارنده‌ها در جای ماندگار (اسلات‌های ۲۰۰ تا ۲۰۲) ذخیره می‌شوند و با قطع برق پاک نمی‌شوند.
+تست روی کامپیوتر جای تست روی برد را نمی‌گیرد.</t>
         </is>
       </c>
     </row>
@@ -929,8 +942,12 @@
     <row r="13">
       <c r="A13" s="76" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1100,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -1108,12 +1125,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -1193,17 +1210,17 @@
       <c r="M5" s="56" t="n"/>
       <c r="N5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O5" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q5" s="60">
@@ -1277,17 +1294,17 @@
       <c r="M6" s="56" t="n"/>
       <c r="N6" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O6" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q6" s="60">
@@ -1361,17 +1378,17 @@
       <c r="M7" s="56" t="n"/>
       <c r="N7" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O7" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q7" s="60">
@@ -1445,17 +1462,17 @@
       <c r="M8" s="61" t="n"/>
       <c r="N8" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O8" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q8" s="64">
@@ -1528,17 +1545,17 @@
       <c r="M9" s="56" t="n"/>
       <c r="N9" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O9" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q9" s="60">
@@ -1611,17 +1628,17 @@
       <c r="M10" s="61" t="n"/>
       <c r="N10" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O10" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q10" s="64">
@@ -1695,17 +1712,17 @@
       <c r="M11" s="61" t="n"/>
       <c r="N11" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O11" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q11" s="64">
@@ -1778,17 +1795,17 @@
       <c r="M12" s="61" t="n"/>
       <c r="N12" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O12" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q12" s="64">
@@ -1862,17 +1879,17 @@
       <c r="M13" s="56" t="n"/>
       <c r="N13" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O13" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P13" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q13" s="60">
@@ -1945,17 +1962,17 @@
       <c r="M14" s="56" t="n"/>
       <c r="N14" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O14" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P14" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q14" s="60">
@@ -2028,17 +2045,17 @@
       <c r="M15" s="61" t="n"/>
       <c r="N15" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O15" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P15" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q15" s="64">
@@ -2112,17 +2129,17 @@
       <c r="M16" s="61" t="n"/>
       <c r="N16" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O16" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P16" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q16" s="64">
@@ -2195,22 +2212,22 @@
       </c>
       <c r="M17" s="65" t="inlineStr">
         <is>
-          <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (DEF-IM-001) — رگرسیون هاست در host_test_imbalance.c پوشش داده شد</t>
+          <t>ایراد ممیزی ۲۰۲۶-۱۰-۰۶ (با شناسهٔ DEF-IM-001): این مورد در تست هاست (host_test_imbalance.c) پوشش داده شد.</t>
         </is>
       </c>
       <c r="N17" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O17" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P17" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q17" s="64">
@@ -2287,17 +2304,17 @@
       </c>
       <c r="N18" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O18" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P18" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q18" s="60">
@@ -2370,17 +2387,17 @@
       <c r="M19" s="56" t="n"/>
       <c r="N19" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O19" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P19" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q19" s="60">
@@ -2453,17 +2470,17 @@
       <c r="M20" s="56" t="n"/>
       <c r="N20" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O20" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P20" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q20" s="60">
@@ -3390,7 +3407,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -3415,12 +3432,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -3501,17 +3518,17 @@
       <c r="M5" s="61" t="n"/>
       <c r="N5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O5" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q5" s="64" t="inlineStr">
@@ -4112,7 +4129,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -4137,12 +4154,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -5129,7 +5146,7 @@
       </c>
       <c r="J3" s="70" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="70" t="inlineStr">
@@ -5323,12 +5340,12 @@
     <row r="8">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="53" t="n"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -199,7 +199,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -234,6 +234,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -480,6 +490,35 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,14 +892,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Imbalance</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>Imbalance | سناریوی ۵: قضاوت عدم‌توازن دو نیم‌باتری با شمارش ماندگار رویداد و قفل</t>
         </is>
@@ -904,7 +943,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>یک رویداد وقتی شمرده می‌شود که اختلاف، پیوسته و به اندازهٔ زمان پایداری (شناسهٔ ۱۱۲) بالای حد بماند.
 پایان هر دوره وقتی است که اختلاف به اندازهٔ هیسترزیس (شناسهٔ ۱۱۳) پایین بیاید.
@@ -913,7 +952,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>اگر تعداد رویدادها به حد قفل (شناسهٔ ۱۱۴) برسد، دستگاه قفل می‌کند:
 چراغ قرمز چشمک می‌زند و هر از گاهی بوق می‌آید.
@@ -923,7 +962,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>اگر باتری ۳ ثانیه پشت سر هم نباشد، یعنی باتری عوض شده است.
 آن وقت همهٔ شمارنده‌ها و قفل خودکار از نو شروع می‌شوند.</t>
@@ -931,7 +970,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>شمارنده‌ها در جای ماندگار (اسلات‌های ۲۰۰ تا ۲۰۲) ذخیره می‌شوند و با قطع برق پاک نمی‌شوند.
 تست روی کامپیوتر جای تست روی برد را نمی‌گیرد.</t>
@@ -940,7 +979,7 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="82" t="inlineStr">
         <is>
           <t>اولویت‌ها ساده‌اند:
 «بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
@@ -989,7 +1028,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Imbalance</t>
         </is>
@@ -1058,87 +1097,87 @@
       <c r="Q3" s="53" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1150,54 +1189,54 @@
           <t>IM-001</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>آستانهٔ استراحت</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>دو باتری ۱۲ ولت وصل است؛ دستگاه خاموش و بیکار (نه شارژ، نه بار)</t>
         </is>
       </c>
-      <c r="E5" s="56" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>گام ۱: یکی از باتری‌ها را با یک لامپ ۱۲ ولت کمی خالی کن تا از آن یکی ضعیف‌تر شود.
 گام ۲: باتری‌ها را سر جا وصل کن و دستگاه را نیم ساعت بیکار بگذار.
 گام ۳: در پنل ببین رویداد عدم‌توازن شمرده شده یا نه.</t>
         </is>
       </c>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>یک نیم ضعیف‌تر در حالت استراحت</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H5" s="56" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>اختلاف دو باتری در استراحت دیده و یک رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="56" t="inlineStr">
+      <c r="I5" s="61" t="inlineStr">
         <is>
           <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
-      <c r="J5" s="56" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr">
         <is>
           <t>باید ببینید: اختلاف دو باتری در استراحت در پنل دیده می‌شود و یک رویداد شمرده می‌شود. اگر با اختلاف واضح نشمرد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K5" s="56" t="inlineStr">
+      <c r="K5" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1208,22 +1247,22 @@
         </is>
       </c>
       <c r="M5" s="56" t="n"/>
-      <c r="N5" s="56" t="inlineStr">
+      <c r="N5" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O5" s="58" t="inlineStr">
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P5" s="58" t="inlineStr">
+      <c r="P5" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q5" s="60">
+      <c r="Q5" s="64">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -1234,54 +1273,54 @@
           <t>IM-003</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>آستانهٔ دشارژ</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="85" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="84" t="inlineStr">
         <is>
           <t>دستگاه روی باتری دارد به یک بار واقعی کار می‌کند</t>
         </is>
       </c>
-      <c r="E6" s="56" t="inlineStr">
+      <c r="E6" s="84" t="inlineStr">
         <is>
           <t>گام ۱: حین کار، باتری‌ای که ضعیف‌تر است را زیر نظر بگیر (از اول یکی را کمی خالی‌تر وصل کن).
 گام ۲: بگذار دستگاه مدتی با بار کار کند.
 گام ۳: شمارندهٔ رویداد را در پنل چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="86" t="inlineStr">
         <is>
           <t>دو باتری نابرابر زیر بار واقعی</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="86" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H6" s="56" t="inlineStr">
+      <c r="H6" s="84" t="inlineStr">
         <is>
           <t>اختلاف زیر بار هم دیده و رویداد شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I6" s="56" t="inlineStr">
+      <c r="I6" s="84" t="inlineStr">
         <is>
           <t>رویداد در شمارنده می‌ماند</t>
         </is>
       </c>
-      <c r="J6" s="56" t="inlineStr">
+      <c r="J6" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: اختلاف زیر بار هم دیده و رویداد شمرده می‌شود. اگر فقط در استراحت شمرد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K6" s="56" t="inlineStr">
+      <c r="K6" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1292,22 +1331,22 @@
         </is>
       </c>
       <c r="M6" s="56" t="n"/>
-      <c r="N6" s="56" t="inlineStr">
+      <c r="N6" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O6" s="58" t="inlineStr">
+      <c r="O6" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P6" s="58" t="inlineStr">
+      <c r="P6" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="87">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -1318,54 +1357,54 @@
           <t>IM-007</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>قفل شدن</t>
         </is>
       </c>
-      <c r="C7" s="57" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="56" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>دو باتری نابرابر داری؛ برای زود دیدن نتیجه از پنل حدّ رویدادهای مجاز را موقتاً روی یک بگذار</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد عدم‌توازن بساز (مثل IM-001).
 گام ۲: وقتی قفل شد چراغ‌ها را ببین: فقط قرمز چشمک می‌زند، سبز و زرد خاموش‌اند.
 گام ۳: حدّ را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F7" s="58" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>رویداد عدم‌توازن با حدّ موقتِ یک</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H7" s="56" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن می‌نشیند: قرمز چشمک‌زنِ تنها، بدون سبز و زرد</t>
         </is>
       </c>
-      <c r="I7" s="56" t="inlineStr">
+      <c r="I7" s="61" t="inlineStr">
         <is>
           <t>قفل تا تعویض باتری</t>
         </is>
       </c>
-      <c r="J7" s="56" t="inlineStr">
+      <c r="J7" s="61" t="inlineStr">
         <is>
           <t>باید ببینید: قفل می‌نشیند؛ فقط قرمز چشمک می‌زند و سبز و زرد خاموش‌اند. اگر قفل نشد یا چهره اشتباه بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K7" s="56" t="inlineStr">
+      <c r="K7" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1376,22 +1415,22 @@
         </is>
       </c>
       <c r="M7" s="56" t="n"/>
-      <c r="N7" s="56" t="inlineStr">
+      <c r="N7" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O7" s="58" t="inlineStr">
+      <c r="O7" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P7" s="58" t="inlineStr">
+      <c r="P7" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q7" s="60">
+      <c r="Q7" s="64">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -1402,54 +1441,54 @@
           <t>IM-010</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="84" t="inlineStr">
         <is>
           <t>وتوی خروجی</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="85" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="84" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است و از پنل گزینهٔ «قطع خروجی هنگام قفل» روشن است؛ یک بار روی خروجی داری</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="84" t="inlineStr">
         <is>
           <t>گام ۱: برق شهر را بکش.
 گام ۲: بار را نگاه کن؛ نباید از این باتری روشن شود.
 گام ۳: برق شهر را برگردان.</t>
         </is>
       </c>
-      <c r="F8" s="63" t="inlineStr">
+      <c r="F8" s="86" t="inlineStr">
         <is>
           <t>قطع برق شهر در قفل با وتوی خروجی</t>
         </is>
       </c>
-      <c r="G8" s="63" t="inlineStr">
+      <c r="G8" s="86" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="61" t="inlineStr">
+      <c r="H8" s="84" t="inlineStr">
         <is>
           <t>باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود</t>
         </is>
       </c>
-      <c r="I8" s="61" t="inlineStr">
+      <c r="I8" s="84" t="inlineStr">
         <is>
           <t>وتو تا پاک‌شدن قفل</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: باتریِ قفل‌شده روی خروجی نمی‌آید و بار روشن نمی‌شود؛ با برگشت برق شهر کار عادی می‌شود. اگر بار از باتری قفل‌شده روشن شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K8" s="61" t="inlineStr">
+      <c r="K8" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1460,22 +1499,22 @@
         </is>
       </c>
       <c r="M8" s="61" t="n"/>
-      <c r="N8" s="61" t="inlineStr">
+      <c r="N8" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O8" s="63" t="inlineStr">
+      <c r="O8" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P8" s="63" t="inlineStr">
+      <c r="P8" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q8" s="64">
+      <c r="Q8" s="87">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -1486,53 +1525,53 @@
           <t>IM-013</t>
         </is>
       </c>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>ریست با تعویض باتری</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است و چراغ قرمز چشمک می‌زند</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>گام ۱: هر دو باتری را با دو باتری سالم و هم‌شارژ عوض کن.
 گام ۲: چند دقیقه صبر کن و چراغ‌ها را ببین.</t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>تعویض واقعی هر دو باتری</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H9" s="56" t="inlineStr">
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I9" s="56" t="inlineStr">
+      <c r="I9" s="61" t="inlineStr">
         <is>
           <t>پاک‌شدن خودکار با تعویض</t>
         </is>
       </c>
-      <c r="J9" s="56" t="inlineStr">
+      <c r="J9" s="61" t="inlineStr">
         <is>
           <t>باید ببینید: با تعویض باتری قفل خودش پاک می‌شود، چشمک قرمز می‌رود و رفتار عادی برمی‌گردد. اگر با باتری سالم قفل ماند، قبول نیست.</t>
         </is>
       </c>
-      <c r="K9" s="56" t="inlineStr">
+      <c r="K9" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1543,22 +1582,22 @@
         </is>
       </c>
       <c r="M9" s="56" t="n"/>
-      <c r="N9" s="56" t="inlineStr">
+      <c r="N9" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O9" s="58" t="inlineStr">
+      <c r="O9" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P9" s="58" t="inlineStr">
+      <c r="P9" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q9" s="60">
+      <c r="Q9" s="64">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -1569,53 +1608,53 @@
           <t>IM-002</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="84" t="inlineStr">
         <is>
           <t>گیت زمانی پس از شارژ</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="85" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="84" t="inlineStr">
         <is>
           <t>باتری‌ها تازه شارژشان تمام شده است</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E10" s="84" t="inlineStr">
         <is>
           <t>گام ۱: درست بعد از تمام‌شدن شارژ، یک باتری را کمی ضعیف کن (لامپ ۱۲ ولت).
 گام ۲: در همان دقایق اول پنل را چک کن.</t>
         </is>
       </c>
-      <c r="F10" s="63" t="inlineStr">
+      <c r="F10" s="86" t="inlineStr">
         <is>
           <t>اختلاف بلافاصله بعد از شارژ</t>
         </is>
       </c>
-      <c r="G10" s="63" t="inlineStr">
+      <c r="G10" s="86" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H10" s="61" t="inlineStr">
+      <c r="H10" s="84" t="inlineStr">
         <is>
           <t>درست بعد از شارژ رویداد حساب نمی‌شود؛ دستگاه اول فرصت استراحت و جاافتادن می‌دهد</t>
         </is>
       </c>
-      <c r="I10" s="61" t="inlineStr">
+      <c r="I10" s="84" t="inlineStr">
         <is>
           <t>بدون رویداد زودهنگام</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: درست بعد از شارژ رویدادی حساب نمی‌شود و دستگاه اول فرصت استراحت می‌دهد. اگر فوری بعد از شارژ رویداد شمرد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K10" s="61" t="inlineStr">
+      <c r="K10" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1626,22 +1665,22 @@
         </is>
       </c>
       <c r="M10" s="61" t="n"/>
-      <c r="N10" s="61" t="inlineStr">
+      <c r="N10" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O10" s="63" t="inlineStr">
+      <c r="O10" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P10" s="63" t="inlineStr">
+      <c r="P10" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q10" s="64">
+      <c r="Q10" s="87">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -1736,53 +1775,53 @@
           <t>IM-006</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="84" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="85" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="65" t="inlineStr">
+      <c r="D12" s="88" t="inlineStr">
         <is>
           <t>چند رویداد عدم‌توازن را با IM-001 ساخته‌ای و شمرده شده‌اند</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="E12" s="84" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: دوباره روشن کن و شمارنده را در پنل بخوان.</t>
         </is>
       </c>
-      <c r="F12" s="63" t="inlineStr">
+      <c r="F12" s="86" t="inlineStr">
         <is>
           <t>قطع و وصل کامل برق</t>
         </is>
       </c>
-      <c r="G12" s="63" t="inlineStr">
+      <c r="G12" s="86" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="61" t="inlineStr">
+      <c r="H12" s="84" t="inlineStr">
         <is>
           <t>شمارندهٔ رویدادها بعد از روشن‌شدن سر جایش هست و از صفر شروع نشده</t>
         </is>
       </c>
-      <c r="I12" s="61" t="inlineStr">
+      <c r="I12" s="84" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: شمارندهٔ رویدادها بعد از خاموش و روشن‌کردن سر جایش است و از صفر شروع نشده. اگر صفر شده بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K12" s="61" t="inlineStr">
+      <c r="K12" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1793,22 +1832,22 @@
         </is>
       </c>
       <c r="M12" s="61" t="n"/>
-      <c r="N12" s="61" t="inlineStr">
+      <c r="N12" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O12" s="63" t="inlineStr">
+      <c r="O12" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P12" s="63" t="inlineStr">
+      <c r="P12" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q12" s="64">
+      <c r="Q12" s="87">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -1819,54 +1858,54 @@
           <t>IM-009</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>بوق ساعتی</t>
         </is>
       </c>
-      <c r="C13" s="58" t="inlineStr">
+      <c r="C13" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="66" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است (IM-007)؛ از پنل دورهٔ بوق قفل را موقتاً کوتاه کرده‌ای</t>
         </is>
       </c>
-      <c r="E13" s="56" t="inlineStr">
+      <c r="E13" s="61" t="inlineStr">
         <is>
           <t>گام ۱: با کرنومتر صبر کن تا وقت بوق برسد.
 گام ۲: به بوق و چراغ قرمز دقت کن.
 گام ۳: دورهٔ بوق را به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F13" s="58" t="inlineStr">
+      <c r="F13" s="63" t="inlineStr">
         <is>
           <t>قفل فعال با دورهٔ بوق کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G13" s="58" t="inlineStr">
+      <c r="G13" s="63" t="inlineStr">
         <is>
           <t>چند دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="56" t="inlineStr">
+      <c r="H13" s="61" t="inlineStr">
         <is>
           <t>سر وقت، یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I13" s="56" t="inlineStr">
+      <c r="I13" s="61" t="inlineStr">
         <is>
           <t>بوق دوره‌ای در قفل</t>
         </is>
       </c>
-      <c r="J13" s="56" t="inlineStr">
+      <c r="J13" s="61" t="inlineStr">
         <is>
           <t>باید بشنوید و ببینید: سر وقت یک بوق کوتاه می‌آید و قرمز همچنان چشمک می‌زند. اگر بوق نیامد یا به‌هم‌ریخته بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K13" s="56" t="inlineStr">
+      <c r="K13" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1877,22 +1916,22 @@
         </is>
       </c>
       <c r="M13" s="56" t="n"/>
-      <c r="N13" s="56" t="inlineStr">
+      <c r="N13" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O13" s="58" t="inlineStr">
+      <c r="O13" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P13" s="58" t="inlineStr">
+      <c r="P13" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q13" s="60">
+      <c r="Q13" s="64">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
@@ -1903,53 +1942,53 @@
           <t>IM-011</t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="84" t="inlineStr">
         <is>
           <t>برداشتن تیک ۱۱۷</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="86" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
+      <c r="D14" s="84" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است؛ گزینهٔ قطع خروجی را از پنل خاموش می‌کنی</t>
         </is>
       </c>
-      <c r="E14" s="56" t="inlineStr">
+      <c r="E14" s="84" t="inlineStr">
         <is>
           <t>گام ۱: تیک قطع خروجی را از پنل بردار.
 گام ۲: برق شهر را بکش و بار را نگاه کن.</t>
         </is>
       </c>
-      <c r="F14" s="58" t="inlineStr">
+      <c r="F14" s="86" t="inlineStr">
         <is>
           <t>برداشتن تیک قطع خروجی در قفل</t>
         </is>
       </c>
-      <c r="G14" s="58" t="inlineStr">
+      <c r="G14" s="86" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="56" t="inlineStr">
+      <c r="H14" s="84" t="inlineStr">
         <is>
           <t>این بار باتری روی خروجی می‌آید و بار کار می‌کند، هرچند قفل هنوز هست</t>
         </is>
       </c>
-      <c r="I14" s="56" t="inlineStr">
+      <c r="I14" s="84" t="inlineStr">
         <is>
           <t>وتو تابع تیک پنل</t>
         </is>
       </c>
-      <c r="J14" s="56" t="inlineStr">
+      <c r="J14" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: با برداشتن تیک، باتری روی خروجی می‌آید و بار کار می‌کند هرچند قفل هنوز هست. اگر وتو همیشگی ماند، قبول نیست.</t>
         </is>
       </c>
-      <c r="K14" s="56" t="inlineStr">
+      <c r="K14" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1960,22 +1999,22 @@
         </is>
       </c>
       <c r="M14" s="56" t="n"/>
-      <c r="N14" s="56" t="inlineStr">
+      <c r="N14" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O14" s="58" t="inlineStr">
+      <c r="O14" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P14" s="58" t="inlineStr">
+      <c r="P14" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q14" s="60">
+      <c r="Q14" s="87">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -2069,54 +2108,54 @@
           <t>IM-014</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="84" t="inlineStr">
         <is>
           <t>جدا شدن کوتاه</t>
         </is>
       </c>
-      <c r="C16" s="63" t="inlineStr">
+      <c r="C16" s="86" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr">
+      <c r="D16" s="84" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال است</t>
         </is>
       </c>
-      <c r="E16" s="65" t="inlineStr">
+      <c r="E16" s="88" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌ها را فقط چند ثانیه جدا کن و سریع وصل کن.
 گام ۲: چراغ‌ها را ببین؛ قفل باید سر جایش باشد.
 گام ۳: حالا تعویض واقعی (IM-013) انجام بده و تفاوت را ببین.</t>
         </is>
       </c>
-      <c r="F16" s="63" t="inlineStr">
+      <c r="F16" s="86" t="inlineStr">
         <is>
           <t>جدا کردن کوتاه در برابر تعویض واقعی</t>
         </is>
       </c>
-      <c r="G16" s="63" t="inlineStr">
+      <c r="G16" s="86" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H16" s="61" t="inlineStr">
+      <c r="H16" s="84" t="inlineStr">
         <is>
           <t>قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند</t>
         </is>
       </c>
-      <c r="I16" s="61" t="inlineStr">
+      <c r="I16" s="84" t="inlineStr">
         <is>
           <t>قفل در برابر قطع کوتاه مقاوم</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: قطع چندثانیه‌ای قفل را پاک نمی‌کند؛ فقط تعویض واقعی پاکش می‌کند. اگر با قطع کوتاه پاک شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K16" s="61" t="inlineStr">
+      <c r="K16" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -2127,22 +2166,22 @@
         </is>
       </c>
       <c r="M16" s="61" t="n"/>
-      <c r="N16" s="61" t="inlineStr">
+      <c r="N16" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O16" s="63" t="inlineStr">
+      <c r="O16" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P16" s="63" t="inlineStr">
+      <c r="P16" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q16" s="64">
+      <c r="Q16" s="87">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -2241,53 +2280,53 @@
           <t>IM-017</t>
         </is>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="84" t="inlineStr">
         <is>
           <t>ماندگاری شمارنده و قفل پس از قطع برق</t>
         </is>
       </c>
-      <c r="C18" s="57" t="inlineStr">
+      <c r="C18" s="85" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D18" s="56" t="inlineStr">
+      <c r="D18" s="84" t="inlineStr">
         <is>
           <t>قفل عدم‌توازن فعال و شمارنده چند رویداد دارد</t>
         </is>
       </c>
-      <c r="E18" s="56" t="inlineStr">
+      <c r="E18" s="84" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: روشن کن و چراغ‌ها و شمارنده را چک کن.</t>
         </is>
       </c>
-      <c r="F18" s="58" t="inlineStr">
+      <c r="F18" s="86" t="inlineStr">
         <is>
           <t>قطع و وصل برق در قفل</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
+      <c r="G18" s="86" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="56" t="inlineStr">
+      <c r="H18" s="84" t="inlineStr">
         <is>
           <t>قفل و شمارنده بعد از روشن‌شدن دقیقاً سر جایشان‌اند</t>
         </is>
       </c>
-      <c r="I18" s="56" t="inlineStr">
+      <c r="I18" s="84" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J18" s="56" t="inlineStr">
+      <c r="J18" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: قفل و شمارنده بعد از خاموش و روشن‌کردن دقیقاً سر جایشان‌اند. اگر با قطع برق پاک شدند، قبول نیست.</t>
         </is>
       </c>
-      <c r="K18" s="56" t="inlineStr">
+      <c r="K18" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -2297,27 +2336,27 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="56" t="inlineStr">
+      <c r="M18" s="84" t="inlineStr">
         <is>
           <t>'برنامه تست'!A5</t>
         </is>
       </c>
-      <c r="N18" s="56" t="inlineStr">
+      <c r="N18" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O18" s="58" t="inlineStr">
+      <c r="O18" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P18" s="58" t="inlineStr">
+      <c r="P18" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q18" s="60">
+      <c r="Q18" s="87">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -2328,53 +2367,53 @@
           <t>IM-005</t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>نوسان دور حد</t>
         </is>
       </c>
-      <c r="C19" s="58" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>به‌جای یک باتری منبع آزمایشگاهی گذاشته‌ای تا ولتاژش را بازی بدهی</t>
         </is>
       </c>
-      <c r="E19" s="56" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را دور مرز اختلاف مجاز، کم‌کم بالا و پایین کن.
 گام ۲: شمارندهٔ رویداد را در پنل زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F19" s="58" t="inlineStr">
+      <c r="F19" s="63" t="inlineStr">
         <is>
           <t>نوسان ولتاژ یک نیم دور مرز</t>
         </is>
       </c>
-      <c r="G19" s="58" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>ربع ساعت</t>
         </is>
       </c>
-      <c r="H19" s="56" t="inlineStr">
+      <c r="H19" s="61" t="inlineStr">
         <is>
           <t>با نوسان‌های کوچک شمارنده بالا نمی‌رود؛ فقط اختلاف واقعی و ماندگار شمرده می‌شود</t>
         </is>
       </c>
-      <c r="I19" s="56" t="inlineStr">
+      <c r="I19" s="61" t="inlineStr">
         <is>
           <t>بدون رویداد کاذب</t>
         </is>
       </c>
-      <c r="J19" s="56" t="inlineStr">
+      <c r="J19" s="61" t="inlineStr">
         <is>
           <t>باید ببینید: با نوسان‌های کوچک شمارنده بالا نمی‌رود و فقط اختلاف واقعی و ماندگار شمرده می‌شود. اگر با هر نوسان شمرد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K19" s="56" t="inlineStr">
+      <c r="K19" s="61" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -2385,22 +2424,22 @@
         </is>
       </c>
       <c r="M19" s="56" t="n"/>
-      <c r="N19" s="56" t="inlineStr">
+      <c r="N19" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O19" s="58" t="inlineStr">
+      <c r="O19" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P19" s="58" t="inlineStr">
+      <c r="P19" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q19" s="60">
+      <c r="Q19" s="64">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
@@ -2411,53 +2450,53 @@
           <t>IM-015</t>
         </is>
       </c>
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="84" t="inlineStr">
         <is>
           <t>بازهٔ پارامترها</t>
         </is>
       </c>
-      <c r="C20" s="58" t="inlineStr">
+      <c r="C20" s="86" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D20" s="56" t="inlineStr">
+      <c r="D20" s="84" t="inlineStr">
         <is>
           <t>پنل باز است و تنظیم‌های عدم‌توازن را می‌بینی</t>
         </is>
       </c>
-      <c r="E20" s="56" t="inlineStr">
+      <c r="E20" s="84" t="inlineStr">
         <is>
           <t>گام ۱: از پنل یک حدّ ناممکن بفرست (مثلاً اختلاف مجاز خیلی بزرگ یا منفیِ معادل).
 گام ۲: مقدار ذخیره‌شده را دوباره از پنل بخوان.</t>
         </is>
       </c>
-      <c r="F20" s="58" t="inlineStr">
+      <c r="F20" s="86" t="inlineStr">
         <is>
           <t>فرستادن مقدار بیرون بازه از پنل</t>
         </is>
       </c>
-      <c r="G20" s="58" t="inlineStr">
+      <c r="G20" s="86" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="56" t="inlineStr">
+      <c r="H20" s="84" t="inlineStr">
         <is>
           <t>دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند</t>
         </is>
       </c>
-      <c r="I20" s="56" t="inlineStr">
+      <c r="I20" s="84" t="inlineStr">
         <is>
           <t>حفظ مقدار قبلی</t>
         </is>
       </c>
-      <c r="J20" s="56" t="inlineStr">
+      <c r="J20" s="84" t="inlineStr">
         <is>
           <t>باید ببینید: دستگاه مقدار خراب را قبول نمی‌کند و مقدار درست قبلی سر جایش می‌ماند. اگر مقدار ناممکن ذخیره شد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K20" s="56" t="inlineStr">
+      <c r="K20" s="84" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -2468,22 +2507,22 @@
         </is>
       </c>
       <c r="M20" s="56" t="n"/>
-      <c r="N20" s="56" t="inlineStr">
+      <c r="N20" s="84" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O20" s="58" t="inlineStr">
+      <c r="O20" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P20" s="58" t="inlineStr">
+      <c r="P20" s="86" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q20" s="60">
+      <c r="Q20" s="87">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
@@ -3300,7 +3339,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -3365,87 +3404,87 @@
       <c r="Q3" s="53" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3995,7 +4034,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4022,7 +4061,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -4087,87 +4126,87 @@
       <c r="Q3" s="53" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4716,15 +4755,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Imbalance</t>
         </is>
       </c>
-      <c r="B1" s="48" t="n"/>
-      <c r="C1" s="48" t="n"/>
-      <c r="D1" s="48" t="n"/>
-      <c r="E1" s="48" t="n"/>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="53" t="n"/>
@@ -5061,7 +5100,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="72" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Imbalance</t>
         </is>
@@ -5080,23 +5119,23 @@
       <c r="M1" s="53" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="48" t="n"/>
-      <c r="C2" s="48" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="48" t="n"/>
-      <c r="F2" s="48" t="n"/>
-      <c r="G2" s="48" t="n"/>
-      <c r="H2" s="48" t="n"/>
-      <c r="I2" s="48" t="n"/>
-      <c r="J2" s="48" t="n"/>
-      <c r="K2" s="48" t="n"/>
-      <c r="L2" s="48" t="n"/>
-      <c r="M2" s="48" t="n"/>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="70" t="inlineStr">
@@ -5259,7 +5298,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Imbalance</t>
         </is>
@@ -5495,7 +5534,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5606,7 +5645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5620,11 +5659,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="53" t="n"/>
-      <c r="B2" s="53" t="n"/>
-      <c r="C2" s="53" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -5636,7 +5671,6 @@
           <t>Imbalance_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="53" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -5649,7 +5683,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="53" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -5662,7 +5695,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="53" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -5670,13 +5702,13 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="53" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -5684,7 +5716,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,8 +198,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -246,6 +262,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -288,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -518,6 +539,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -977,7 +1019,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="82" t="inlineStr">
         <is>
@@ -987,6 +1028,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="90" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B15" s="91" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1025,9 +1078,12 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="83" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Imbalance</t>
@@ -1049,6 +1105,11 @@
       <c r="O1" s="53" t="n"/>
       <c r="P1" s="53" t="n"/>
       <c r="Q1" s="53" t="n"/>
+      <c r="T1" s="92" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="54" t="inlineStr">
@@ -1072,6 +1133,14 @@
       <c r="O2" s="53" t="n"/>
       <c r="P2" s="53" t="n"/>
       <c r="Q2" s="53" t="n"/>
+      <c r="T2" s="93" t="inlineStr">
+        <is>
+          <t>ولتاژ نیم بالای باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U2" s="94" t="n">
+        <v>12500</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="54" t="inlineStr">
@@ -1095,6 +1164,14 @@
       <c r="O3" s="53" t="n"/>
       <c r="P3" s="53" t="n"/>
       <c r="Q3" s="53" t="n"/>
+      <c r="T3" s="93" t="inlineStr">
+        <is>
+          <t>ولتاژ نیم پایین باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U3" s="94" t="n">
+        <v>11800</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="80" t="inlineStr">
@@ -1181,6 +1258,19 @@
         <is>
           <t>تاریخ</t>
         </is>
+      </c>
+      <c r="R4" s="80" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="93" t="inlineStr">
+        <is>
+          <t>حد اختلاف (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U4" s="94" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
@@ -1266,6 +1356,18 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="91">
+        <f>"اختلاف دو نیم: "&amp;ABS($U$2-$U$3)&amp;" میلی‌ولت؛ "&amp;IF(ABS($U$2-$U$3)&gt;$U$4,"بالای حد است: اگر پیوسته بماند یک رویداد شمرده می‌شود","زیر حد است: عادی")</f>
+        <v/>
+      </c>
+      <c r="T5" s="93" t="inlineStr">
+        <is>
+          <t>تعداد رویداد تا حالا</t>
+        </is>
+      </c>
+      <c r="U5" s="94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="55" t="inlineStr">
@@ -1350,6 +1452,18 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="91">
+        <f>"اختلاف دو نیم: "&amp;ABS($U$2-$U$3)&amp;" میلی‌ولت؛ "&amp;IF(ABS($U$2-$U$3)&gt;$U$4,"بالای حد است: اگر پیوسته بماند یک رویداد شمرده می‌شود","زیر حد است: عادی")</f>
+        <v/>
+      </c>
+      <c r="T6" s="93" t="inlineStr">
+        <is>
+          <t>حد قفل (تعداد رویداد)</t>
+        </is>
+      </c>
+      <c r="U6" s="94" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
@@ -1434,6 +1548,15 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="91">
+        <f>IF($U$5&gt;=$U$6,"قفل فعال: فقط قرمز چشمک می‌زند و بوق دوره‌ای می‌آید",IF(ABS($U$2-$U$3)&gt;$U$4,"هنوز قفل نیست؛ اختلاف بالاست و رویدادها شمرده می‌شوند","قفل نیست"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="95" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="55" t="inlineStr">
@@ -1518,6 +1641,10 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="91">
+        <f>IF($U$5&gt;=$U$6,"قفل + وتوی خروجی (اگر شناسهٔ ۱۱۷ روشن باشد): خروجی قطع است","وتوی خروجی فعال نیست")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="55" t="inlineStr">
@@ -1601,6 +1728,11 @@
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
+      <c r="R9" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="55" t="inlineStr">
@@ -1682,6 +1814,10 @@
       </c>
       <c r="Q10" s="87">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+      <c r="R10" s="91">
+        <f>"اختلاف دو نیم: "&amp;ABS($U$2-$U$3)&amp;" میلی‌ولت؛ "&amp;IF(ABS($U$2-$U$3)&gt;$U$4,"بالای حد است: اگر پیوسته بماند یک رویداد شمرده می‌شود","زیر حد است: عادی")</f>
         <v/>
       </c>
     </row>
@@ -1768,6 +1904,10 @@
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
+      <c r="R11" s="91">
+        <f>"اختلاف دو نیم: "&amp;ABS($U$2-$U$3)&amp;" میلی‌ولت؛ "&amp;IF(ABS($U$2-$U$3)&gt;$U$4,"بالای حد است: اگر پیوسته بماند یک رویداد شمرده می‌شود","زیر حد است: عادی")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="55" t="inlineStr">
@@ -1850,6 +1990,11 @@
       <c r="Q12" s="87">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
+      </c>
+      <c r="R12" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
@@ -1935,6 +2080,10 @@
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
+      <c r="R13" s="91">
+        <f>IF($U$5&gt;=$U$6,"در قفل: بوق دوره‌ای (ساعتی) می‌آید","بوق عدم‌توازن نمی‌آید")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="55" t="inlineStr">
@@ -2018,6 +2167,11 @@
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
+      <c r="R14" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
@@ -2100,6 +2254,11 @@
       <c r="Q15" s="64">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
+      </c>
+      <c r="R15" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
@@ -2185,6 +2344,11 @@
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
+      <c r="R16" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="55" t="inlineStr">
@@ -2273,6 +2437,11 @@
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
+      <c r="R17" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="55" t="inlineStr">
@@ -2360,6 +2529,11 @@
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
+      <c r="R18" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="55" t="inlineStr">
@@ -2443,6 +2617,10 @@
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
+      <c r="R19" s="91">
+        <f>"اختلاف دو نیم: "&amp;ABS($U$2-$U$3)&amp;" میلی‌ولت؛ "&amp;IF(ABS($U$2-$U$3)&gt;$U$4,"بالای حد است: اگر پیوسته بماند یک رویداد شمرده می‌شود","زیر حد است: عادی")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="55" t="inlineStr">
@@ -2525,6 +2703,11 @@
       <c r="Q20" s="87">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
+      </c>
+      <c r="R20" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3289,6 +3472,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q60"/>
+  <mergeCells count="2">
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T7:U7"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
@@ -5645,7 +5832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5659,7 +5846,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -5708,7 +5894,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
